--- a/produits/management/commands/articles.xlsx
+++ b/produits/management/commands/articles.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5389" uniqueCount="2609">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5389" uniqueCount="2608">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -4912,7 +4912,7 @@
     <t xml:space="preserve">350000.0</t>
   </si>
   <si>
-    <t xml:space="preserve">Pampers.Douceur.S48	</t>
+    <t xml:space="preserve">Pampers.Douceur.S48</t>
   </si>
   <si>
     <t xml:space="preserve">Savon Classic</t>
@@ -5224,7 +5224,7 @@
     <t xml:space="preserve">Insecticide.Meilleur.300ml</t>
   </si>
   <si>
-    <t xml:space="preserve">Biscuit.Monsta.Bites.50Pièces	</t>
+    <t xml:space="preserve">Biscuit.Monsta.Bites.50Pièces</t>
   </si>
   <si>
     <t xml:space="preserve">Papier.Serviette.Expert</t>
@@ -5311,9 +5311,6 @@
     <t xml:space="preserve">76.0</t>
   </si>
   <si>
-    <t xml:space="preserve">Yo! best PF	</t>
-  </si>
-  <si>
     <t xml:space="preserve">Juwisy 12Bouteilles</t>
   </si>
   <si>
@@ -5416,7 +5413,7 @@
     <t xml:space="preserve">Cirage.Vivo.Pâte.Noir</t>
   </si>
   <si>
-    <t xml:space="preserve">Sac.Farine.Champion.25kg	</t>
+    <t xml:space="preserve">Sac.Farine.Champion.25kg</t>
   </si>
   <si>
     <t xml:space="preserve">49500.0</t>
@@ -5431,7 +5428,7 @@
     <t xml:space="preserve">534.0</t>
   </si>
   <si>
-    <t xml:space="preserve">Huile.Soyola.5Litres	</t>
+    <t xml:space="preserve">Huile.Soyola.5Litres</t>
   </si>
   <si>
     <t xml:space="preserve">Nkolo Mboka</t>
@@ -5491,7 +5488,7 @@
     <t xml:space="preserve">Handy.Andy 500ml</t>
   </si>
   <si>
-    <t xml:space="preserve">Bonjour 6g	</t>
+    <t xml:space="preserve">Bonjour 6g</t>
   </si>
   <si>
     <t xml:space="preserve">Benny Poulet</t>
@@ -5500,7 +5497,7 @@
     <t xml:space="preserve">Chaussette.Blanche.N°25-28</t>
   </si>
   <si>
-    <t xml:space="preserve">Chocolat.Toffee.Bar.Sachet	</t>
+    <t xml:space="preserve">Chocolat.Toffee.Bar.Sachet</t>
   </si>
   <si>
     <t xml:space="preserve">290.0</t>
@@ -5629,7 +5626,7 @@
     <t xml:space="preserve">PH.Douceur.Bleu.4Pièces</t>
   </si>
   <si>
-    <t xml:space="preserve">PH.Douceur.Bleu.20Pièces	</t>
+    <t xml:space="preserve">PH.Douceur.Bleu.20Pièces</t>
   </si>
   <si>
     <t xml:space="preserve">9340.0</t>
@@ -5647,7 +5644,7 @@
     <t xml:space="preserve">Bic.Europa.Bleu.GF</t>
   </si>
   <si>
-    <t xml:space="preserve">Mayonnaise.Culino.Lemon.500ml	</t>
+    <t xml:space="preserve">Mayonnaise.Culino.Lemon.500ml</t>
   </si>
   <si>
     <t xml:space="preserve">Max Maracuja</t>
@@ -5719,10 +5716,10 @@
     <t xml:space="preserve">28.0</t>
   </si>
   <si>
-    <t xml:space="preserve">Top.Tomate.Chaîne	</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Top.Pondu.Chaîne	</t>
+    <t xml:space="preserve">Top.Tomate.Chaîne</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Top.Pondu.Chaîne</t>
   </si>
   <si>
     <t xml:space="preserve">ThÃ© Noki</t>
@@ -5854,7 +5851,7 @@
     <t xml:space="preserve">LongLife.Milk.250ml</t>
   </si>
   <si>
-    <t xml:space="preserve">LongLife.Milk.500ml	</t>
+    <t xml:space="preserve">LongLife.Milk.500ml</t>
   </si>
   <si>
     <t xml:space="preserve">30000.0</t>
@@ -6004,7 +6001,7 @@
     <t xml:space="preserve">1750000.0</t>
   </si>
   <si>
-    <t xml:space="preserve">Crème.Bio.Plus.Aloé.175ml	</t>
+    <t xml:space="preserve">Crème.Bio.Plus.Aloé.175ml</t>
   </si>
   <si>
     <t xml:space="preserve">Crème.Miki.Clair.110ml</t>
@@ -6028,13 +6025,13 @@
     <t xml:space="preserve">Hard.Rockk.Energy</t>
   </si>
   <si>
-    <t xml:space="preserve">Malti.Café.300ml	</t>
+    <t xml:space="preserve">Malti.Café.300ml</t>
   </si>
   <si>
     <t xml:space="preserve">21840.0</t>
   </si>
   <si>
-    <t xml:space="preserve">Malti.Café.500ml	</t>
+    <t xml:space="preserve">Malti.Café.500ml</t>
   </si>
   <si>
     <t xml:space="preserve">Fiesta</t>
@@ -6067,7 +6064,7 @@
     <t xml:space="preserve">Gilette.Pro.500</t>
   </si>
   <si>
-    <t xml:space="preserve">Sac.Bleu.Sucre.50g	</t>
+    <t xml:space="preserve">Sac.Bleu.Sucre.50g</t>
   </si>
   <si>
     <t xml:space="preserve">158800.0</t>
@@ -6079,7 +6076,7 @@
     <t xml:space="preserve">5330.0</t>
   </si>
   <si>
-    <t xml:space="preserve">Déodorant.Explore.Citris.Women.200ml	</t>
+    <t xml:space="preserve">Déodorant.Explore.Citris.Women.200ml</t>
   </si>
   <si>
     <t xml:space="preserve">Déodorant.Explore.Original.200ml</t>
@@ -6115,7 +6112,7 @@
     <t xml:space="preserve">Huile.Bio.Plus.Coco.60ml</t>
   </si>
   <si>
-    <t xml:space="preserve">Crème.Bio.Plus.Lemon.175ml	</t>
+    <t xml:space="preserve">Crème.Bio.Plus.Lemon.175ml</t>
   </si>
   <si>
     <t xml:space="preserve">77.0</t>
@@ -6142,13 +6139,13 @@
     <t xml:space="preserve">18210.0</t>
   </si>
   <si>
-    <t xml:space="preserve">Huile.Bio.Plus.Lemon.60ml	</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Huile.Bio.Plus.Papaya.60ml	</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Huile.Bio.Plus.Aloé.60ml	</t>
+    <t xml:space="preserve">Huile.Bio.Plus.Lemon.60ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Huile.Bio.Plus.Papaya.60ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Huile.Bio.Plus.Aloé.60ml</t>
   </si>
   <si>
     <t xml:space="preserve">27.0</t>
@@ -6244,13 +6241,13 @@
     <t xml:space="preserve">Creamy.Yogourt.Pop.Sachet</t>
   </si>
   <si>
-    <t xml:space="preserve">Crème.Caro.Light.300ml	.</t>
+    <t xml:space="preserve">Crème.Caro.Light.300ml.</t>
   </si>
   <si>
     <t xml:space="preserve">Crème.Extra.Clair.For.Men.Bleu.150g</t>
   </si>
   <si>
-    <t xml:space="preserve">Crème.Extra.Clair.Orange.Bleu.300ml	</t>
+    <t xml:space="preserve">Crème.Extra.Clair.Orange.Bleu.300ml</t>
   </si>
   <si>
     <t xml:space="preserve">4770.0</t>
@@ -6415,10 +6412,10 @@
     <t xml:space="preserve">Déodorant.Explore.Cool.Breeze.Women.200ml</t>
   </si>
   <si>
-    <t xml:space="preserve">Déodorant.Explore.Desiré.Men.200ml	</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Déodorant.Explore.Women.200ml	</t>
+    <t xml:space="preserve">Déodorant.Explore.Desiré.Men.200ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Déodorant.Explore.Women.200ml</t>
   </si>
   <si>
     <t xml:space="preserve">Déodorant.Eskoda.Pink.200ml</t>
@@ -6490,10 +6487,10 @@
     <t xml:space="preserve">114.0</t>
   </si>
   <si>
-    <t xml:space="preserve">Déodorant.Explore.Océan.50ml	</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Déodorant.Explore.Original.50ml	</t>
+    <t xml:space="preserve">Déodorant.Explore.Océan.50ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Déodorant.Explore.Original.50ml</t>
   </si>
   <si>
     <t xml:space="preserve">Jimbo Lemon</t>
@@ -6676,13 +6673,13 @@
     <t xml:space="preserve">Ampoule.Meilleur.30Watts</t>
   </si>
   <si>
-    <t xml:space="preserve">Pommade.Vaseline.250ml	</t>
+    <t xml:space="preserve">Pommade.Vaseline.250ml</t>
   </si>
   <si>
     <t xml:space="preserve">5900.0</t>
   </si>
   <si>
-    <t xml:space="preserve">Lotion.Vaseline.Even.Tone.Bleu.Men.400ml	</t>
+    <t xml:space="preserve">Lotion.Vaseline.Even.Tone.Bleu.Men.400ml</t>
   </si>
   <si>
     <t xml:space="preserve">Bouillie Blédine</t>
@@ -6694,7 +6691,7 @@
     <t xml:space="preserve">FruitBom.Ananas</t>
   </si>
   <si>
-    <t xml:space="preserve">Fruticana.Smoothie.Red	</t>
+    <t xml:space="preserve">Fruticana.Smoothie.Red</t>
   </si>
   <si>
     <t xml:space="preserve">Pommade.Vaseline.100ml</t>
@@ -6802,7 +6799,7 @@
     <t xml:space="preserve">Huile.Mama's.Cooking.Oil.2.5Litres</t>
   </si>
   <si>
-    <t xml:space="preserve">Huile.Soyola.2.5Litres	</t>
+    <t xml:space="preserve">Huile.Soyola.2.5Litres</t>
   </si>
   <si>
     <t xml:space="preserve">14850.0</t>
@@ -6835,7 +6832,7 @@
     <t xml:space="preserve">5800.0</t>
   </si>
   <si>
-    <t xml:space="preserve">Pile.Royal.Crayon	</t>
+    <t xml:space="preserve">Pile.Royal.Crayon</t>
   </si>
   <si>
     <t xml:space="preserve">Fruticana.Smoothie.Orange</t>
@@ -6931,7 +6928,7 @@
     <t xml:space="preserve">Canadian.Pure.1.5Litre</t>
   </si>
   <si>
-    <t xml:space="preserve">Boom.400g.box	</t>
+    <t xml:space="preserve">Boom.400g.box</t>
   </si>
   <si>
     <t xml:space="preserve">2720.0</t>
@@ -6973,7 +6970,7 @@
     <t xml:space="preserve">23800.0</t>
   </si>
   <si>
-    <t xml:space="preserve">Biscuit N°1	Milk</t>
+    <t xml:space="preserve">Biscuit N°1Milk</t>
   </si>
   <si>
     <t xml:space="preserve">Hard.Rockk.Tangawis</t>
@@ -7072,13 +7069,13 @@
     <t xml:space="preserve">DÃ©odorant.Xavier.Laurent.Je.t'aime.150ml.</t>
   </si>
   <si>
-    <t xml:space="preserve">Déodorant.Xavier.Laurent.Infinity.150ml	</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Déodorant.Xavier.Laurent.Tango.150ml	</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Déodorant.Xavier.Laurent.L'amour.150ml	</t>
+    <t xml:space="preserve">Déodorant.Xavier.Laurent.Infinity.150ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Déodorant.Xavier.Laurent.Tango.150ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Déodorant.Xavier.Laurent.L'amour.150ml</t>
   </si>
   <si>
     <t xml:space="preserve">Brosse.à.Dent.Cesirch</t>
@@ -7381,7 +7378,7 @@
     <t xml:space="preserve">69.0</t>
   </si>
   <si>
-    <t xml:space="preserve">Appy.Apple.Plastic	</t>
+    <t xml:space="preserve">Appy.Apple.Plastic</t>
   </si>
   <si>
     <t xml:space="preserve">11950.0</t>
@@ -7651,7 +7648,7 @@
     <t xml:space="preserve">Sardine Liberator</t>
   </si>
   <si>
-    <t xml:space="preserve">France.Lait.900g.N°1	</t>
+    <t xml:space="preserve">France.Lait.900g.N°1</t>
   </si>
   <si>
     <t xml:space="preserve">49900.0</t>
@@ -7675,7 +7672,7 @@
     <t xml:space="preserve">109.0</t>
   </si>
   <si>
-    <t xml:space="preserve">Ampoule.Torgh.5.Watts	</t>
+    <t xml:space="preserve">Ampoule.Torgh.5.Watts</t>
   </si>
   <si>
     <t xml:space="preserve">126.0</t>
@@ -7699,7 +7696,7 @@
     <t xml:space="preserve">Dentifrice.Bonjour.100g</t>
   </si>
   <si>
-    <t xml:space="preserve">Dentifrice.Bonjour.50g	</t>
+    <t xml:space="preserve">Dentifrice.Bonjour.50g</t>
   </si>
   <si>
     <t xml:space="preserve">21450.0</t>
@@ -7843,7 +7840,7 @@
     <t xml:space="preserve">Ketchup.Mayo.250ml</t>
   </si>
   <si>
-    <t xml:space="preserve">Juwisi.24Bouteilles.430ml	</t>
+    <t xml:space="preserve">Juwisi.24Bouteilles.430ml</t>
   </si>
   <si>
     <t xml:space="preserve">Coca 300ml</t>
@@ -7948,10 +7945,10 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:N1793"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5.46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="40.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="40.88"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="4.07"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="9.35"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="9.91"/>
@@ -7961,8 +7958,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="10.46"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="8.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="6.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="7.41"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="8.23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="10.46"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="8.79"/>
   </cols>
   <sheetData>
@@ -50502,7 +50498,7 @@
         <v>1207</v>
       </c>
       <c r="B1183" s="0" t="s">
-        <v>1763</v>
+        <v>1496</v>
       </c>
       <c r="C1183" s="0" t="n">
         <v>3</v>
@@ -50537,7 +50533,7 @@
         <v>1208</v>
       </c>
       <c r="B1184" s="0" t="s">
-        <v>1764</v>
+        <v>1763</v>
       </c>
       <c r="C1184" s="0" t="n">
         <v>3</v>
@@ -50575,13 +50571,13 @@
         <v>1209</v>
       </c>
       <c r="B1185" s="0" t="s">
+        <v>1764</v>
+      </c>
+      <c r="C1185" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1185" s="0" t="s">
         <v>1765</v>
-      </c>
-      <c r="C1185" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1185" s="0" t="s">
-        <v>1766</v>
       </c>
       <c r="F1185" s="0" t="s">
         <v>512</v>
@@ -50610,13 +50606,13 @@
         <v>1210</v>
       </c>
       <c r="B1186" s="0" t="s">
+        <v>1766</v>
+      </c>
+      <c r="C1186" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="E1186" s="0" t="s">
         <v>1767</v>
-      </c>
-      <c r="C1186" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="E1186" s="0" t="s">
-        <v>1768</v>
       </c>
       <c r="F1186" s="0" t="s">
         <v>22</v>
@@ -50648,13 +50644,13 @@
         <v>1211</v>
       </c>
       <c r="B1187" s="0" t="s">
+        <v>1768</v>
+      </c>
+      <c r="C1187" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="E1187" s="0" t="s">
         <v>1769</v>
-      </c>
-      <c r="C1187" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="E1187" s="0" t="s">
-        <v>1770</v>
       </c>
       <c r="F1187" s="0" t="s">
         <v>22</v>
@@ -50683,7 +50679,7 @@
         <v>1212</v>
       </c>
       <c r="B1188" s="0" t="s">
-        <v>1771</v>
+        <v>1770</v>
       </c>
       <c r="C1188" s="0" t="n">
         <v>5</v>
@@ -50692,7 +50688,7 @@
         <v>248</v>
       </c>
       <c r="F1188" s="0" t="s">
-        <v>1772</v>
+        <v>1771</v>
       </c>
       <c r="G1188" s="0" t="n">
         <v>0</v>
@@ -50718,7 +50714,7 @@
         <v>1213</v>
       </c>
       <c r="B1189" s="0" t="s">
-        <v>1773</v>
+        <v>1772</v>
       </c>
       <c r="C1189" s="0" t="n">
         <v>3</v>
@@ -50756,7 +50752,7 @@
         <v>1214</v>
       </c>
       <c r="B1190" s="0" t="s">
-        <v>1774</v>
+        <v>1773</v>
       </c>
       <c r="C1190" s="0" t="n">
         <v>3</v>
@@ -50765,7 +50761,7 @@
         <v>312</v>
       </c>
       <c r="F1190" s="0" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="G1190" s="0" t="n">
         <v>0</v>
@@ -50791,7 +50787,7 @@
         <v>1215</v>
       </c>
       <c r="B1191" s="0" t="s">
-        <v>1776</v>
+        <v>1775</v>
       </c>
       <c r="C1191" s="0" t="n">
         <v>3</v>
@@ -50829,13 +50825,13 @@
         <v>1216</v>
       </c>
       <c r="B1192" s="0" t="s">
+        <v>1776</v>
+      </c>
+      <c r="C1192" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="E1192" s="0" t="s">
         <v>1777</v>
-      </c>
-      <c r="C1192" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="E1192" s="0" t="s">
-        <v>1778</v>
       </c>
       <c r="F1192" s="0" t="s">
         <v>22</v>
@@ -50867,7 +50863,7 @@
         <v>1217</v>
       </c>
       <c r="B1193" s="0" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="C1193" s="0" t="n">
         <v>3</v>
@@ -50902,7 +50898,7 @@
         <v>1218</v>
       </c>
       <c r="B1194" s="0" t="s">
-        <v>1780</v>
+        <v>1779</v>
       </c>
       <c r="C1194" s="0" t="n">
         <v>3</v>
@@ -50940,13 +50936,13 @@
         <v>1219</v>
       </c>
       <c r="B1195" s="0" t="s">
+        <v>1780</v>
+      </c>
+      <c r="C1195" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="E1195" s="0" t="s">
         <v>1781</v>
-      </c>
-      <c r="C1195" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="E1195" s="0" t="s">
-        <v>1782</v>
       </c>
       <c r="F1195" s="0" t="s">
         <v>22</v>
@@ -50975,13 +50971,13 @@
         <v>1220</v>
       </c>
       <c r="B1196" s="0" t="s">
+        <v>1782</v>
+      </c>
+      <c r="C1196" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="E1196" s="0" t="s">
         <v>1783</v>
-      </c>
-      <c r="C1196" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="E1196" s="0" t="s">
-        <v>1784</v>
       </c>
       <c r="F1196" s="0" t="s">
         <v>22</v>
@@ -51013,13 +51009,13 @@
         <v>1221</v>
       </c>
       <c r="B1197" s="0" t="s">
+        <v>1784</v>
+      </c>
+      <c r="C1197" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="E1197" s="0" t="s">
         <v>1785</v>
-      </c>
-      <c r="C1197" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="E1197" s="0" t="s">
-        <v>1786</v>
       </c>
       <c r="F1197" s="0" t="s">
         <v>22</v>
@@ -51051,7 +51047,7 @@
         <v>1222</v>
       </c>
       <c r="B1198" s="0" t="s">
-        <v>1787</v>
+        <v>1786</v>
       </c>
       <c r="C1198" s="0" t="n">
         <v>5</v>
@@ -51089,13 +51085,13 @@
         <v>1223</v>
       </c>
       <c r="B1199" s="0" t="s">
+        <v>1787</v>
+      </c>
+      <c r="C1199" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="E1199" s="0" t="s">
         <v>1788</v>
-      </c>
-      <c r="C1199" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="E1199" s="0" t="s">
-        <v>1789</v>
       </c>
       <c r="F1199" s="0" t="s">
         <v>22</v>
@@ -51127,13 +51123,13 @@
         <v>1224</v>
       </c>
       <c r="B1200" s="0" t="s">
+        <v>1789</v>
+      </c>
+      <c r="C1200" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="E1200" s="0" t="s">
         <v>1790</v>
-      </c>
-      <c r="C1200" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="E1200" s="0" t="s">
-        <v>1791</v>
       </c>
       <c r="F1200" s="0" t="s">
         <v>22</v>
@@ -51165,13 +51161,13 @@
         <v>1225</v>
       </c>
       <c r="B1201" s="0" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="C1201" s="0" t="n">
         <v>5</v>
       </c>
       <c r="E1201" s="0" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="F1201" s="0" t="s">
         <v>22</v>
@@ -51203,13 +51199,13 @@
         <v>1226</v>
       </c>
       <c r="B1202" s="0" t="s">
+        <v>1792</v>
+      </c>
+      <c r="C1202" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1202" s="0" t="s">
         <v>1793</v>
-      </c>
-      <c r="C1202" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1202" s="0" t="s">
-        <v>1794</v>
       </c>
       <c r="F1202" s="0" t="s">
         <v>22</v>
@@ -51238,13 +51234,13 @@
         <v>1227</v>
       </c>
       <c r="B1203" s="0" t="s">
+        <v>1794</v>
+      </c>
+      <c r="C1203" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1203" s="0" t="s">
         <v>1795</v>
-      </c>
-      <c r="C1203" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1203" s="0" t="s">
-        <v>1796</v>
       </c>
       <c r="F1203" s="0" t="s">
         <v>22</v>
@@ -51273,7 +51269,7 @@
         <v>1228</v>
       </c>
       <c r="B1204" s="0" t="s">
-        <v>1797</v>
+        <v>1796</v>
       </c>
       <c r="C1204" s="0" t="n">
         <v>3</v>
@@ -51311,13 +51307,13 @@
         <v>1229</v>
       </c>
       <c r="B1205" s="0" t="s">
+        <v>1797</v>
+      </c>
+      <c r="C1205" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1205" s="0" t="s">
         <v>1798</v>
-      </c>
-      <c r="C1205" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1205" s="0" t="s">
-        <v>1799</v>
       </c>
       <c r="F1205" s="0" t="s">
         <v>22</v>
@@ -51349,7 +51345,7 @@
         <v>1230</v>
       </c>
       <c r="B1206" s="0" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="C1206" s="0" t="n">
         <v>3</v>
@@ -51387,7 +51383,7 @@
         <v>1231</v>
       </c>
       <c r="B1207" s="0" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="C1207" s="0" t="n">
         <v>5</v>
@@ -51396,7 +51392,7 @@
         <v>162</v>
       </c>
       <c r="F1207" s="0" t="s">
-        <v>1802</v>
+        <v>1801</v>
       </c>
       <c r="G1207" s="0" t="n">
         <v>0</v>
@@ -51422,7 +51418,7 @@
         <v>1232</v>
       </c>
       <c r="B1208" s="0" t="s">
-        <v>1803</v>
+        <v>1802</v>
       </c>
       <c r="C1208" s="0" t="n">
         <v>3</v>
@@ -51457,13 +51453,13 @@
         <v>1233</v>
       </c>
       <c r="B1209" s="0" t="s">
+        <v>1803</v>
+      </c>
+      <c r="C1209" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1209" s="0" t="s">
         <v>1804</v>
-      </c>
-      <c r="C1209" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1209" s="0" t="s">
-        <v>1805</v>
       </c>
       <c r="F1209" s="0" t="s">
         <v>977</v>
@@ -51492,7 +51488,7 @@
         <v>1234</v>
       </c>
       <c r="B1210" s="0" t="s">
-        <v>1806</v>
+        <v>1805</v>
       </c>
       <c r="C1210" s="0" t="n">
         <v>3</v>
@@ -51501,7 +51497,7 @@
         <v>893</v>
       </c>
       <c r="F1210" s="0" t="s">
-        <v>1807</v>
+        <v>1806</v>
       </c>
       <c r="G1210" s="0" t="n">
         <v>0</v>
@@ -51527,7 +51523,7 @@
         <v>1235</v>
       </c>
       <c r="B1211" s="0" t="s">
-        <v>1808</v>
+        <v>1807</v>
       </c>
       <c r="C1211" s="0" t="n">
         <v>3</v>
@@ -51562,16 +51558,16 @@
         <v>1236</v>
       </c>
       <c r="B1212" s="0" t="s">
+        <v>1808</v>
+      </c>
+      <c r="C1212" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="E1212" s="0" t="s">
         <v>1809</v>
       </c>
-      <c r="C1212" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="E1212" s="0" t="s">
+      <c r="F1212" s="0" t="s">
         <v>1810</v>
-      </c>
-      <c r="F1212" s="0" t="s">
-        <v>1811</v>
       </c>
       <c r="G1212" s="0" t="n">
         <v>0</v>
@@ -51603,7 +51599,7 @@
         <v>3</v>
       </c>
       <c r="E1213" s="0" t="s">
-        <v>1812</v>
+        <v>1811</v>
       </c>
       <c r="F1213" s="0" t="s">
         <v>22</v>
@@ -51635,7 +51631,7 @@
         <v>1238</v>
       </c>
       <c r="B1214" s="0" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="C1214" s="0" t="n">
         <v>5</v>
@@ -51670,7 +51666,7 @@
         <v>1239</v>
       </c>
       <c r="B1215" s="0" t="s">
-        <v>1814</v>
+        <v>1813</v>
       </c>
       <c r="C1215" s="0" t="n">
         <v>5</v>
@@ -51705,7 +51701,7 @@
         <v>1240</v>
       </c>
       <c r="B1216" s="0" t="s">
-        <v>1815</v>
+        <v>1814</v>
       </c>
       <c r="C1216" s="0" t="n">
         <v>3</v>
@@ -51740,7 +51736,7 @@
         <v>1241</v>
       </c>
       <c r="B1217" s="0" t="s">
-        <v>1816</v>
+        <v>1815</v>
       </c>
       <c r="C1217" s="0" t="n">
         <v>3</v>
@@ -51775,7 +51771,7 @@
         <v>1242</v>
       </c>
       <c r="B1218" s="0" t="s">
-        <v>1817</v>
+        <v>1816</v>
       </c>
       <c r="C1218" s="0" t="n">
         <v>3</v>
@@ -51810,7 +51806,7 @@
         <v>1243</v>
       </c>
       <c r="B1219" s="0" t="s">
-        <v>1818</v>
+        <v>1817</v>
       </c>
       <c r="C1219" s="0" t="n">
         <v>3</v>
@@ -51845,7 +51841,7 @@
         <v>1244</v>
       </c>
       <c r="B1220" s="0" t="s">
-        <v>1819</v>
+        <v>1818</v>
       </c>
       <c r="C1220" s="0" t="n">
         <v>3</v>
@@ -51883,13 +51879,13 @@
         <v>1245</v>
       </c>
       <c r="B1221" s="0" t="s">
+        <v>1819</v>
+      </c>
+      <c r="C1221" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1221" s="0" t="s">
         <v>1820</v>
-      </c>
-      <c r="C1221" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1221" s="0" t="s">
-        <v>1821</v>
       </c>
       <c r="F1221" s="0" t="s">
         <v>1659</v>
@@ -51918,7 +51914,7 @@
         <v>1246</v>
       </c>
       <c r="B1222" s="0" t="s">
-        <v>1822</v>
+        <v>1821</v>
       </c>
       <c r="C1222" s="0" t="n">
         <v>3</v>
@@ -51927,7 +51923,7 @@
         <v>153</v>
       </c>
       <c r="F1222" s="0" t="s">
-        <v>1772</v>
+        <v>1771</v>
       </c>
       <c r="G1222" s="0" t="n">
         <v>0</v>
@@ -51953,7 +51949,7 @@
         <v>1247</v>
       </c>
       <c r="B1223" s="0" t="s">
-        <v>1823</v>
+        <v>1822</v>
       </c>
       <c r="C1223" s="0" t="n">
         <v>3</v>
@@ -51988,7 +51984,7 @@
         <v>1248</v>
       </c>
       <c r="B1224" s="0" t="s">
-        <v>1824</v>
+        <v>1823</v>
       </c>
       <c r="C1224" s="0" t="n">
         <v>3</v>
@@ -52023,7 +52019,7 @@
         <v>1249</v>
       </c>
       <c r="B1225" s="0" t="s">
-        <v>1825</v>
+        <v>1824</v>
       </c>
       <c r="C1225" s="0" t="n">
         <v>3</v>
@@ -52058,7 +52054,7 @@
         <v>1250</v>
       </c>
       <c r="B1226" s="0" t="s">
-        <v>1826</v>
+        <v>1825</v>
       </c>
       <c r="C1226" s="0" t="n">
         <v>3</v>
@@ -52067,7 +52063,7 @@
         <v>1710</v>
       </c>
       <c r="F1226" s="0" t="s">
-        <v>1827</v>
+        <v>1826</v>
       </c>
       <c r="G1226" s="0" t="n">
         <v>0</v>
@@ -52093,7 +52089,7 @@
         <v>1251</v>
       </c>
       <c r="B1227" s="0" t="s">
-        <v>1828</v>
+        <v>1827</v>
       </c>
       <c r="C1227" s="0" t="n">
         <v>3</v>
@@ -52131,16 +52127,16 @@
         <v>1252</v>
       </c>
       <c r="B1228" s="0" t="s">
+        <v>1828</v>
+      </c>
+      <c r="C1228" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1228" s="0" t="s">
+        <v>1777</v>
+      </c>
+      <c r="F1228" s="0" t="s">
         <v>1829</v>
-      </c>
-      <c r="C1228" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1228" s="0" t="s">
-        <v>1778</v>
-      </c>
-      <c r="F1228" s="0" t="s">
-        <v>1830</v>
       </c>
       <c r="G1228" s="0" t="n">
         <v>0</v>
@@ -52166,7 +52162,7 @@
         <v>1253</v>
       </c>
       <c r="B1229" s="0" t="s">
-        <v>1831</v>
+        <v>1830</v>
       </c>
       <c r="C1229" s="0" t="n">
         <v>3</v>
@@ -52236,7 +52232,7 @@
         <v>1255</v>
       </c>
       <c r="B1231" s="0" t="s">
-        <v>1832</v>
+        <v>1831</v>
       </c>
       <c r="C1231" s="0" t="n">
         <v>3</v>
@@ -52271,13 +52267,13 @@
         <v>1256</v>
       </c>
       <c r="B1232" s="0" t="s">
+        <v>1832</v>
+      </c>
+      <c r="C1232" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1232" s="0" t="s">
         <v>1833</v>
-      </c>
-      <c r="C1232" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1232" s="0" t="s">
-        <v>1834</v>
       </c>
       <c r="F1232" s="0" t="s">
         <v>22</v>
@@ -52309,7 +52305,7 @@
         <v>1257</v>
       </c>
       <c r="B1233" s="0" t="s">
-        <v>1835</v>
+        <v>1834</v>
       </c>
       <c r="C1233" s="0" t="n">
         <v>3</v>
@@ -52344,7 +52340,7 @@
         <v>1258</v>
       </c>
       <c r="B1234" s="0" t="s">
-        <v>1836</v>
+        <v>1835</v>
       </c>
       <c r="C1234" s="0" t="n">
         <v>3</v>
@@ -52353,7 +52349,7 @@
         <v>1358</v>
       </c>
       <c r="F1234" s="0" t="s">
-        <v>1837</v>
+        <v>1836</v>
       </c>
       <c r="G1234" s="0" t="n">
         <v>0</v>
@@ -52379,7 +52375,7 @@
         <v>1259</v>
       </c>
       <c r="B1235" s="0" t="s">
-        <v>1838</v>
+        <v>1837</v>
       </c>
       <c r="C1235" s="0" t="n">
         <v>3</v>
@@ -52388,7 +52384,7 @@
         <v>351</v>
       </c>
       <c r="F1235" s="0" t="s">
-        <v>1839</v>
+        <v>1838</v>
       </c>
       <c r="G1235" s="0" t="n">
         <v>0</v>
@@ -52414,7 +52410,7 @@
         <v>1260</v>
       </c>
       <c r="B1236" s="0" t="s">
-        <v>1840</v>
+        <v>1839</v>
       </c>
       <c r="C1236" s="0" t="n">
         <v>3</v>
@@ -52423,7 +52419,7 @@
         <v>117</v>
       </c>
       <c r="F1236" s="0" t="s">
-        <v>1841</v>
+        <v>1840</v>
       </c>
       <c r="G1236" s="0" t="n">
         <v>0</v>
@@ -52449,7 +52445,7 @@
         <v>1261</v>
       </c>
       <c r="B1237" s="0" t="s">
-        <v>1842</v>
+        <v>1841</v>
       </c>
       <c r="C1237" s="0" t="n">
         <v>3</v>
@@ -52458,7 +52454,7 @@
         <v>886</v>
       </c>
       <c r="F1237" s="0" t="s">
-        <v>1843</v>
+        <v>1842</v>
       </c>
       <c r="G1237" s="0" t="n">
         <v>0</v>
@@ -52484,7 +52480,7 @@
         <v>1262</v>
       </c>
       <c r="B1238" s="0" t="s">
-        <v>1844</v>
+        <v>1843</v>
       </c>
       <c r="C1238" s="0" t="n">
         <v>3</v>
@@ -52519,7 +52515,7 @@
         <v>1263</v>
       </c>
       <c r="B1239" s="0" t="s">
-        <v>1845</v>
+        <v>1844</v>
       </c>
       <c r="C1239" s="0" t="n">
         <v>3</v>
@@ -52554,13 +52550,13 @@
         <v>1264</v>
       </c>
       <c r="B1240" s="0" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C1240" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1240" s="0" t="s">
         <v>1846</v>
-      </c>
-      <c r="C1240" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1240" s="0" t="s">
-        <v>1847</v>
       </c>
       <c r="F1240" s="0" t="s">
         <v>22</v>
@@ -52589,7 +52585,7 @@
         <v>1265</v>
       </c>
       <c r="B1241" s="0" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="C1241" s="0" t="n">
         <v>3</v>
@@ -52627,13 +52623,13 @@
         <v>1266</v>
       </c>
       <c r="B1242" s="0" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C1242" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1242" s="0" t="s">
         <v>1849</v>
-      </c>
-      <c r="C1242" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1242" s="0" t="s">
-        <v>1850</v>
       </c>
       <c r="F1242" s="0" t="s">
         <v>447</v>
@@ -52662,7 +52658,7 @@
         <v>1267</v>
       </c>
       <c r="B1243" s="0" t="s">
-        <v>1851</v>
+        <v>1850</v>
       </c>
       <c r="C1243" s="0" t="n">
         <v>3</v>
@@ -52697,7 +52693,7 @@
         <v>1268</v>
       </c>
       <c r="B1244" s="0" t="s">
-        <v>1852</v>
+        <v>1851</v>
       </c>
       <c r="C1244" s="0" t="n">
         <v>3</v>
@@ -52732,13 +52728,13 @@
         <v>1269</v>
       </c>
       <c r="B1245" s="0" t="s">
+        <v>1852</v>
+      </c>
+      <c r="C1245" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1245" s="0" t="s">
         <v>1853</v>
-      </c>
-      <c r="C1245" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1245" s="0" t="s">
-        <v>1854</v>
       </c>
       <c r="F1245" s="0" t="s">
         <v>22</v>
@@ -52767,7 +52763,7 @@
         <v>1270</v>
       </c>
       <c r="B1246" s="0" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
       <c r="C1246" s="0" t="n">
         <v>3</v>
@@ -52776,7 +52772,7 @@
         <v>856</v>
       </c>
       <c r="F1246" s="0" t="s">
-        <v>1856</v>
+        <v>1855</v>
       </c>
       <c r="G1246" s="0" t="n">
         <v>0</v>
@@ -52802,7 +52798,7 @@
         <v>1271</v>
       </c>
       <c r="B1247" s="0" t="s">
-        <v>1857</v>
+        <v>1856</v>
       </c>
       <c r="C1247" s="0" t="n">
         <v>3</v>
@@ -52840,7 +52836,7 @@
         <v>1272</v>
       </c>
       <c r="B1248" s="0" t="s">
-        <v>1858</v>
+        <v>1857</v>
       </c>
       <c r="C1248" s="0" t="n">
         <v>3</v>
@@ -52878,16 +52874,16 @@
         <v>1273</v>
       </c>
       <c r="B1249" s="0" t="s">
+        <v>1858</v>
+      </c>
+      <c r="C1249" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1249" s="0" t="s">
         <v>1859</v>
       </c>
-      <c r="C1249" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1249" s="0" t="s">
+      <c r="F1249" s="0" t="s">
         <v>1860</v>
-      </c>
-      <c r="F1249" s="0" t="s">
-        <v>1861</v>
       </c>
       <c r="G1249" s="0" t="n">
         <v>0</v>
@@ -52913,16 +52909,16 @@
         <v>1274</v>
       </c>
       <c r="B1250" s="0" t="s">
+        <v>1861</v>
+      </c>
+      <c r="C1250" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1250" s="0" t="s">
         <v>1862</v>
       </c>
-      <c r="C1250" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1250" s="0" t="s">
+      <c r="F1250" s="0" t="s">
         <v>1863</v>
-      </c>
-      <c r="F1250" s="0" t="s">
-        <v>1864</v>
       </c>
       <c r="G1250" s="0" t="n">
         <v>0</v>
@@ -52986,13 +52982,13 @@
         <v>1276</v>
       </c>
       <c r="B1252" s="0" t="s">
+        <v>1864</v>
+      </c>
+      <c r="C1252" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1252" s="0" t="s">
         <v>1865</v>
-      </c>
-      <c r="C1252" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1252" s="0" t="s">
-        <v>1866</v>
       </c>
       <c r="F1252" s="0" t="s">
         <v>447</v>
@@ -53021,7 +53017,7 @@
         <v>1277</v>
       </c>
       <c r="B1253" s="0" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
       <c r="C1253" s="0" t="n">
         <v>3</v>
@@ -53056,7 +53052,7 @@
         <v>1278</v>
       </c>
       <c r="B1254" s="0" t="s">
-        <v>1868</v>
+        <v>1867</v>
       </c>
       <c r="C1254" s="0" t="n">
         <v>3</v>
@@ -53091,13 +53087,13 @@
         <v>1279</v>
       </c>
       <c r="B1255" s="0" t="s">
+        <v>1868</v>
+      </c>
+      <c r="C1255" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1255" s="0" t="s">
         <v>1869</v>
-      </c>
-      <c r="C1255" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1255" s="0" t="s">
-        <v>1870</v>
       </c>
       <c r="F1255" s="0" t="s">
         <v>1437</v>
@@ -53161,7 +53157,7 @@
         <v>1281</v>
       </c>
       <c r="B1257" s="0" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
       <c r="C1257" s="0" t="n">
         <v>3</v>
@@ -53199,7 +53195,7 @@
         <v>1282</v>
       </c>
       <c r="B1258" s="0" t="s">
-        <v>1872</v>
+        <v>1871</v>
       </c>
       <c r="C1258" s="0" t="n">
         <v>3</v>
@@ -53234,7 +53230,7 @@
         <v>1283</v>
       </c>
       <c r="B1259" s="0" t="s">
-        <v>1873</v>
+        <v>1872</v>
       </c>
       <c r="C1259" s="0" t="n">
         <v>3</v>
@@ -53272,7 +53268,7 @@
         <v>1284</v>
       </c>
       <c r="B1260" s="0" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
       <c r="C1260" s="0" t="n">
         <v>3</v>
@@ -53310,7 +53306,7 @@
         <v>1285</v>
       </c>
       <c r="B1261" s="0" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
       <c r="C1261" s="0" t="n">
         <v>3</v>
@@ -53345,7 +53341,7 @@
         <v>1286</v>
       </c>
       <c r="B1262" s="0" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
       <c r="C1262" s="0" t="n">
         <v>3</v>
@@ -53380,7 +53376,7 @@
         <v>1287</v>
       </c>
       <c r="B1263" s="0" t="s">
-        <v>1877</v>
+        <v>1876</v>
       </c>
       <c r="C1263" s="0" t="n">
         <v>3</v>
@@ -53418,7 +53414,7 @@
         <v>1288</v>
       </c>
       <c r="B1264" s="0" t="s">
-        <v>1878</v>
+        <v>1877</v>
       </c>
       <c r="C1264" s="0" t="n">
         <v>3</v>
@@ -53456,7 +53452,7 @@
         <v>1289</v>
       </c>
       <c r="B1265" s="0" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
       <c r="C1265" s="0" t="n">
         <v>3</v>
@@ -53526,13 +53522,13 @@
         <v>1291</v>
       </c>
       <c r="B1267" s="0" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
       <c r="C1267" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E1267" s="0" t="s">
-        <v>1778</v>
+        <v>1777</v>
       </c>
       <c r="F1267" s="0" t="s">
         <v>22</v>
@@ -53564,13 +53560,13 @@
         <v>1292</v>
       </c>
       <c r="B1268" s="0" t="s">
+        <v>1880</v>
+      </c>
+      <c r="C1268" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1268" s="0" t="s">
         <v>1881</v>
-      </c>
-      <c r="C1268" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1268" s="0" t="s">
-        <v>1882</v>
       </c>
       <c r="F1268" s="0" t="s">
         <v>22</v>
@@ -53599,13 +53595,13 @@
         <v>1293</v>
       </c>
       <c r="B1269" s="0" t="s">
+        <v>1882</v>
+      </c>
+      <c r="C1269" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1269" s="0" t="s">
         <v>1883</v>
-      </c>
-      <c r="C1269" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1269" s="0" t="s">
-        <v>1884</v>
       </c>
       <c r="F1269" s="0" t="s">
         <v>1252</v>
@@ -53634,13 +53630,13 @@
         <v>1294</v>
       </c>
       <c r="B1270" s="0" t="s">
+        <v>1884</v>
+      </c>
+      <c r="C1270" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1270" s="0" t="s">
         <v>1885</v>
-      </c>
-      <c r="C1270" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1270" s="0" t="s">
-        <v>1886</v>
       </c>
       <c r="F1270" s="0" t="s">
         <v>866</v>
@@ -53669,13 +53665,13 @@
         <v>1295</v>
       </c>
       <c r="B1271" s="0" t="s">
+        <v>1886</v>
+      </c>
+      <c r="C1271" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1271" s="0" t="s">
         <v>1887</v>
-      </c>
-      <c r="C1271" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1271" s="0" t="s">
-        <v>1888</v>
       </c>
       <c r="F1271" s="0" t="s">
         <v>1305</v>
@@ -53704,7 +53700,7 @@
         <v>1296</v>
       </c>
       <c r="B1272" s="0" t="s">
-        <v>1889</v>
+        <v>1888</v>
       </c>
       <c r="C1272" s="0" t="n">
         <v>3</v>
@@ -53739,13 +53735,13 @@
         <v>1297</v>
       </c>
       <c r="B1273" s="0" t="s">
+        <v>1889</v>
+      </c>
+      <c r="C1273" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1273" s="0" t="s">
         <v>1890</v>
-      </c>
-      <c r="C1273" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1273" s="0" t="s">
-        <v>1891</v>
       </c>
       <c r="F1273" s="0" t="s">
         <v>22</v>
@@ -53777,7 +53773,7 @@
         <v>1298</v>
       </c>
       <c r="B1274" s="0" t="s">
-        <v>1892</v>
+        <v>1891</v>
       </c>
       <c r="C1274" s="0" t="n">
         <v>3</v>
@@ -53812,7 +53808,7 @@
         <v>1299</v>
       </c>
       <c r="B1275" s="0" t="s">
-        <v>1893</v>
+        <v>1892</v>
       </c>
       <c r="C1275" s="0" t="n">
         <v>3</v>
@@ -53847,13 +53843,13 @@
         <v>1300</v>
       </c>
       <c r="B1276" s="0" t="s">
+        <v>1893</v>
+      </c>
+      <c r="C1276" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1276" s="0" t="s">
         <v>1894</v>
-      </c>
-      <c r="C1276" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1276" s="0" t="s">
-        <v>1895</v>
       </c>
       <c r="F1276" s="0" t="s">
         <v>1599</v>
@@ -53882,16 +53878,16 @@
         <v>1301</v>
       </c>
       <c r="B1277" s="0" t="s">
+        <v>1895</v>
+      </c>
+      <c r="C1277" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1277" s="0" t="s">
         <v>1896</v>
       </c>
-      <c r="C1277" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1277" s="0" t="s">
+      <c r="F1277" s="0" t="s">
         <v>1897</v>
-      </c>
-      <c r="F1277" s="0" t="s">
-        <v>1898</v>
       </c>
       <c r="G1277" s="0" t="n">
         <v>0</v>
@@ -53917,13 +53913,13 @@
         <v>1302</v>
       </c>
       <c r="B1278" s="0" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="C1278" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E1278" s="0" t="s">
-        <v>1866</v>
+        <v>1865</v>
       </c>
       <c r="F1278" s="0" t="s">
         <v>22</v>
@@ -53952,7 +53948,7 @@
         <v>1303</v>
       </c>
       <c r="B1279" s="0" t="s">
-        <v>1900</v>
+        <v>1899</v>
       </c>
       <c r="C1279" s="0" t="n">
         <v>3</v>
@@ -53987,7 +53983,7 @@
         <v>1304</v>
       </c>
       <c r="B1280" s="0" t="s">
-        <v>1901</v>
+        <v>1900</v>
       </c>
       <c r="C1280" s="0" t="n">
         <v>3</v>
@@ -54025,13 +54021,13 @@
         <v>1305</v>
       </c>
       <c r="B1281" s="0" t="s">
+        <v>1901</v>
+      </c>
+      <c r="C1281" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1281" s="0" t="s">
         <v>1902</v>
-      </c>
-      <c r="C1281" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1281" s="0" t="s">
-        <v>1903</v>
       </c>
       <c r="F1281" s="0" t="s">
         <v>1093</v>
@@ -54060,13 +54056,13 @@
         <v>1306</v>
       </c>
       <c r="B1282" s="0" t="s">
+        <v>1903</v>
+      </c>
+      <c r="C1282" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1282" s="0" t="s">
         <v>1904</v>
-      </c>
-      <c r="C1282" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1282" s="0" t="s">
-        <v>1905</v>
       </c>
       <c r="F1282" s="0" t="s">
         <v>22</v>
@@ -54095,7 +54091,7 @@
         <v>1307</v>
       </c>
       <c r="B1283" s="0" t="s">
-        <v>1906</v>
+        <v>1905</v>
       </c>
       <c r="C1283" s="0" t="n">
         <v>3</v>
@@ -54133,7 +54129,7 @@
         <v>1308</v>
       </c>
       <c r="B1284" s="0" t="s">
-        <v>1907</v>
+        <v>1906</v>
       </c>
       <c r="C1284" s="0" t="n">
         <v>3</v>
@@ -54171,16 +54167,16 @@
         <v>1309</v>
       </c>
       <c r="B1285" s="0" t="s">
+        <v>1907</v>
+      </c>
+      <c r="C1285" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1285" s="0" t="s">
         <v>1908</v>
       </c>
-      <c r="C1285" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1285" s="0" t="s">
+      <c r="F1285" s="0" t="s">
         <v>1909</v>
-      </c>
-      <c r="F1285" s="0" t="s">
-        <v>1910</v>
       </c>
       <c r="G1285" s="0" t="n">
         <v>0</v>
@@ -54206,16 +54202,16 @@
         <v>1310</v>
       </c>
       <c r="B1286" s="0" t="s">
+        <v>1910</v>
+      </c>
+      <c r="C1286" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1286" s="0" t="s">
         <v>1911</v>
       </c>
-      <c r="C1286" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1286" s="0" t="s">
+      <c r="F1286" s="0" t="s">
         <v>1912</v>
-      </c>
-      <c r="F1286" s="0" t="s">
-        <v>1913</v>
       </c>
       <c r="G1286" s="0" t="n">
         <v>0</v>
@@ -54241,7 +54237,7 @@
         <v>1311</v>
       </c>
       <c r="B1287" s="0" t="s">
-        <v>1914</v>
+        <v>1913</v>
       </c>
       <c r="C1287" s="0" t="n">
         <v>3</v>
@@ -54250,7 +54246,7 @@
         <v>117</v>
       </c>
       <c r="F1287" s="0" t="s">
-        <v>1915</v>
+        <v>1914</v>
       </c>
       <c r="G1287" s="0" t="n">
         <v>0</v>
@@ -54276,7 +54272,7 @@
         <v>1312</v>
       </c>
       <c r="B1288" s="0" t="s">
-        <v>1916</v>
+        <v>1915</v>
       </c>
       <c r="C1288" s="0" t="n">
         <v>5</v>
@@ -54311,16 +54307,16 @@
         <v>1313</v>
       </c>
       <c r="B1289" s="0" t="s">
+        <v>1916</v>
+      </c>
+      <c r="C1289" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1289" s="0" t="s">
         <v>1917</v>
       </c>
-      <c r="C1289" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1289" s="0" t="s">
+      <c r="F1289" s="0" t="s">
         <v>1918</v>
-      </c>
-      <c r="F1289" s="0" t="s">
-        <v>1919</v>
       </c>
       <c r="G1289" s="0" t="n">
         <v>0</v>
@@ -54346,16 +54342,16 @@
         <v>1314</v>
       </c>
       <c r="B1290" s="0" t="s">
+        <v>1919</v>
+      </c>
+      <c r="C1290" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1290" s="0" t="s">
         <v>1920</v>
       </c>
-      <c r="C1290" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1290" s="0" t="s">
+      <c r="F1290" s="0" t="s">
         <v>1921</v>
-      </c>
-      <c r="F1290" s="0" t="s">
-        <v>1922</v>
       </c>
       <c r="G1290" s="0" t="n">
         <v>0</v>
@@ -54381,13 +54377,13 @@
         <v>1315</v>
       </c>
       <c r="B1291" s="0" t="s">
-        <v>1923</v>
+        <v>1922</v>
       </c>
       <c r="C1291" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E1291" s="0" t="s">
-        <v>1918</v>
+        <v>1917</v>
       </c>
       <c r="F1291" s="0" t="s">
         <v>1599</v>
@@ -54416,13 +54412,13 @@
         <v>1316</v>
       </c>
       <c r="B1292" s="0" t="s">
-        <v>1924</v>
+        <v>1923</v>
       </c>
       <c r="C1292" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E1292" s="0" t="s">
-        <v>1918</v>
+        <v>1917</v>
       </c>
       <c r="F1292" s="0" t="s">
         <v>1394</v>
@@ -54451,13 +54447,13 @@
         <v>1317</v>
       </c>
       <c r="B1293" s="0" t="s">
-        <v>1925</v>
+        <v>1924</v>
       </c>
       <c r="C1293" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E1293" s="0" t="s">
-        <v>1918</v>
+        <v>1917</v>
       </c>
       <c r="F1293" s="0" t="s">
         <v>1309</v>
@@ -54486,16 +54482,16 @@
         <v>1318</v>
       </c>
       <c r="B1294" s="0" t="s">
+        <v>1925</v>
+      </c>
+      <c r="C1294" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1294" s="0" t="s">
+        <v>1917</v>
+      </c>
+      <c r="F1294" s="0" t="s">
         <v>1926</v>
-      </c>
-      <c r="C1294" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1294" s="0" t="s">
-        <v>1918</v>
-      </c>
-      <c r="F1294" s="0" t="s">
-        <v>1927</v>
       </c>
       <c r="G1294" s="0" t="n">
         <v>0</v>
@@ -54521,7 +54517,7 @@
         <v>1319</v>
       </c>
       <c r="B1295" s="0" t="s">
-        <v>1928</v>
+        <v>1927</v>
       </c>
       <c r="C1295" s="0" t="n">
         <v>3</v>
@@ -54556,7 +54552,7 @@
         <v>1320</v>
       </c>
       <c r="B1296" s="0" t="s">
-        <v>1929</v>
+        <v>1928</v>
       </c>
       <c r="C1296" s="0" t="n">
         <v>3</v>
@@ -54565,7 +54561,7 @@
         <v>1578</v>
       </c>
       <c r="F1296" s="0" t="s">
-        <v>1930</v>
+        <v>1929</v>
       </c>
       <c r="G1296" s="0" t="n">
         <v>0</v>
@@ -54591,13 +54587,13 @@
         <v>1321</v>
       </c>
       <c r="B1297" s="0" t="s">
+        <v>1930</v>
+      </c>
+      <c r="C1297" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1297" s="0" t="s">
         <v>1931</v>
-      </c>
-      <c r="C1297" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1297" s="0" t="s">
-        <v>1932</v>
       </c>
       <c r="F1297" s="0" t="s">
         <v>1235</v>
@@ -54626,7 +54622,7 @@
         <v>1322</v>
       </c>
       <c r="B1298" s="0" t="s">
-        <v>1933</v>
+        <v>1932</v>
       </c>
       <c r="C1298" s="0" t="n">
         <v>3</v>
@@ -54661,7 +54657,7 @@
         <v>1323</v>
       </c>
       <c r="B1299" s="0" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
       <c r="C1299" s="0" t="n">
         <v>3</v>
@@ -54696,7 +54692,7 @@
         <v>1324</v>
       </c>
       <c r="B1300" s="0" t="s">
-        <v>1935</v>
+        <v>1934</v>
       </c>
       <c r="C1300" s="0" t="n">
         <v>3</v>
@@ -54769,7 +54765,7 @@
         <v>1326</v>
       </c>
       <c r="B1302" s="0" t="s">
-        <v>1936</v>
+        <v>1935</v>
       </c>
       <c r="C1302" s="0" t="n">
         <v>3</v>
@@ -54804,7 +54800,7 @@
         <v>1327</v>
       </c>
       <c r="B1303" s="0" t="s">
-        <v>1937</v>
+        <v>1936</v>
       </c>
       <c r="C1303" s="0" t="n">
         <v>3</v>
@@ -54839,13 +54835,13 @@
         <v>1328</v>
       </c>
       <c r="B1304" s="0" t="s">
+        <v>1937</v>
+      </c>
+      <c r="C1304" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1304" s="0" t="s">
         <v>1938</v>
-      </c>
-      <c r="C1304" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1304" s="0" t="s">
-        <v>1939</v>
       </c>
       <c r="F1304" s="0" t="s">
         <v>22</v>
@@ -54874,7 +54870,7 @@
         <v>1329</v>
       </c>
       <c r="B1305" s="0" t="s">
-        <v>1940</v>
+        <v>1939</v>
       </c>
       <c r="C1305" s="0" t="n">
         <v>3</v>
@@ -54909,13 +54905,13 @@
         <v>1330</v>
       </c>
       <c r="B1306" s="0" t="s">
+        <v>1940</v>
+      </c>
+      <c r="C1306" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1306" s="0" t="s">
         <v>1941</v>
-      </c>
-      <c r="C1306" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1306" s="0" t="s">
-        <v>1942</v>
       </c>
       <c r="F1306" s="0" t="s">
         <v>22</v>
@@ -54944,7 +54940,7 @@
         <v>1331</v>
       </c>
       <c r="B1307" s="0" t="s">
-        <v>1943</v>
+        <v>1942</v>
       </c>
       <c r="C1307" s="0" t="n">
         <v>3</v>
@@ -54979,13 +54975,13 @@
         <v>1332</v>
       </c>
       <c r="B1308" s="0" t="s">
+        <v>1943</v>
+      </c>
+      <c r="C1308" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1308" s="0" t="s">
         <v>1944</v>
-      </c>
-      <c r="C1308" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1308" s="0" t="s">
-        <v>1945</v>
       </c>
       <c r="F1308" s="0" t="s">
         <v>22</v>
@@ -55014,7 +55010,7 @@
         <v>1333</v>
       </c>
       <c r="B1309" s="0" t="s">
-        <v>1946</v>
+        <v>1945</v>
       </c>
       <c r="C1309" s="0" t="n">
         <v>3</v>
@@ -55049,13 +55045,13 @@
         <v>1334</v>
       </c>
       <c r="B1310" s="0" t="s">
+        <v>1946</v>
+      </c>
+      <c r="C1310" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1310" s="0" t="s">
         <v>1947</v>
-      </c>
-      <c r="C1310" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1310" s="0" t="s">
-        <v>1948</v>
       </c>
       <c r="F1310" s="0" t="s">
         <v>22</v>
@@ -55093,10 +55089,10 @@
         <v>3</v>
       </c>
       <c r="E1311" s="0" t="s">
+        <v>1948</v>
+      </c>
+      <c r="F1311" s="0" t="s">
         <v>1949</v>
-      </c>
-      <c r="F1311" s="0" t="s">
-        <v>1950</v>
       </c>
       <c r="G1311" s="0" t="n">
         <v>0</v>
@@ -55128,7 +55124,7 @@
         <v>3</v>
       </c>
       <c r="E1312" s="0" t="s">
-        <v>1951</v>
+        <v>1950</v>
       </c>
       <c r="F1312" s="0" t="s">
         <v>22</v>
@@ -55227,7 +55223,7 @@
         <v>1339</v>
       </c>
       <c r="B1315" s="0" t="s">
-        <v>1952</v>
+        <v>1951</v>
       </c>
       <c r="C1315" s="0" t="n">
         <v>3</v>
@@ -55262,13 +55258,13 @@
         <v>1340</v>
       </c>
       <c r="B1316" s="0" t="s">
+        <v>1952</v>
+      </c>
+      <c r="C1316" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1316" s="0" t="s">
         <v>1953</v>
-      </c>
-      <c r="C1316" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1316" s="0" t="s">
-        <v>1954</v>
       </c>
       <c r="F1316" s="0" t="s">
         <v>88</v>
@@ -55300,7 +55296,7 @@
         <v>1341</v>
       </c>
       <c r="B1317" s="0" t="s">
-        <v>1955</v>
+        <v>1954</v>
       </c>
       <c r="C1317" s="0" t="n">
         <v>3</v>
@@ -55309,7 +55305,7 @@
         <v>1125</v>
       </c>
       <c r="F1317" s="0" t="s">
-        <v>1898</v>
+        <v>1897</v>
       </c>
       <c r="G1317" s="0" t="n">
         <v>0</v>
@@ -55335,13 +55331,13 @@
         <v>1342</v>
       </c>
       <c r="B1318" s="0" t="s">
+        <v>1955</v>
+      </c>
+      <c r="C1318" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1318" s="0" t="s">
         <v>1956</v>
-      </c>
-      <c r="C1318" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1318" s="0" t="s">
-        <v>1957</v>
       </c>
       <c r="F1318" s="0" t="s">
         <v>22</v>
@@ -55370,13 +55366,13 @@
         <v>1343</v>
       </c>
       <c r="B1319" s="0" t="s">
+        <v>1957</v>
+      </c>
+      <c r="C1319" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1319" s="0" t="s">
         <v>1958</v>
-      </c>
-      <c r="C1319" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1319" s="0" t="s">
-        <v>1959</v>
       </c>
       <c r="F1319" s="0" t="s">
         <v>22</v>
@@ -55405,13 +55401,13 @@
         <v>1344</v>
       </c>
       <c r="B1320" s="0" t="s">
+        <v>1959</v>
+      </c>
+      <c r="C1320" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1320" s="0" t="s">
         <v>1960</v>
-      </c>
-      <c r="C1320" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1320" s="0" t="s">
-        <v>1961</v>
       </c>
       <c r="F1320" s="0" t="s">
         <v>22</v>
@@ -55449,7 +55445,7 @@
         <v>1277</v>
       </c>
       <c r="F1321" s="0" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="G1321" s="0" t="n">
         <v>0</v>
@@ -55475,7 +55471,7 @@
         <v>1346</v>
       </c>
       <c r="B1322" s="0" t="s">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="C1322" s="0" t="n">
         <v>3</v>
@@ -55510,13 +55506,13 @@
         <v>1347</v>
       </c>
       <c r="B1323" s="0" t="s">
+        <v>1952</v>
+      </c>
+      <c r="C1323" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1323" s="0" t="s">
         <v>1953</v>
-      </c>
-      <c r="C1323" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1323" s="0" t="s">
-        <v>1954</v>
       </c>
       <c r="F1323" s="0" t="s">
         <v>88</v>
@@ -55545,7 +55541,7 @@
         <v>1348</v>
       </c>
       <c r="B1324" s="0" t="s">
-        <v>1964</v>
+        <v>1963</v>
       </c>
       <c r="C1324" s="0" t="n">
         <v>3</v>
@@ -55580,7 +55576,7 @@
         <v>1349</v>
       </c>
       <c r="B1325" s="0" t="s">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="C1325" s="0" t="n">
         <v>3</v>
@@ -55615,7 +55611,7 @@
         <v>1350</v>
       </c>
       <c r="B1326" s="0" t="s">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="C1326" s="0" t="n">
         <v>3</v>
@@ -55650,16 +55646,16 @@
         <v>1351</v>
       </c>
       <c r="B1327" s="0" t="s">
+        <v>1966</v>
+      </c>
+      <c r="C1327" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1327" s="0" t="s">
         <v>1967</v>
       </c>
-      <c r="C1327" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1327" s="0" t="s">
-        <v>1968</v>
-      </c>
       <c r="F1327" s="0" t="s">
-        <v>1839</v>
+        <v>1838</v>
       </c>
       <c r="G1327" s="0" t="n">
         <v>0</v>
@@ -55685,13 +55681,13 @@
         <v>1352</v>
       </c>
       <c r="B1328" s="0" t="s">
+        <v>1968</v>
+      </c>
+      <c r="C1328" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1328" s="0" t="s">
         <v>1969</v>
-      </c>
-      <c r="C1328" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1328" s="0" t="s">
-        <v>1970</v>
       </c>
       <c r="F1328" s="0" t="s">
         <v>122</v>
@@ -55720,13 +55716,13 @@
         <v>1353</v>
       </c>
       <c r="B1329" s="0" t="s">
+        <v>1970</v>
+      </c>
+      <c r="C1329" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1329" s="0" t="s">
         <v>1971</v>
-      </c>
-      <c r="C1329" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1329" s="0" t="s">
-        <v>1972</v>
       </c>
       <c r="F1329" s="0" t="s">
         <v>122</v>
@@ -55755,13 +55751,13 @@
         <v>1354</v>
       </c>
       <c r="B1330" s="0" t="s">
+        <v>1972</v>
+      </c>
+      <c r="C1330" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1330" s="0" t="s">
         <v>1973</v>
-      </c>
-      <c r="C1330" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1330" s="0" t="s">
-        <v>1974</v>
       </c>
       <c r="F1330" s="0" t="s">
         <v>122</v>
@@ -55790,7 +55786,7 @@
         <v>1355</v>
       </c>
       <c r="B1331" s="0" t="s">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="C1331" s="0" t="n">
         <v>3</v>
@@ -55825,7 +55821,7 @@
         <v>1356</v>
       </c>
       <c r="B1332" s="0" t="s">
-        <v>1976</v>
+        <v>1975</v>
       </c>
       <c r="C1332" s="0" t="n">
         <v>3</v>
@@ -55860,7 +55856,7 @@
         <v>1357</v>
       </c>
       <c r="B1333" s="0" t="s">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="C1333" s="0" t="n">
         <v>3</v>
@@ -55895,7 +55891,7 @@
         <v>1358</v>
       </c>
       <c r="B1334" s="0" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="C1334" s="0" t="n">
         <v>3</v>
@@ -55904,7 +55900,7 @@
         <v>427</v>
       </c>
       <c r="F1334" s="0" t="s">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="G1334" s="0" t="n">
         <v>0</v>
@@ -55930,16 +55926,16 @@
         <v>1359</v>
       </c>
       <c r="B1335" s="0" t="s">
+        <v>1979</v>
+      </c>
+      <c r="C1335" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1335" s="0" t="s">
+        <v>1865</v>
+      </c>
+      <c r="F1335" s="0" t="s">
         <v>1980</v>
-      </c>
-      <c r="C1335" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1335" s="0" t="s">
-        <v>1866</v>
-      </c>
-      <c r="F1335" s="0" t="s">
-        <v>1981</v>
       </c>
       <c r="G1335" s="0" t="n">
         <v>0</v>
@@ -55965,13 +55961,13 @@
         <v>1360</v>
       </c>
       <c r="B1336" s="0" t="s">
+        <v>1981</v>
+      </c>
+      <c r="C1336" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1336" s="0" t="s">
         <v>1982</v>
-      </c>
-      <c r="C1336" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1336" s="0" t="s">
-        <v>1983</v>
       </c>
       <c r="F1336" s="0" t="s">
         <v>22</v>
@@ -56003,13 +55999,13 @@
         <v>1361</v>
       </c>
       <c r="B1337" s="0" t="s">
+        <v>1983</v>
+      </c>
+      <c r="C1337" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1337" s="0" t="s">
         <v>1984</v>
-      </c>
-      <c r="C1337" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1337" s="0" t="s">
-        <v>1985</v>
       </c>
       <c r="F1337" s="0" t="s">
         <v>22</v>
@@ -56038,16 +56034,16 @@
         <v>1362</v>
       </c>
       <c r="B1338" s="0" t="s">
+        <v>1985</v>
+      </c>
+      <c r="C1338" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1338" s="0" t="s">
+        <v>1809</v>
+      </c>
+      <c r="F1338" s="0" t="s">
         <v>1986</v>
-      </c>
-      <c r="C1338" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1338" s="0" t="s">
-        <v>1810</v>
-      </c>
-      <c r="F1338" s="0" t="s">
-        <v>1987</v>
       </c>
       <c r="G1338" s="0" t="n">
         <v>0</v>
@@ -56073,7 +56069,7 @@
         <v>1363</v>
       </c>
       <c r="B1339" s="0" t="s">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="C1339" s="0" t="n">
         <v>3</v>
@@ -56108,13 +56104,13 @@
         <v>1364</v>
       </c>
       <c r="B1340" s="0" t="s">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="C1340" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E1340" s="0" t="s">
-        <v>1778</v>
+        <v>1777</v>
       </c>
       <c r="F1340" s="0" t="s">
         <v>22</v>
@@ -56146,7 +56142,7 @@
         <v>1365</v>
       </c>
       <c r="B1341" s="0" t="s">
-        <v>1990</v>
+        <v>1989</v>
       </c>
       <c r="C1341" s="0" t="n">
         <v>3</v>
@@ -56181,7 +56177,7 @@
         <v>1366</v>
       </c>
       <c r="B1342" s="0" t="s">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="C1342" s="0" t="n">
         <v>3</v>
@@ -56190,7 +56186,7 @@
         <v>1723</v>
       </c>
       <c r="F1342" s="0" t="s">
-        <v>1992</v>
+        <v>1991</v>
       </c>
       <c r="G1342" s="0" t="n">
         <v>0</v>
@@ -56216,13 +56212,13 @@
         <v>1367</v>
       </c>
       <c r="B1343" s="0" t="s">
-        <v>1953</v>
+        <v>1952</v>
       </c>
       <c r="C1343" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E1343" s="0" t="s">
-        <v>1993</v>
+        <v>1992</v>
       </c>
       <c r="F1343" s="0" t="s">
         <v>88</v>
@@ -56254,13 +56250,13 @@
         <v>1368</v>
       </c>
       <c r="B1344" s="0" t="s">
-        <v>1994</v>
+        <v>1993</v>
       </c>
       <c r="C1344" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E1344" s="0" t="s">
-        <v>1921</v>
+        <v>1920</v>
       </c>
       <c r="F1344" s="0" t="s">
         <v>1705</v>
@@ -56289,7 +56285,7 @@
         <v>1369</v>
       </c>
       <c r="B1345" s="0" t="s">
-        <v>1995</v>
+        <v>1994</v>
       </c>
       <c r="C1345" s="0" t="n">
         <v>3</v>
@@ -56298,7 +56294,7 @@
         <v>810</v>
       </c>
       <c r="F1345" s="0" t="s">
-        <v>1996</v>
+        <v>1995</v>
       </c>
       <c r="G1345" s="0" t="n">
         <v>0</v>
@@ -56324,13 +56320,13 @@
         <v>1370</v>
       </c>
       <c r="B1346" s="0" t="s">
+        <v>1996</v>
+      </c>
+      <c r="C1346" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1346" s="0" t="s">
         <v>1997</v>
-      </c>
-      <c r="C1346" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1346" s="0" t="s">
-        <v>1998</v>
       </c>
       <c r="F1346" s="0" t="s">
         <v>22</v>
@@ -56359,13 +56355,13 @@
         <v>1371</v>
       </c>
       <c r="B1347" s="0" t="s">
+        <v>1998</v>
+      </c>
+      <c r="C1347" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1347" s="0" t="s">
         <v>1999</v>
-      </c>
-      <c r="C1347" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1347" s="0" t="s">
-        <v>2000</v>
       </c>
       <c r="F1347" s="0" t="s">
         <v>662</v>
@@ -56394,13 +56390,13 @@
         <v>1372</v>
       </c>
       <c r="B1348" s="0" t="s">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="C1348" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E1348" s="0" t="s">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="F1348" s="0" t="s">
         <v>22</v>
@@ -56429,13 +56425,13 @@
         <v>1373</v>
       </c>
       <c r="B1349" s="0" t="s">
+        <v>2001</v>
+      </c>
+      <c r="C1349" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1349" s="0" t="s">
         <v>2002</v>
-      </c>
-      <c r="C1349" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1349" s="0" t="s">
-        <v>2003</v>
       </c>
       <c r="F1349" s="0" t="s">
         <v>22</v>
@@ -56467,7 +56463,7 @@
         <v>1374</v>
       </c>
       <c r="B1350" s="0" t="s">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="C1350" s="0" t="n">
         <v>3</v>
@@ -56505,13 +56501,13 @@
         <v>1375</v>
       </c>
       <c r="B1351" s="0" t="s">
+        <v>2004</v>
+      </c>
+      <c r="C1351" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1351" s="0" t="s">
         <v>2005</v>
-      </c>
-      <c r="C1351" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1351" s="0" t="s">
-        <v>2006</v>
       </c>
       <c r="F1351" s="0" t="s">
         <v>22</v>
@@ -56543,7 +56539,7 @@
         <v>1376</v>
       </c>
       <c r="B1352" s="0" t="s">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="C1352" s="0" t="n">
         <v>3</v>
@@ -56578,7 +56574,7 @@
         <v>1377</v>
       </c>
       <c r="B1353" s="0" t="s">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="C1353" s="0" t="n">
         <v>3</v>
@@ -56613,13 +56609,13 @@
         <v>1378</v>
       </c>
       <c r="B1354" s="0" t="s">
+        <v>2008</v>
+      </c>
+      <c r="C1354" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1354" s="0" t="s">
         <v>2009</v>
-      </c>
-      <c r="C1354" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1354" s="0" t="s">
-        <v>2010</v>
       </c>
       <c r="F1354" s="0" t="s">
         <v>22</v>
@@ -56648,13 +56644,13 @@
         <v>1379</v>
       </c>
       <c r="B1355" s="0" t="s">
+        <v>2010</v>
+      </c>
+      <c r="C1355" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1355" s="0" t="s">
         <v>2011</v>
-      </c>
-      <c r="C1355" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1355" s="0" t="s">
-        <v>2012</v>
       </c>
       <c r="F1355" s="0" t="s">
         <v>22</v>
@@ -56686,7 +56682,7 @@
         <v>1380</v>
       </c>
       <c r="B1356" s="0" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="C1356" s="0" t="n">
         <v>3</v>
@@ -56721,7 +56717,7 @@
         <v>1381</v>
       </c>
       <c r="B1357" s="0" t="s">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="C1357" s="0" t="n">
         <v>3</v>
@@ -56759,13 +56755,13 @@
         <v>1382</v>
       </c>
       <c r="B1358" s="0" t="s">
+        <v>2014</v>
+      </c>
+      <c r="C1358" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1358" s="0" t="s">
         <v>2015</v>
-      </c>
-      <c r="C1358" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1358" s="0" t="s">
-        <v>2016</v>
       </c>
       <c r="F1358" s="0" t="s">
         <v>22</v>
@@ -56794,13 +56790,13 @@
         <v>1383</v>
       </c>
       <c r="B1359" s="0" t="s">
+        <v>2016</v>
+      </c>
+      <c r="C1359" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1359" s="0" t="s">
         <v>2017</v>
-      </c>
-      <c r="C1359" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1359" s="0" t="s">
-        <v>2018</v>
       </c>
       <c r="F1359" s="0" t="s">
         <v>22</v>
@@ -56829,13 +56825,13 @@
         <v>1384</v>
       </c>
       <c r="B1360" s="0" t="s">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="C1360" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E1360" s="0" t="s">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="F1360" s="0" t="s">
         <v>22</v>
@@ -56864,13 +56860,13 @@
         <v>1385</v>
       </c>
       <c r="B1361" s="0" t="s">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C1361" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E1361" s="0" t="s">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="F1361" s="0" t="s">
         <v>22</v>
@@ -56899,7 +56895,7 @@
         <v>1386</v>
       </c>
       <c r="B1362" s="0" t="s">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C1362" s="0" t="n">
         <v>3</v>
@@ -56937,13 +56933,13 @@
         <v>1387</v>
       </c>
       <c r="B1363" s="0" t="s">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C1363" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E1363" s="0" t="s">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="F1363" s="0" t="s">
         <v>22</v>
@@ -56972,16 +56968,16 @@
         <v>1388</v>
       </c>
       <c r="B1364" s="0" t="s">
+        <v>2022</v>
+      </c>
+      <c r="C1364" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1364" s="0" t="s">
+        <v>2017</v>
+      </c>
+      <c r="F1364" s="0" t="s">
         <v>2023</v>
-      </c>
-      <c r="C1364" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1364" s="0" t="s">
-        <v>2018</v>
-      </c>
-      <c r="F1364" s="0" t="s">
-        <v>2024</v>
       </c>
       <c r="G1364" s="0" t="n">
         <v>0</v>
@@ -57042,13 +57038,13 @@
         <v>1390</v>
       </c>
       <c r="B1366" s="0" t="s">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C1366" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E1366" s="0" t="s">
-        <v>1766</v>
+        <v>1765</v>
       </c>
       <c r="F1366" s="0" t="s">
         <v>88</v>
@@ -57077,13 +57073,13 @@
         <v>1391</v>
       </c>
       <c r="B1367" s="0" t="s">
+        <v>2025</v>
+      </c>
+      <c r="C1367" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1367" s="0" t="s">
         <v>2026</v>
-      </c>
-      <c r="C1367" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1367" s="0" t="s">
-        <v>2027</v>
       </c>
       <c r="F1367" s="0" t="s">
         <v>22</v>
@@ -57112,7 +57108,7 @@
         <v>1392</v>
       </c>
       <c r="B1368" s="0" t="s">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="C1368" s="0" t="n">
         <v>3</v>
@@ -57150,7 +57146,7 @@
         <v>1393</v>
       </c>
       <c r="B1369" s="0" t="s">
-        <v>2029</v>
+        <v>2028</v>
       </c>
       <c r="C1369" s="0" t="n">
         <v>3</v>
@@ -57185,7 +57181,7 @@
         <v>1394</v>
       </c>
       <c r="B1370" s="0" t="s">
-        <v>2030</v>
+        <v>2029</v>
       </c>
       <c r="C1370" s="0" t="n">
         <v>3</v>
@@ -57220,7 +57216,7 @@
         <v>1395</v>
       </c>
       <c r="B1371" s="0" t="s">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="C1371" s="0" t="n">
         <v>3</v>
@@ -57229,7 +57225,7 @@
         <v>1578</v>
       </c>
       <c r="F1371" s="0" t="s">
-        <v>2032</v>
+        <v>2031</v>
       </c>
       <c r="G1371" s="0" t="n">
         <v>0</v>
@@ -57255,13 +57251,13 @@
         <v>1396</v>
       </c>
       <c r="B1372" s="0" t="s">
+        <v>2032</v>
+      </c>
+      <c r="C1372" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1372" s="0" t="s">
         <v>2033</v>
-      </c>
-      <c r="C1372" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1372" s="0" t="s">
-        <v>2034</v>
       </c>
       <c r="F1372" s="0" t="s">
         <v>1238</v>
@@ -57290,7 +57286,7 @@
         <v>1397</v>
       </c>
       <c r="B1373" s="0" t="s">
-        <v>2035</v>
+        <v>2034</v>
       </c>
       <c r="C1373" s="0" t="n">
         <v>3</v>
@@ -57325,13 +57321,13 @@
         <v>1398</v>
       </c>
       <c r="B1374" s="0" t="s">
+        <v>2035</v>
+      </c>
+      <c r="C1374" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1374" s="0" t="s">
         <v>2036</v>
-      </c>
-      <c r="C1374" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1374" s="0" t="s">
-        <v>2037</v>
       </c>
       <c r="F1374" s="0" t="s">
         <v>22</v>
@@ -57360,13 +57356,13 @@
         <v>1399</v>
       </c>
       <c r="B1375" s="0" t="s">
+        <v>2037</v>
+      </c>
+      <c r="C1375" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1375" s="0" t="s">
         <v>2038</v>
-      </c>
-      <c r="C1375" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1375" s="0" t="s">
-        <v>2039</v>
       </c>
       <c r="F1375" s="0" t="s">
         <v>22</v>
@@ -57395,7 +57391,7 @@
         <v>1400</v>
       </c>
       <c r="B1376" s="0" t="s">
-        <v>2040</v>
+        <v>2039</v>
       </c>
       <c r="C1376" s="0" t="n">
         <v>3</v>
@@ -57430,7 +57426,7 @@
         <v>1401</v>
       </c>
       <c r="B1377" s="0" t="s">
-        <v>2041</v>
+        <v>2040</v>
       </c>
       <c r="C1377" s="0" t="n">
         <v>3</v>
@@ -57465,7 +57461,7 @@
         <v>1402</v>
       </c>
       <c r="B1378" s="0" t="s">
-        <v>2042</v>
+        <v>2041</v>
       </c>
       <c r="C1378" s="0" t="n">
         <v>3</v>
@@ -57474,7 +57470,7 @@
         <v>391</v>
       </c>
       <c r="F1378" s="0" t="s">
-        <v>2043</v>
+        <v>2042</v>
       </c>
       <c r="G1378" s="0" t="n">
         <v>0</v>
@@ -57500,13 +57496,13 @@
         <v>1403</v>
       </c>
       <c r="B1379" s="0" t="s">
+        <v>2043</v>
+      </c>
+      <c r="C1379" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1379" s="0" t="s">
         <v>2044</v>
-      </c>
-      <c r="C1379" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1379" s="0" t="s">
-        <v>2045</v>
       </c>
       <c r="F1379" s="0" t="s">
         <v>259</v>
@@ -57535,16 +57531,16 @@
         <v>1404</v>
       </c>
       <c r="B1380" s="0" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1380" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1380" s="0" t="s">
         <v>2046</v>
       </c>
-      <c r="C1380" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1380" s="0" t="s">
-        <v>2047</v>
-      </c>
       <c r="F1380" s="0" t="s">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="G1380" s="0" t="n">
         <v>0</v>
@@ -57570,7 +57566,7 @@
         <v>1405</v>
       </c>
       <c r="B1381" s="0" t="s">
-        <v>2048</v>
+        <v>2047</v>
       </c>
       <c r="C1381" s="0" t="n">
         <v>3</v>
@@ -57605,13 +57601,13 @@
         <v>1406</v>
       </c>
       <c r="B1382" s="0" t="s">
-        <v>1953</v>
+        <v>1952</v>
       </c>
       <c r="C1382" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E1382" s="0" t="s">
-        <v>2049</v>
+        <v>2048</v>
       </c>
       <c r="F1382" s="0" t="s">
         <v>88</v>
@@ -57640,7 +57636,7 @@
         <v>1407</v>
       </c>
       <c r="B1383" s="0" t="s">
-        <v>2050</v>
+        <v>2049</v>
       </c>
       <c r="C1383" s="0" t="n">
         <v>3</v>
@@ -57675,7 +57671,7 @@
         <v>1408</v>
       </c>
       <c r="B1384" s="0" t="s">
-        <v>2051</v>
+        <v>2050</v>
       </c>
       <c r="C1384" s="0" t="n">
         <v>3</v>
@@ -57684,7 +57680,7 @@
         <v>51</v>
       </c>
       <c r="F1384" s="0" t="s">
-        <v>2052</v>
+        <v>2051</v>
       </c>
       <c r="G1384" s="0" t="n">
         <v>0</v>
@@ -57710,16 +57706,16 @@
         <v>1409</v>
       </c>
       <c r="B1385" s="0" t="s">
+        <v>2052</v>
+      </c>
+      <c r="C1385" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1385" s="0" t="s">
         <v>2053</v>
       </c>
-      <c r="C1385" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1385" s="0" t="s">
+      <c r="F1385" s="0" t="s">
         <v>2054</v>
-      </c>
-      <c r="F1385" s="0" t="s">
-        <v>2055</v>
       </c>
       <c r="G1385" s="0" t="n">
         <v>0</v>
@@ -57745,7 +57741,7 @@
         <v>1410</v>
       </c>
       <c r="B1386" s="0" t="s">
-        <v>2056</v>
+        <v>2055</v>
       </c>
       <c r="C1386" s="0" t="n">
         <v>3</v>
@@ -57856,7 +57852,7 @@
         <v>3</v>
       </c>
       <c r="E1389" s="0" t="s">
-        <v>1948</v>
+        <v>1947</v>
       </c>
       <c r="F1389" s="0" t="s">
         <v>22</v>
@@ -57885,7 +57881,7 @@
         <v>1414</v>
       </c>
       <c r="B1390" s="0" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="C1390" s="0" t="n">
         <v>3</v>
@@ -57923,13 +57919,13 @@
         <v>1415</v>
       </c>
       <c r="B1391" s="0" t="s">
+        <v>2057</v>
+      </c>
+      <c r="C1391" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1391" s="0" t="s">
         <v>2058</v>
-      </c>
-      <c r="C1391" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1391" s="0" t="s">
-        <v>2059</v>
       </c>
       <c r="F1391" s="0" t="s">
         <v>22</v>
@@ -57958,13 +57954,13 @@
         <v>1416</v>
       </c>
       <c r="B1392" s="0" t="s">
+        <v>2059</v>
+      </c>
+      <c r="C1392" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1392" s="0" t="s">
         <v>2060</v>
-      </c>
-      <c r="C1392" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1392" s="0" t="s">
-        <v>2061</v>
       </c>
       <c r="F1392" s="0" t="s">
         <v>1387</v>
@@ -57993,13 +57989,13 @@
         <v>1417</v>
       </c>
       <c r="B1393" s="0" t="s">
-        <v>2062</v>
+        <v>2061</v>
       </c>
       <c r="C1393" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E1393" s="0" t="s">
-        <v>2061</v>
+        <v>2060</v>
       </c>
       <c r="F1393" s="0" t="s">
         <v>916</v>
@@ -58028,16 +58024,16 @@
         <v>1418</v>
       </c>
       <c r="B1394" s="0" t="s">
+        <v>2062</v>
+      </c>
+      <c r="C1394" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1394" s="0" t="s">
+        <v>2060</v>
+      </c>
+      <c r="F1394" s="0" t="s">
         <v>2063</v>
-      </c>
-      <c r="C1394" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1394" s="0" t="s">
-        <v>2061</v>
-      </c>
-      <c r="F1394" s="0" t="s">
-        <v>2064</v>
       </c>
       <c r="G1394" s="0" t="n">
         <v>0</v>
@@ -58063,13 +58059,13 @@
         <v>1419</v>
       </c>
       <c r="B1395" s="0" t="s">
-        <v>2065</v>
+        <v>2064</v>
       </c>
       <c r="C1395" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E1395" s="0" t="s">
-        <v>1948</v>
+        <v>1947</v>
       </c>
       <c r="F1395" s="0" t="s">
         <v>22</v>
@@ -58098,13 +58094,13 @@
         <v>1420</v>
       </c>
       <c r="B1396" s="0" t="s">
-        <v>2066</v>
+        <v>2065</v>
       </c>
       <c r="C1396" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E1396" s="0" t="s">
-        <v>1948</v>
+        <v>1947</v>
       </c>
       <c r="F1396" s="0" t="s">
         <v>528</v>
@@ -58133,13 +58129,13 @@
         <v>1421</v>
       </c>
       <c r="B1397" s="0" t="s">
-        <v>2067</v>
+        <v>2066</v>
       </c>
       <c r="C1397" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E1397" s="0" t="s">
-        <v>1948</v>
+        <v>1947</v>
       </c>
       <c r="F1397" s="0" t="s">
         <v>22</v>
@@ -58168,7 +58164,7 @@
         <v>1422</v>
       </c>
       <c r="B1398" s="0" t="s">
-        <v>2068</v>
+        <v>2067</v>
       </c>
       <c r="C1398" s="0" t="n">
         <v>3</v>
@@ -58203,7 +58199,7 @@
         <v>1423</v>
       </c>
       <c r="B1399" s="0" t="s">
-        <v>2069</v>
+        <v>2068</v>
       </c>
       <c r="C1399" s="0" t="n">
         <v>3</v>
@@ -58241,7 +58237,7 @@
         <v>1424</v>
       </c>
       <c r="B1400" s="0" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="C1400" s="0" t="n">
         <v>3</v>
@@ -58276,7 +58272,7 @@
         <v>1425</v>
       </c>
       <c r="B1401" s="0" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="C1401" s="0" t="n">
         <v>3</v>
@@ -58311,7 +58307,7 @@
         <v>1426</v>
       </c>
       <c r="B1402" s="0" t="s">
-        <v>2072</v>
+        <v>2071</v>
       </c>
       <c r="C1402" s="0" t="n">
         <v>3</v>
@@ -58320,7 +58316,7 @@
         <v>177</v>
       </c>
       <c r="F1402" s="0" t="s">
-        <v>1927</v>
+        <v>1926</v>
       </c>
       <c r="G1402" s="0" t="n">
         <v>0</v>
@@ -58346,7 +58342,7 @@
         <v>1427</v>
       </c>
       <c r="B1403" s="0" t="s">
-        <v>2073</v>
+        <v>2072</v>
       </c>
       <c r="C1403" s="0" t="n">
         <v>3</v>
@@ -58381,7 +58377,7 @@
         <v>1428</v>
       </c>
       <c r="B1404" s="0" t="s">
-        <v>2074</v>
+        <v>2073</v>
       </c>
       <c r="C1404" s="0" t="n">
         <v>3</v>
@@ -58390,7 +58386,7 @@
         <v>645</v>
       </c>
       <c r="F1404" s="0" t="s">
-        <v>1772</v>
+        <v>1771</v>
       </c>
       <c r="G1404" s="0" t="n">
         <v>0</v>
@@ -58416,13 +58412,13 @@
         <v>1429</v>
       </c>
       <c r="B1405" s="0" t="s">
-        <v>2075</v>
+        <v>2074</v>
       </c>
       <c r="C1405" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E1405" s="0" t="s">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="F1405" s="0" t="s">
         <v>854</v>
@@ -58451,13 +58447,13 @@
         <v>1430</v>
       </c>
       <c r="B1406" s="0" t="s">
+        <v>2075</v>
+      </c>
+      <c r="C1406" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1406" s="0" t="s">
         <v>2076</v>
-      </c>
-      <c r="C1406" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1406" s="0" t="s">
-        <v>2077</v>
       </c>
       <c r="F1406" s="0" t="s">
         <v>1394</v>
@@ -58486,7 +58482,7 @@
         <v>1431</v>
       </c>
       <c r="B1407" s="0" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="C1407" s="0" t="n">
         <v>3</v>
@@ -58521,7 +58517,7 @@
         <v>1432</v>
       </c>
       <c r="B1408" s="0" t="s">
-        <v>2079</v>
+        <v>2078</v>
       </c>
       <c r="C1408" s="0" t="n">
         <v>3</v>
@@ -58556,7 +58552,7 @@
         <v>1433</v>
       </c>
       <c r="B1409" s="0" t="s">
-        <v>2080</v>
+        <v>2079</v>
       </c>
       <c r="C1409" s="0" t="n">
         <v>3</v>
@@ -58594,13 +58590,13 @@
         <v>1434</v>
       </c>
       <c r="B1410" s="0" t="s">
+        <v>2080</v>
+      </c>
+      <c r="C1410" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1410" s="0" t="s">
         <v>2081</v>
-      </c>
-      <c r="C1410" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1410" s="0" t="s">
-        <v>2082</v>
       </c>
       <c r="F1410" s="0" t="s">
         <v>22</v>
@@ -58629,13 +58625,13 @@
         <v>1435</v>
       </c>
       <c r="B1411" s="0" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C1411" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E1411" s="0" t="s">
-        <v>2082</v>
+        <v>2081</v>
       </c>
       <c r="F1411" s="0" t="s">
         <v>22</v>
@@ -58664,13 +58660,13 @@
         <v>1436</v>
       </c>
       <c r="B1412" s="0" t="s">
+        <v>2083</v>
+      </c>
+      <c r="C1412" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1412" s="0" t="s">
         <v>2084</v>
-      </c>
-      <c r="C1412" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1412" s="0" t="s">
-        <v>2085</v>
       </c>
       <c r="F1412" s="0" t="s">
         <v>1512</v>
@@ -58699,7 +58695,7 @@
         <v>1437</v>
       </c>
       <c r="B1413" s="0" t="s">
-        <v>2086</v>
+        <v>2085</v>
       </c>
       <c r="C1413" s="0" t="n">
         <v>3</v>
@@ -58734,13 +58730,13 @@
         <v>1438</v>
       </c>
       <c r="B1414" s="0" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1414" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1414" s="0" t="s">
         <v>2087</v>
-      </c>
-      <c r="C1414" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1414" s="0" t="s">
-        <v>2088</v>
       </c>
       <c r="F1414" s="0" t="s">
         <v>106</v>
@@ -58769,7 +58765,7 @@
         <v>1439</v>
       </c>
       <c r="B1415" s="0" t="s">
-        <v>2089</v>
+        <v>2088</v>
       </c>
       <c r="C1415" s="0" t="n">
         <v>3</v>
@@ -58804,13 +58800,13 @@
         <v>1440</v>
       </c>
       <c r="B1416" s="0" t="s">
-        <v>2090</v>
+        <v>2089</v>
       </c>
       <c r="C1416" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E1416" s="0" t="s">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="F1416" s="0" t="s">
         <v>22</v>
@@ -58874,13 +58870,13 @@
         <v>1442</v>
       </c>
       <c r="B1418" s="0" t="s">
+        <v>2090</v>
+      </c>
+      <c r="C1418" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1418" s="0" t="s">
         <v>2091</v>
-      </c>
-      <c r="C1418" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1418" s="0" t="s">
-        <v>2092</v>
       </c>
       <c r="F1418" s="0" t="s">
         <v>22</v>
@@ -58909,13 +58905,13 @@
         <v>1443</v>
       </c>
       <c r="B1419" s="0" t="s">
+        <v>2092</v>
+      </c>
+      <c r="C1419" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1419" s="0" t="s">
         <v>2093</v>
-      </c>
-      <c r="C1419" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1419" s="0" t="s">
-        <v>2094</v>
       </c>
       <c r="F1419" s="0" t="s">
         <v>22</v>
@@ -58947,13 +58943,13 @@
         <v>1444</v>
       </c>
       <c r="B1420" s="0" t="s">
-        <v>2095</v>
+        <v>2094</v>
       </c>
       <c r="C1420" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E1420" s="0" t="s">
-        <v>2094</v>
+        <v>2093</v>
       </c>
       <c r="F1420" s="0" t="s">
         <v>22</v>
@@ -58982,13 +58978,13 @@
         <v>1445</v>
       </c>
       <c r="B1421" s="0" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1421" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1421" s="0" t="s">
         <v>2096</v>
-      </c>
-      <c r="C1421" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1421" s="0" t="s">
-        <v>2097</v>
       </c>
       <c r="F1421" s="0" t="s">
         <v>22</v>
@@ -59017,13 +59013,13 @@
         <v>1446</v>
       </c>
       <c r="B1422" s="0" t="s">
+        <v>2097</v>
+      </c>
+      <c r="C1422" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1422" s="0" t="s">
         <v>2098</v>
-      </c>
-      <c r="C1422" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1422" s="0" t="s">
-        <v>2099</v>
       </c>
       <c r="F1422" s="0" t="s">
         <v>22</v>
@@ -59052,13 +59048,13 @@
         <v>1447</v>
       </c>
       <c r="B1423" s="0" t="s">
+        <v>2099</v>
+      </c>
+      <c r="C1423" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1423" s="0" t="s">
         <v>2100</v>
-      </c>
-      <c r="C1423" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1423" s="0" t="s">
-        <v>2101</v>
       </c>
       <c r="F1423" s="0" t="s">
         <v>22</v>
@@ -59087,7 +59083,7 @@
         <v>1448</v>
       </c>
       <c r="B1424" s="0" t="s">
-        <v>2102</v>
+        <v>2101</v>
       </c>
       <c r="C1424" s="0" t="n">
         <v>3</v>
@@ -59157,16 +59153,16 @@
         <v>1450</v>
       </c>
       <c r="B1426" s="0" t="s">
-        <v>1828</v>
+        <v>1827</v>
       </c>
       <c r="C1426" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E1426" s="0" t="s">
+        <v>2102</v>
+      </c>
+      <c r="F1426" s="0" t="s">
         <v>2103</v>
-      </c>
-      <c r="F1426" s="0" t="s">
-        <v>2104</v>
       </c>
       <c r="G1426" s="0" t="n">
         <v>0</v>
@@ -59192,7 +59188,7 @@
         <v>1451</v>
       </c>
       <c r="B1427" s="0" t="s">
-        <v>2105</v>
+        <v>2104</v>
       </c>
       <c r="C1427" s="0" t="n">
         <v>3</v>
@@ -59227,7 +59223,7 @@
         <v>1452</v>
       </c>
       <c r="B1428" s="0" t="s">
-        <v>2106</v>
+        <v>2105</v>
       </c>
       <c r="C1428" s="0" t="n">
         <v>3</v>
@@ -59262,7 +59258,7 @@
         <v>1453</v>
       </c>
       <c r="B1429" s="0" t="s">
-        <v>2107</v>
+        <v>2106</v>
       </c>
       <c r="C1429" s="0" t="n">
         <v>3</v>
@@ -59297,13 +59293,13 @@
         <v>1454</v>
       </c>
       <c r="B1430" s="0" t="s">
+        <v>2107</v>
+      </c>
+      <c r="C1430" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1430" s="0" t="s">
         <v>2108</v>
-      </c>
-      <c r="C1430" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1430" s="0" t="s">
-        <v>2109</v>
       </c>
       <c r="F1430" s="0" t="s">
         <v>22</v>
@@ -59332,7 +59328,7 @@
         <v>1455</v>
       </c>
       <c r="B1431" s="0" t="s">
-        <v>2110</v>
+        <v>2109</v>
       </c>
       <c r="C1431" s="0" t="n">
         <v>3</v>
@@ -59367,7 +59363,7 @@
         <v>1456</v>
       </c>
       <c r="B1432" s="0" t="s">
-        <v>2111</v>
+        <v>2110</v>
       </c>
       <c r="C1432" s="0" t="n">
         <v>3</v>
@@ -59376,7 +59372,7 @@
         <v>1450</v>
       </c>
       <c r="F1432" s="0" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="G1432" s="0" t="n">
         <v>0</v>
@@ -59402,13 +59398,13 @@
         <v>1457</v>
       </c>
       <c r="B1433" s="0" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1433" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1433" s="0" t="s">
         <v>2113</v>
-      </c>
-      <c r="C1433" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1433" s="0" t="s">
-        <v>2114</v>
       </c>
       <c r="F1433" s="0" t="s">
         <v>854</v>
@@ -59437,13 +59433,13 @@
         <v>1458</v>
       </c>
       <c r="B1434" s="0" t="s">
-        <v>2115</v>
+        <v>2114</v>
       </c>
       <c r="C1434" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E1434" s="0" t="s">
-        <v>1850</v>
+        <v>1849</v>
       </c>
       <c r="F1434" s="0" t="s">
         <v>22</v>
@@ -59472,7 +59468,7 @@
         <v>1459</v>
       </c>
       <c r="B1435" s="0" t="s">
-        <v>2116</v>
+        <v>2115</v>
       </c>
       <c r="C1435" s="0" t="n">
         <v>3</v>
@@ -59510,7 +59506,7 @@
         <v>1460</v>
       </c>
       <c r="B1436" s="0" t="s">
-        <v>2117</v>
+        <v>2116</v>
       </c>
       <c r="C1436" s="0" t="n">
         <v>3</v>
@@ -59545,13 +59541,13 @@
         <v>1461</v>
       </c>
       <c r="B1437" s="0" t="s">
+        <v>2117</v>
+      </c>
+      <c r="C1437" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1437" s="0" t="s">
         <v>2118</v>
-      </c>
-      <c r="C1437" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1437" s="0" t="s">
-        <v>2119</v>
       </c>
       <c r="F1437" s="0" t="s">
         <v>662</v>
@@ -59580,7 +59576,7 @@
         <v>1462</v>
       </c>
       <c r="B1438" s="0" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
       <c r="C1438" s="0" t="n">
         <v>3</v>
@@ -59615,7 +59611,7 @@
         <v>1463</v>
       </c>
       <c r="B1439" s="0" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="C1439" s="0" t="n">
         <v>3</v>
@@ -59624,7 +59620,7 @@
         <v>98</v>
       </c>
       <c r="F1439" s="0" t="s">
-        <v>2122</v>
+        <v>2121</v>
       </c>
       <c r="G1439" s="0" t="n">
         <v>0</v>
@@ -59650,13 +59646,13 @@
         <v>1464</v>
       </c>
       <c r="B1440" s="0" t="s">
-        <v>2123</v>
+        <v>2122</v>
       </c>
       <c r="C1440" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E1440" s="0" t="s">
-        <v>2061</v>
+        <v>2060</v>
       </c>
       <c r="F1440" s="0" t="s">
         <v>662</v>
@@ -59685,13 +59681,13 @@
         <v>1465</v>
       </c>
       <c r="B1441" s="0" t="s">
+        <v>2123</v>
+      </c>
+      <c r="C1441" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1441" s="0" t="s">
         <v>2124</v>
-      </c>
-      <c r="C1441" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1441" s="0" t="s">
-        <v>2125</v>
       </c>
       <c r="F1441" s="0" t="s">
         <v>338</v>
@@ -59720,7 +59716,7 @@
         <v>1466</v>
       </c>
       <c r="B1442" s="0" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="C1442" s="0" t="n">
         <v>3</v>
@@ -59755,13 +59751,13 @@
         <v>1467</v>
       </c>
       <c r="B1443" s="0" t="s">
+        <v>2126</v>
+      </c>
+      <c r="C1443" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1443" s="0" t="s">
         <v>2127</v>
-      </c>
-      <c r="C1443" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1443" s="0" t="s">
-        <v>2128</v>
       </c>
       <c r="F1443" s="0" t="s">
         <v>22</v>
@@ -59787,7 +59783,7 @@
         <v>1468</v>
       </c>
       <c r="B1444" s="0" t="s">
-        <v>2129</v>
+        <v>2128</v>
       </c>
       <c r="C1444" s="0" t="n">
         <v>3</v>
@@ -59822,13 +59818,13 @@
         <v>1469</v>
       </c>
       <c r="B1445" s="0" t="s">
-        <v>2130</v>
+        <v>2129</v>
       </c>
       <c r="C1445" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E1445" s="0" t="s">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="F1445" s="0" t="s">
         <v>88</v>
@@ -59857,13 +59853,13 @@
         <v>1470</v>
       </c>
       <c r="B1446" s="0" t="s">
-        <v>2131</v>
+        <v>2130</v>
       </c>
       <c r="C1446" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E1446" s="0" t="s">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="F1446" s="0" t="s">
         <v>502</v>
@@ -59892,13 +59888,13 @@
         <v>1471</v>
       </c>
       <c r="B1447" s="0" t="s">
-        <v>2132</v>
+        <v>2131</v>
       </c>
       <c r="C1447" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E1447" s="0" t="s">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="F1447" s="0" t="s">
         <v>941</v>
@@ -59927,13 +59923,13 @@
         <v>1472</v>
       </c>
       <c r="B1448" s="0" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
       <c r="C1448" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E1448" s="0" t="s">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="F1448" s="0" t="s">
         <v>854</v>
@@ -59962,13 +59958,13 @@
         <v>1473</v>
       </c>
       <c r="B1449" s="0" t="s">
-        <v>2134</v>
+        <v>2133</v>
       </c>
       <c r="C1449" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E1449" s="0" t="s">
-        <v>2082</v>
+        <v>2081</v>
       </c>
       <c r="F1449" s="0" t="s">
         <v>22</v>
@@ -59997,13 +59993,13 @@
         <v>1474</v>
       </c>
       <c r="B1450" s="0" t="s">
-        <v>2135</v>
+        <v>2134</v>
       </c>
       <c r="C1450" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E1450" s="0" t="s">
-        <v>2082</v>
+        <v>2081</v>
       </c>
       <c r="F1450" s="0" t="s">
         <v>22</v>
@@ -60032,13 +60028,13 @@
         <v>1475</v>
       </c>
       <c r="B1451" s="0" t="s">
-        <v>2136</v>
+        <v>2135</v>
       </c>
       <c r="C1451" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E1451" s="0" t="s">
-        <v>2082</v>
+        <v>2081</v>
       </c>
       <c r="F1451" s="0" t="s">
         <v>27</v>
@@ -60067,13 +60063,13 @@
         <v>1476</v>
       </c>
       <c r="B1452" s="0" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="C1452" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E1452" s="0" t="s">
-        <v>2082</v>
+        <v>2081</v>
       </c>
       <c r="F1452" s="0" t="s">
         <v>22</v>
@@ -60102,16 +60098,16 @@
         <v>1477</v>
       </c>
       <c r="B1453" s="0" t="s">
-        <v>2138</v>
+        <v>2137</v>
       </c>
       <c r="C1453" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E1453" s="0" t="s">
-        <v>2082</v>
+        <v>2081</v>
       </c>
       <c r="F1453" s="0" t="s">
-        <v>1830</v>
+        <v>1829</v>
       </c>
       <c r="G1453" s="0" t="n">
         <v>0</v>
@@ -60137,13 +60133,13 @@
         <v>1478</v>
       </c>
       <c r="B1454" s="0" t="s">
+        <v>2138</v>
+      </c>
+      <c r="C1454" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1454" s="0" t="s">
         <v>2139</v>
-      </c>
-      <c r="C1454" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1454" s="0" t="s">
-        <v>2140</v>
       </c>
       <c r="F1454" s="0" t="s">
         <v>1252</v>
@@ -60172,13 +60168,13 @@
         <v>1479</v>
       </c>
       <c r="B1455" s="0" t="s">
+        <v>2140</v>
+      </c>
+      <c r="C1455" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1455" s="0" t="s">
         <v>2141</v>
-      </c>
-      <c r="C1455" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1455" s="0" t="s">
-        <v>2142</v>
       </c>
       <c r="F1455" s="0" t="s">
         <v>22</v>
@@ -60207,7 +60203,7 @@
         <v>1480</v>
       </c>
       <c r="B1456" s="0" t="s">
-        <v>2143</v>
+        <v>2142</v>
       </c>
       <c r="C1456" s="0" t="n">
         <v>3</v>
@@ -60242,7 +60238,7 @@
         <v>1481</v>
       </c>
       <c r="B1457" s="0" t="s">
-        <v>2144</v>
+        <v>2143</v>
       </c>
       <c r="C1457" s="0" t="n">
         <v>3</v>
@@ -60277,7 +60273,7 @@
         <v>1482</v>
       </c>
       <c r="B1458" s="0" t="s">
-        <v>2145</v>
+        <v>2144</v>
       </c>
       <c r="C1458" s="0" t="n">
         <v>3</v>
@@ -60312,16 +60308,16 @@
         <v>1483</v>
       </c>
       <c r="B1459" s="0" t="s">
+        <v>2145</v>
+      </c>
+      <c r="C1459" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1459" s="0" t="s">
+        <v>1887</v>
+      </c>
+      <c r="F1459" s="0" t="s">
         <v>2146</v>
-      </c>
-      <c r="C1459" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1459" s="0" t="s">
-        <v>1888</v>
-      </c>
-      <c r="F1459" s="0" t="s">
-        <v>2147</v>
       </c>
       <c r="G1459" s="0" t="n">
         <v>0</v>
@@ -60347,7 +60343,7 @@
         <v>1484</v>
       </c>
       <c r="B1460" s="0" t="s">
-        <v>2148</v>
+        <v>2147</v>
       </c>
       <c r="C1460" s="0" t="n">
         <v>3</v>
@@ -60356,7 +60352,7 @@
         <v>439</v>
       </c>
       <c r="F1460" s="0" t="s">
-        <v>2149</v>
+        <v>2148</v>
       </c>
       <c r="G1460" s="0" t="n">
         <v>0</v>
@@ -60382,13 +60378,13 @@
         <v>1485</v>
       </c>
       <c r="B1461" s="0" t="s">
-        <v>2150</v>
+        <v>2149</v>
       </c>
       <c r="C1461" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E1461" s="0" t="s">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="F1461" s="0" t="s">
         <v>22</v>
@@ -60417,16 +60413,16 @@
         <v>1486</v>
       </c>
       <c r="B1462" s="0" t="s">
-        <v>2151</v>
+        <v>2150</v>
       </c>
       <c r="C1462" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E1462" s="0" t="s">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="F1462" s="0" t="s">
-        <v>1950</v>
+        <v>1949</v>
       </c>
       <c r="G1462" s="0" t="n">
         <v>0</v>
@@ -60452,13 +60448,13 @@
         <v>1487</v>
       </c>
       <c r="B1463" s="0" t="s">
-        <v>2152</v>
+        <v>2151</v>
       </c>
       <c r="C1463" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E1463" s="0" t="s">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="F1463" s="0" t="s">
         <v>136</v>
@@ -60487,13 +60483,13 @@
         <v>1488</v>
       </c>
       <c r="B1464" s="0" t="s">
-        <v>2153</v>
+        <v>2152</v>
       </c>
       <c r="C1464" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E1464" s="0" t="s">
-        <v>2082</v>
+        <v>2081</v>
       </c>
       <c r="F1464" s="0" t="s">
         <v>857</v>
@@ -60522,16 +60518,16 @@
         <v>1489</v>
       </c>
       <c r="B1465" s="0" t="s">
+        <v>2153</v>
+      </c>
+      <c r="C1465" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1465" s="0" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1465" s="0" t="s">
         <v>2154</v>
-      </c>
-      <c r="C1465" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1465" s="0" t="s">
-        <v>2082</v>
-      </c>
-      <c r="F1465" s="0" t="s">
-        <v>2155</v>
       </c>
       <c r="G1465" s="0" t="n">
         <v>0</v>
@@ -60557,13 +60553,13 @@
         <v>1490</v>
       </c>
       <c r="B1466" s="0" t="s">
-        <v>2156</v>
+        <v>2155</v>
       </c>
       <c r="C1466" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E1466" s="0" t="s">
-        <v>2082</v>
+        <v>2081</v>
       </c>
       <c r="F1466" s="0" t="s">
         <v>136</v>
@@ -60592,13 +60588,13 @@
         <v>1491</v>
       </c>
       <c r="B1467" s="0" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="C1467" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E1467" s="0" t="s">
-        <v>2082</v>
+        <v>2081</v>
       </c>
       <c r="F1467" s="0" t="s">
         <v>857</v>
@@ -60627,7 +60623,7 @@
         <v>1492</v>
       </c>
       <c r="B1468" s="0" t="s">
-        <v>2158</v>
+        <v>2157</v>
       </c>
       <c r="C1468" s="0" t="n">
         <v>3</v>
@@ -60662,7 +60658,7 @@
         <v>1493</v>
       </c>
       <c r="B1469" s="0" t="s">
-        <v>2159</v>
+        <v>2158</v>
       </c>
       <c r="C1469" s="0" t="n">
         <v>3</v>
@@ -60697,13 +60693,13 @@
         <v>1494</v>
       </c>
       <c r="B1470" s="0" t="s">
-        <v>2160</v>
+        <v>2159</v>
       </c>
       <c r="C1470" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E1470" s="0" t="s">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="F1470" s="0" t="s">
         <v>22</v>
@@ -60732,7 +60728,7 @@
         <v>1495</v>
       </c>
       <c r="B1471" s="0" t="s">
-        <v>2161</v>
+        <v>2160</v>
       </c>
       <c r="C1471" s="0" t="n">
         <v>3</v>
@@ -60767,7 +60763,7 @@
         <v>1496</v>
       </c>
       <c r="B1472" s="0" t="s">
-        <v>2162</v>
+        <v>2161</v>
       </c>
       <c r="C1472" s="0" t="n">
         <v>3</v>
@@ -60802,7 +60798,7 @@
         <v>1497</v>
       </c>
       <c r="B1473" s="0" t="s">
-        <v>2163</v>
+        <v>2162</v>
       </c>
       <c r="C1473" s="0" t="n">
         <v>3</v>
@@ -60837,13 +60833,13 @@
         <v>1498</v>
       </c>
       <c r="B1474" s="0" t="s">
+        <v>2163</v>
+      </c>
+      <c r="C1474" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1474" s="0" t="s">
         <v>2164</v>
-      </c>
-      <c r="C1474" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1474" s="0" t="s">
-        <v>2165</v>
       </c>
       <c r="F1474" s="0" t="s">
         <v>857</v>
@@ -60872,13 +60868,13 @@
         <v>1499</v>
       </c>
       <c r="B1475" s="0" t="s">
+        <v>2165</v>
+      </c>
+      <c r="C1475" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1475" s="0" t="s">
         <v>2166</v>
-      </c>
-      <c r="C1475" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1475" s="0" t="s">
-        <v>2167</v>
       </c>
       <c r="F1475" s="0" t="s">
         <v>122</v>
@@ -60907,7 +60903,7 @@
         <v>1502</v>
       </c>
       <c r="B1476" s="0" t="s">
-        <v>2168</v>
+        <v>2167</v>
       </c>
       <c r="C1476" s="0" t="n">
         <v>3</v>
@@ -60916,7 +60912,7 @@
         <v>187</v>
       </c>
       <c r="F1476" s="0" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
       <c r="G1476" s="0" t="n">
         <v>0</v>
@@ -60942,7 +60938,7 @@
         <v>1503</v>
       </c>
       <c r="B1477" s="0" t="s">
-        <v>2170</v>
+        <v>2169</v>
       </c>
       <c r="C1477" s="0" t="n">
         <v>3</v>
@@ -60977,13 +60973,13 @@
         <v>1504</v>
       </c>
       <c r="B1478" s="0" t="s">
+        <v>2170</v>
+      </c>
+      <c r="C1478" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1478" s="0" t="s">
         <v>2171</v>
-      </c>
-      <c r="C1478" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1478" s="0" t="s">
-        <v>2172</v>
       </c>
       <c r="F1478" s="0" t="s">
         <v>22</v>
@@ -61009,13 +61005,13 @@
         <v>1505</v>
       </c>
       <c r="B1479" s="0" t="s">
+        <v>2172</v>
+      </c>
+      <c r="C1479" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1479" s="0" t="s">
         <v>2173</v>
-      </c>
-      <c r="C1479" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1479" s="0" t="s">
-        <v>2174</v>
       </c>
       <c r="F1479" s="0" t="s">
         <v>22</v>
@@ -61044,13 +61040,13 @@
         <v>1506</v>
       </c>
       <c r="B1480" s="0" t="s">
+        <v>2174</v>
+      </c>
+      <c r="C1480" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1480" s="0" t="s">
         <v>2175</v>
-      </c>
-      <c r="C1480" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1480" s="0" t="s">
-        <v>2176</v>
       </c>
       <c r="F1480" s="0" t="s">
         <v>22</v>
@@ -61079,7 +61075,7 @@
         <v>1507</v>
       </c>
       <c r="B1481" s="0" t="s">
-        <v>2177</v>
+        <v>2176</v>
       </c>
       <c r="C1481" s="0" t="n">
         <v>3</v>
@@ -61114,16 +61110,16 @@
         <v>1508</v>
       </c>
       <c r="B1482" s="0" t="s">
+        <v>2177</v>
+      </c>
+      <c r="C1482" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1482" s="0" t="s">
+        <v>1865</v>
+      </c>
+      <c r="F1482" s="0" t="s">
         <v>2178</v>
-      </c>
-      <c r="C1482" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1482" s="0" t="s">
-        <v>1866</v>
-      </c>
-      <c r="F1482" s="0" t="s">
-        <v>2179</v>
       </c>
       <c r="G1482" s="0" t="n">
         <v>0</v>
@@ -61149,13 +61145,13 @@
         <v>1509</v>
       </c>
       <c r="B1483" s="0" t="s">
-        <v>2180</v>
+        <v>2179</v>
       </c>
       <c r="C1483" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E1483" s="0" t="s">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="F1483" s="0" t="s">
         <v>22</v>
@@ -61184,7 +61180,7 @@
         <v>1510</v>
       </c>
       <c r="B1484" s="0" t="s">
-        <v>2181</v>
+        <v>2180</v>
       </c>
       <c r="C1484" s="0" t="n">
         <v>3</v>
@@ -61216,7 +61212,7 @@
         <v>1511</v>
       </c>
       <c r="B1485" s="0" t="s">
-        <v>2182</v>
+        <v>2181</v>
       </c>
       <c r="C1485" s="0" t="n">
         <v>3</v>
@@ -61254,13 +61250,13 @@
         <v>1512</v>
       </c>
       <c r="B1486" s="0" t="s">
-        <v>2183</v>
+        <v>2182</v>
       </c>
       <c r="C1486" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E1486" s="0" t="s">
-        <v>2142</v>
+        <v>2141</v>
       </c>
       <c r="F1486" s="0" t="s">
         <v>22</v>
@@ -61289,7 +61285,7 @@
         <v>1513</v>
       </c>
       <c r="B1487" s="0" t="s">
-        <v>2184</v>
+        <v>2183</v>
       </c>
       <c r="C1487" s="0" t="n">
         <v>3</v>
@@ -61324,7 +61320,7 @@
         <v>1514</v>
       </c>
       <c r="B1488" s="0" t="s">
-        <v>2144</v>
+        <v>2143</v>
       </c>
       <c r="C1488" s="0" t="n">
         <v>3</v>
@@ -61397,7 +61393,7 @@
         <v>1516</v>
       </c>
       <c r="B1490" s="0" t="s">
-        <v>2185</v>
+        <v>2184</v>
       </c>
       <c r="C1490" s="0" t="n">
         <v>3</v>
@@ -61432,7 +61428,7 @@
         <v>1517</v>
       </c>
       <c r="B1491" s="0" t="s">
-        <v>2186</v>
+        <v>2185</v>
       </c>
       <c r="C1491" s="0" t="n">
         <v>3</v>
@@ -61441,7 +61437,7 @@
         <v>1442</v>
       </c>
       <c r="F1491" s="0" t="s">
-        <v>2187</v>
+        <v>2186</v>
       </c>
       <c r="G1491" s="0" t="n">
         <v>0</v>
@@ -61467,13 +61463,13 @@
         <v>1518</v>
       </c>
       <c r="B1492" s="0" t="s">
+        <v>2187</v>
+      </c>
+      <c r="C1492" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1492" s="0" t="s">
         <v>2188</v>
-      </c>
-      <c r="C1492" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1492" s="0" t="s">
-        <v>2189</v>
       </c>
       <c r="F1492" s="0" t="s">
         <v>22</v>
@@ -61502,7 +61498,7 @@
         <v>1519</v>
       </c>
       <c r="B1493" s="0" t="s">
-        <v>2190</v>
+        <v>2189</v>
       </c>
       <c r="C1493" s="0" t="n">
         <v>3</v>
@@ -61537,7 +61533,7 @@
         <v>1520</v>
       </c>
       <c r="B1494" s="0" t="s">
-        <v>2191</v>
+        <v>2190</v>
       </c>
       <c r="C1494" s="0" t="n">
         <v>3</v>
@@ -61569,16 +61565,16 @@
         <v>1521</v>
       </c>
       <c r="B1495" s="0" t="s">
+        <v>2191</v>
+      </c>
+      <c r="C1495" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1495" s="0" t="s">
         <v>2192</v>
       </c>
-      <c r="C1495" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1495" s="0" t="s">
+      <c r="F1495" s="0" t="s">
         <v>2193</v>
-      </c>
-      <c r="F1495" s="0" t="s">
-        <v>2194</v>
       </c>
       <c r="G1495" s="0" t="n">
         <v>0</v>
@@ -61604,7 +61600,7 @@
         <v>1522</v>
       </c>
       <c r="B1496" s="0" t="s">
-        <v>2195</v>
+        <v>2194</v>
       </c>
       <c r="C1496" s="0" t="n">
         <v>3</v>
@@ -61639,13 +61635,13 @@
         <v>1523</v>
       </c>
       <c r="B1497" s="0" t="s">
+        <v>2195</v>
+      </c>
+      <c r="C1497" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1497" s="0" t="s">
         <v>2196</v>
-      </c>
-      <c r="C1497" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1497" s="0" t="s">
-        <v>2197</v>
       </c>
       <c r="F1497" s="0" t="s">
         <v>22</v>
@@ -61680,7 +61676,7 @@
         <v>3</v>
       </c>
       <c r="E1498" s="0" t="s">
-        <v>2198</v>
+        <v>2197</v>
       </c>
       <c r="F1498" s="0" t="s">
         <v>22</v>
@@ -61709,13 +61705,13 @@
         <v>1525</v>
       </c>
       <c r="B1499" s="0" t="s">
+        <v>2198</v>
+      </c>
+      <c r="C1499" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1499" s="0" t="s">
         <v>2199</v>
-      </c>
-      <c r="C1499" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1499" s="0" t="s">
-        <v>2200</v>
       </c>
       <c r="F1499" s="0" t="s">
         <v>22</v>
@@ -61744,13 +61740,13 @@
         <v>1526</v>
       </c>
       <c r="B1500" s="0" t="s">
+        <v>2200</v>
+      </c>
+      <c r="C1500" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1500" s="0" t="s">
         <v>2201</v>
-      </c>
-      <c r="C1500" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1500" s="0" t="s">
-        <v>2202</v>
       </c>
       <c r="F1500" s="0" t="s">
         <v>22</v>
@@ -61817,7 +61813,7 @@
         <v>1528</v>
       </c>
       <c r="B1502" s="0" t="s">
-        <v>2203</v>
+        <v>2202</v>
       </c>
       <c r="C1502" s="0" t="n">
         <v>3</v>
@@ -61852,13 +61848,13 @@
         <v>1529</v>
       </c>
       <c r="B1503" s="0" t="s">
+        <v>2203</v>
+      </c>
+      <c r="C1503" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1503" s="0" t="s">
         <v>2204</v>
-      </c>
-      <c r="C1503" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1503" s="0" t="s">
-        <v>2205</v>
       </c>
       <c r="F1503" s="0" t="s">
         <v>425</v>
@@ -61887,7 +61883,7 @@
         <v>1530</v>
       </c>
       <c r="B1504" s="0" t="s">
-        <v>2206</v>
+        <v>2205</v>
       </c>
       <c r="C1504" s="0" t="n">
         <v>3</v>
@@ -61925,7 +61921,7 @@
         <v>1531</v>
       </c>
       <c r="B1505" s="0" t="s">
-        <v>2207</v>
+        <v>2206</v>
       </c>
       <c r="C1505" s="0" t="n">
         <v>3</v>
@@ -61963,13 +61959,13 @@
         <v>1532</v>
       </c>
       <c r="B1506" s="0" t="s">
+        <v>2207</v>
+      </c>
+      <c r="C1506" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1506" s="0" t="s">
         <v>2208</v>
-      </c>
-      <c r="C1506" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1506" s="0" t="s">
-        <v>2209</v>
       </c>
       <c r="F1506" s="0" t="s">
         <v>1356</v>
@@ -61998,7 +61994,7 @@
         <v>1533</v>
       </c>
       <c r="B1507" s="0" t="s">
-        <v>2210</v>
+        <v>2209</v>
       </c>
       <c r="C1507" s="0" t="n">
         <v>3</v>
@@ -62033,7 +62029,7 @@
         <v>1534</v>
       </c>
       <c r="B1508" s="0" t="s">
-        <v>2211</v>
+        <v>2210</v>
       </c>
       <c r="C1508" s="0" t="n">
         <v>3</v>
@@ -62068,7 +62064,7 @@
         <v>1535</v>
       </c>
       <c r="B1509" s="0" t="s">
-        <v>2212</v>
+        <v>2211</v>
       </c>
       <c r="C1509" s="0" t="n">
         <v>3</v>
@@ -62103,7 +62099,7 @@
         <v>1536</v>
       </c>
       <c r="B1510" s="0" t="s">
-        <v>2213</v>
+        <v>2212</v>
       </c>
       <c r="C1510" s="0" t="n">
         <v>3</v>
@@ -62141,13 +62137,13 @@
         <v>1537</v>
       </c>
       <c r="B1511" s="0" t="s">
-        <v>2214</v>
+        <v>2213</v>
       </c>
       <c r="C1511" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E1511" s="0" t="s">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="F1511" s="0" t="s">
         <v>916</v>
@@ -62176,13 +62172,13 @@
         <v>1538</v>
       </c>
       <c r="B1512" s="0" t="s">
+        <v>2214</v>
+      </c>
+      <c r="C1512" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1512" s="0" t="s">
         <v>2215</v>
-      </c>
-      <c r="C1512" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1512" s="0" t="s">
-        <v>2216</v>
       </c>
       <c r="F1512" s="0" t="s">
         <v>941</v>
@@ -62211,7 +62207,7 @@
         <v>1539</v>
       </c>
       <c r="B1513" s="0" t="s">
-        <v>2217</v>
+        <v>2216</v>
       </c>
       <c r="C1513" s="0" t="n">
         <v>3</v>
@@ -62246,13 +62242,13 @@
         <v>1540</v>
       </c>
       <c r="B1514" s="0" t="s">
+        <v>2217</v>
+      </c>
+      <c r="C1514" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1514" s="0" t="s">
         <v>2218</v>
-      </c>
-      <c r="C1514" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1514" s="0" t="s">
-        <v>2219</v>
       </c>
       <c r="F1514" s="0" t="s">
         <v>1252</v>
@@ -62281,7 +62277,7 @@
         <v>1541</v>
       </c>
       <c r="B1515" s="0" t="s">
-        <v>2220</v>
+        <v>2219</v>
       </c>
       <c r="C1515" s="0" t="n">
         <v>3</v>
@@ -62316,13 +62312,13 @@
         <v>1542</v>
       </c>
       <c r="B1516" s="0" t="s">
+        <v>2220</v>
+      </c>
+      <c r="C1516" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1516" s="0" t="s">
         <v>2221</v>
-      </c>
-      <c r="C1516" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1516" s="0" t="s">
-        <v>2222</v>
       </c>
       <c r="F1516" s="0" t="s">
         <v>718</v>
@@ -62351,7 +62347,7 @@
         <v>1543</v>
       </c>
       <c r="B1517" s="0" t="s">
-        <v>2223</v>
+        <v>2222</v>
       </c>
       <c r="C1517" s="0" t="n">
         <v>3</v>
@@ -62389,7 +62385,7 @@
         <v>1544</v>
       </c>
       <c r="B1518" s="0" t="s">
-        <v>2224</v>
+        <v>2223</v>
       </c>
       <c r="C1518" s="0" t="n">
         <v>3</v>
@@ -62424,7 +62420,7 @@
         <v>1545</v>
       </c>
       <c r="B1519" s="0" t="s">
-        <v>2225</v>
+        <v>2224</v>
       </c>
       <c r="C1519" s="0" t="n">
         <v>3</v>
@@ -62433,7 +62429,7 @@
         <v>835</v>
       </c>
       <c r="F1519" s="0" t="s">
-        <v>2226</v>
+        <v>2225</v>
       </c>
       <c r="G1519" s="0" t="n">
         <v>0</v>
@@ -62459,7 +62455,7 @@
         <v>1546</v>
       </c>
       <c r="B1520" s="0" t="s">
-        <v>2227</v>
+        <v>2226</v>
       </c>
       <c r="C1520" s="0" t="n">
         <v>3</v>
@@ -62494,7 +62490,7 @@
         <v>1547</v>
       </c>
       <c r="B1521" s="0" t="s">
-        <v>2228</v>
+        <v>2227</v>
       </c>
       <c r="C1521" s="0" t="n">
         <v>3</v>
@@ -62532,13 +62528,13 @@
         <v>1548</v>
       </c>
       <c r="B1522" s="0" t="s">
-        <v>2229</v>
+        <v>2228</v>
       </c>
       <c r="C1522" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E1522" s="0" t="s">
-        <v>1821</v>
+        <v>1820</v>
       </c>
       <c r="F1522" s="0" t="s">
         <v>22</v>
@@ -62567,7 +62563,7 @@
         <v>1549</v>
       </c>
       <c r="B1523" s="0" t="s">
-        <v>2230</v>
+        <v>2229</v>
       </c>
       <c r="C1523" s="0" t="n">
         <v>3</v>
@@ -62602,13 +62598,13 @@
         <v>1550</v>
       </c>
       <c r="B1524" s="0" t="s">
+        <v>2230</v>
+      </c>
+      <c r="C1524" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1524" s="0" t="s">
         <v>2231</v>
-      </c>
-      <c r="C1524" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1524" s="0" t="s">
-        <v>2232</v>
       </c>
       <c r="F1524" s="0" t="s">
         <v>22</v>
@@ -62637,13 +62633,13 @@
         <v>1551</v>
       </c>
       <c r="B1525" s="0" t="s">
+        <v>2232</v>
+      </c>
+      <c r="C1525" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1525" s="0" t="s">
         <v>2233</v>
-      </c>
-      <c r="C1525" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1525" s="0" t="s">
-        <v>2234</v>
       </c>
       <c r="F1525" s="0" t="s">
         <v>22</v>
@@ -62672,16 +62668,16 @@
         <v>1552</v>
       </c>
       <c r="B1526" s="0" t="s">
+        <v>2234</v>
+      </c>
+      <c r="C1526" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1526" s="0" t="s">
+        <v>1938</v>
+      </c>
+      <c r="F1526" s="0" t="s">
         <v>2235</v>
-      </c>
-      <c r="C1526" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1526" s="0" t="s">
-        <v>1939</v>
-      </c>
-      <c r="F1526" s="0" t="s">
-        <v>2236</v>
       </c>
       <c r="G1526" s="0" t="n">
         <v>0</v>
@@ -62707,13 +62703,13 @@
         <v>1553</v>
       </c>
       <c r="B1527" s="0" t="s">
+        <v>2236</v>
+      </c>
+      <c r="C1527" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1527" s="0" t="s">
         <v>2237</v>
-      </c>
-      <c r="C1527" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1527" s="0" t="s">
-        <v>2238</v>
       </c>
       <c r="F1527" s="0" t="s">
         <v>22</v>
@@ -62742,7 +62738,7 @@
         <v>1554</v>
       </c>
       <c r="B1528" s="0" t="s">
-        <v>2239</v>
+        <v>2238</v>
       </c>
       <c r="C1528" s="0" t="n">
         <v>3</v>
@@ -62751,7 +62747,7 @@
         <v>39</v>
       </c>
       <c r="F1528" s="0" t="s">
-        <v>2240</v>
+        <v>2239</v>
       </c>
       <c r="G1528" s="0" t="n">
         <v>0</v>
@@ -62777,13 +62773,13 @@
         <v>1555</v>
       </c>
       <c r="B1529" s="0" t="s">
+        <v>2240</v>
+      </c>
+      <c r="C1529" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1529" s="0" t="s">
         <v>2241</v>
-      </c>
-      <c r="C1529" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1529" s="0" t="s">
-        <v>2242</v>
       </c>
       <c r="F1529" s="0" t="s">
         <v>22</v>
@@ -62812,7 +62808,7 @@
         <v>1556</v>
       </c>
       <c r="B1530" s="0" t="s">
-        <v>2243</v>
+        <v>2242</v>
       </c>
       <c r="C1530" s="0" t="n">
         <v>3</v>
@@ -62844,7 +62840,7 @@
         <v>1557</v>
       </c>
       <c r="B1531" s="0" t="s">
-        <v>2244</v>
+        <v>2243</v>
       </c>
       <c r="C1531" s="0" t="n">
         <v>3</v>
@@ -62879,13 +62875,13 @@
         <v>1558</v>
       </c>
       <c r="B1532" s="0" t="s">
+        <v>2244</v>
+      </c>
+      <c r="C1532" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1532" s="0" t="s">
         <v>2245</v>
-      </c>
-      <c r="C1532" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1532" s="0" t="s">
-        <v>2246</v>
       </c>
       <c r="F1532" s="0" t="s">
         <v>1512</v>
@@ -62914,13 +62910,13 @@
         <v>1559</v>
       </c>
       <c r="B1533" s="0" t="s">
+        <v>2246</v>
+      </c>
+      <c r="C1533" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1533" s="0" t="s">
         <v>2247</v>
-      </c>
-      <c r="C1533" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1533" s="0" t="s">
-        <v>2248</v>
       </c>
       <c r="F1533" s="0" t="s">
         <v>859</v>
@@ -62949,13 +62945,13 @@
         <v>1560</v>
       </c>
       <c r="B1534" s="0" t="s">
+        <v>2248</v>
+      </c>
+      <c r="C1534" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1534" s="0" t="s">
         <v>2249</v>
-      </c>
-      <c r="C1534" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1534" s="0" t="s">
-        <v>2250</v>
       </c>
       <c r="F1534" s="0" t="s">
         <v>1599</v>
@@ -62984,13 +62980,13 @@
         <v>1561</v>
       </c>
       <c r="B1535" s="0" t="s">
+        <v>2250</v>
+      </c>
+      <c r="C1535" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1535" s="0" t="s">
         <v>2251</v>
-      </c>
-      <c r="C1535" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1535" s="0" t="s">
-        <v>2252</v>
       </c>
       <c r="F1535" s="0" t="s">
         <v>22</v>
@@ -63019,13 +63015,13 @@
         <v>1562</v>
       </c>
       <c r="B1536" s="0" t="s">
-        <v>2253</v>
+        <v>2252</v>
       </c>
       <c r="C1536" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E1536" s="0" t="s">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="F1536" s="0" t="s">
         <v>22</v>
@@ -63054,13 +63050,13 @@
         <v>1563</v>
       </c>
       <c r="B1537" s="0" t="s">
-        <v>2254</v>
+        <v>2253</v>
       </c>
       <c r="C1537" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E1537" s="0" t="s">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="F1537" s="0" t="s">
         <v>194</v>
@@ -63089,13 +63085,13 @@
         <v>1564</v>
       </c>
       <c r="B1538" s="0" t="s">
+        <v>2254</v>
+      </c>
+      <c r="C1538" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1538" s="0" t="s">
         <v>2255</v>
-      </c>
-      <c r="C1538" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1538" s="0" t="s">
-        <v>2256</v>
       </c>
       <c r="F1538" s="0" t="s">
         <v>22</v>
@@ -63133,7 +63129,7 @@
         <v>3</v>
       </c>
       <c r="E1539" s="0" t="s">
-        <v>2197</v>
+        <v>2196</v>
       </c>
       <c r="F1539" s="0" t="s">
         <v>22</v>
@@ -63159,7 +63155,7 @@
         <v>1566</v>
       </c>
       <c r="B1540" s="0" t="s">
-        <v>2257</v>
+        <v>2256</v>
       </c>
       <c r="C1540" s="0" t="n">
         <v>3</v>
@@ -63168,7 +63164,7 @@
         <v>1488</v>
       </c>
       <c r="F1540" s="0" t="s">
-        <v>2258</v>
+        <v>2257</v>
       </c>
       <c r="G1540" s="0" t="n">
         <v>0</v>
@@ -63229,7 +63225,7 @@
         <v>1568</v>
       </c>
       <c r="B1542" s="0" t="s">
-        <v>2259</v>
+        <v>2258</v>
       </c>
       <c r="C1542" s="0" t="n">
         <v>3</v>
@@ -63264,13 +63260,13 @@
         <v>1569</v>
       </c>
       <c r="B1543" s="0" t="s">
+        <v>2259</v>
+      </c>
+      <c r="C1543" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1543" s="0" t="s">
         <v>2260</v>
-      </c>
-      <c r="C1543" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1543" s="0" t="s">
-        <v>2261</v>
       </c>
       <c r="F1543" s="0" t="s">
         <v>22</v>
@@ -63299,7 +63295,7 @@
         <v>1570</v>
       </c>
       <c r="B1544" s="0" t="s">
-        <v>2262</v>
+        <v>2261</v>
       </c>
       <c r="C1544" s="0" t="n">
         <v>3</v>
@@ -63331,7 +63327,7 @@
         <v>1571</v>
       </c>
       <c r="B1545" s="0" t="s">
-        <v>2263</v>
+        <v>2262</v>
       </c>
       <c r="C1545" s="0" t="n">
         <v>3</v>
@@ -63366,13 +63362,13 @@
         <v>1572</v>
       </c>
       <c r="B1546" s="0" t="s">
+        <v>2263</v>
+      </c>
+      <c r="C1546" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1546" s="0" t="s">
         <v>2264</v>
-      </c>
-      <c r="C1546" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1546" s="0" t="s">
-        <v>2265</v>
       </c>
       <c r="F1546" s="0" t="s">
         <v>88</v>
@@ -63401,7 +63397,7 @@
         <v>1573</v>
       </c>
       <c r="B1547" s="0" t="s">
-        <v>2266</v>
+        <v>2265</v>
       </c>
       <c r="C1547" s="0" t="n">
         <v>3</v>
@@ -63436,13 +63432,13 @@
         <v>1574</v>
       </c>
       <c r="B1548" s="0" t="s">
+        <v>2266</v>
+      </c>
+      <c r="C1548" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1548" s="0" t="s">
         <v>2267</v>
-      </c>
-      <c r="C1548" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1548" s="0" t="s">
-        <v>2268</v>
       </c>
       <c r="F1548" s="0" t="s">
         <v>88</v>
@@ -63471,13 +63467,13 @@
         <v>1575</v>
       </c>
       <c r="B1549" s="0" t="s">
+        <v>2268</v>
+      </c>
+      <c r="C1549" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1549" s="0" t="s">
         <v>2269</v>
-      </c>
-      <c r="C1549" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1549" s="0" t="s">
-        <v>2270</v>
       </c>
       <c r="F1549" s="0" t="s">
         <v>22</v>
@@ -63506,7 +63502,7 @@
         <v>1576</v>
       </c>
       <c r="B1550" s="0" t="s">
-        <v>2271</v>
+        <v>2270</v>
       </c>
       <c r="C1550" s="0" t="n">
         <v>3</v>
@@ -63541,13 +63537,13 @@
         <v>1577</v>
       </c>
       <c r="B1551" s="0" t="s">
+        <v>2271</v>
+      </c>
+      <c r="C1551" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1551" s="0" t="s">
         <v>2272</v>
-      </c>
-      <c r="C1551" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1551" s="0" t="s">
-        <v>2273</v>
       </c>
       <c r="F1551" s="0" t="s">
         <v>22</v>
@@ -63576,7 +63572,7 @@
         <v>1578</v>
       </c>
       <c r="B1552" s="0" t="s">
-        <v>2274</v>
+        <v>2273</v>
       </c>
       <c r="C1552" s="0" t="n">
         <v>3</v>
@@ -63611,7 +63607,7 @@
         <v>1579</v>
       </c>
       <c r="B1553" s="0" t="s">
-        <v>2275</v>
+        <v>2274</v>
       </c>
       <c r="C1553" s="0" t="n">
         <v>3</v>
@@ -63643,13 +63639,13 @@
         <v>1580</v>
       </c>
       <c r="B1554" s="0" t="s">
-        <v>2276</v>
+        <v>2275</v>
       </c>
       <c r="C1554" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E1554" s="0" t="s">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="F1554" s="0" t="s">
         <v>22</v>
@@ -63678,13 +63674,13 @@
         <v>1581</v>
       </c>
       <c r="B1555" s="0" t="s">
-        <v>2277</v>
+        <v>2276</v>
       </c>
       <c r="C1555" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E1555" s="0" t="s">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="F1555" s="0" t="s">
         <v>22</v>
@@ -63713,7 +63709,7 @@
         <v>1582</v>
       </c>
       <c r="B1556" s="0" t="s">
-        <v>2278</v>
+        <v>2277</v>
       </c>
       <c r="C1556" s="0" t="n">
         <v>3</v>
@@ -63748,13 +63744,13 @@
         <v>1583</v>
       </c>
       <c r="B1557" s="0" t="s">
-        <v>2279</v>
+        <v>2278</v>
       </c>
       <c r="C1557" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E1557" s="0" t="s">
-        <v>2209</v>
+        <v>2208</v>
       </c>
       <c r="F1557" s="0" t="s">
         <v>22</v>
@@ -63783,7 +63779,7 @@
         <v>1584</v>
       </c>
       <c r="B1558" s="0" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="C1558" s="0" t="n">
         <v>3</v>
@@ -63818,13 +63814,13 @@
         <v>1585</v>
       </c>
       <c r="B1559" s="0" t="s">
+        <v>2280</v>
+      </c>
+      <c r="C1559" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1559" s="0" t="s">
         <v>2281</v>
-      </c>
-      <c r="C1559" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1559" s="0" t="s">
-        <v>2282</v>
       </c>
       <c r="F1559" s="0" t="s">
         <v>22</v>
@@ -63853,13 +63849,13 @@
         <v>1586</v>
       </c>
       <c r="B1560" s="0" t="s">
-        <v>2283</v>
+        <v>2282</v>
       </c>
       <c r="C1560" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E1560" s="0" t="s">
-        <v>2282</v>
+        <v>2281</v>
       </c>
       <c r="F1560" s="0" t="s">
         <v>1599</v>
@@ -63888,13 +63884,13 @@
         <v>1587</v>
       </c>
       <c r="B1561" s="0" t="s">
-        <v>2284</v>
+        <v>2283</v>
       </c>
       <c r="C1561" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E1561" s="0" t="s">
-        <v>2282</v>
+        <v>2281</v>
       </c>
       <c r="F1561" s="0" t="s">
         <v>930</v>
@@ -63923,7 +63919,7 @@
         <v>1588</v>
       </c>
       <c r="B1562" s="0" t="s">
-        <v>2285</v>
+        <v>2284</v>
       </c>
       <c r="C1562" s="0" t="n">
         <v>3</v>
@@ -63958,7 +63954,7 @@
         <v>1589</v>
       </c>
       <c r="B1563" s="0" t="s">
-        <v>2286</v>
+        <v>2285</v>
       </c>
       <c r="C1563" s="0" t="n">
         <v>3</v>
@@ -63993,16 +63989,16 @@
         <v>1590</v>
       </c>
       <c r="B1564" s="0" t="s">
+        <v>2286</v>
+      </c>
+      <c r="C1564" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1564" s="0" t="s">
         <v>2287</v>
       </c>
-      <c r="C1564" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1564" s="0" t="s">
+      <c r="F1564" s="0" t="s">
         <v>2288</v>
-      </c>
-      <c r="F1564" s="0" t="s">
-        <v>2289</v>
       </c>
       <c r="G1564" s="0" t="n">
         <v>0</v>
@@ -64028,13 +64024,13 @@
         <v>1591</v>
       </c>
       <c r="B1565" s="0" t="s">
+        <v>2289</v>
+      </c>
+      <c r="C1565" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1565" s="0" t="s">
         <v>2290</v>
-      </c>
-      <c r="C1565" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1565" s="0" t="s">
-        <v>2291</v>
       </c>
       <c r="F1565" s="0" t="s">
         <v>22</v>
@@ -64063,13 +64059,13 @@
         <v>1592</v>
       </c>
       <c r="B1566" s="0" t="s">
+        <v>2291</v>
+      </c>
+      <c r="C1566" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1566" s="0" t="s">
         <v>2292</v>
-      </c>
-      <c r="C1566" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1566" s="0" t="s">
-        <v>2293</v>
       </c>
       <c r="F1566" s="0" t="s">
         <v>22</v>
@@ -64098,13 +64094,13 @@
         <v>1593</v>
       </c>
       <c r="B1567" s="0" t="s">
-        <v>2294</v>
+        <v>2293</v>
       </c>
       <c r="C1567" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E1567" s="0" t="s">
-        <v>1768</v>
+        <v>1767</v>
       </c>
       <c r="F1567" s="0" t="s">
         <v>22</v>
@@ -64133,13 +64129,13 @@
         <v>1594</v>
       </c>
       <c r="B1568" s="0" t="s">
-        <v>2295</v>
+        <v>2294</v>
       </c>
       <c r="C1568" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E1568" s="0" t="s">
-        <v>1768</v>
+        <v>1767</v>
       </c>
       <c r="F1568" s="0" t="s">
         <v>22</v>
@@ -64168,7 +64164,7 @@
         <v>1595</v>
       </c>
       <c r="B1569" s="0" t="s">
-        <v>2296</v>
+        <v>2295</v>
       </c>
       <c r="C1569" s="0" t="n">
         <v>3</v>
@@ -64203,7 +64199,7 @@
         <v>1596</v>
       </c>
       <c r="B1570" s="0" t="s">
-        <v>2297</v>
+        <v>2296</v>
       </c>
       <c r="C1570" s="0" t="n">
         <v>3</v>
@@ -64238,7 +64234,7 @@
         <v>1597</v>
       </c>
       <c r="B1571" s="0" t="s">
-        <v>2298</v>
+        <v>2297</v>
       </c>
       <c r="C1571" s="0" t="n">
         <v>3</v>
@@ -64273,13 +64269,13 @@
         <v>1598</v>
       </c>
       <c r="B1572" s="0" t="s">
-        <v>2299</v>
+        <v>2298</v>
       </c>
       <c r="C1572" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E1572" s="0" t="s">
-        <v>2238</v>
+        <v>2237</v>
       </c>
       <c r="F1572" s="0" t="s">
         <v>22</v>
@@ -64308,7 +64304,7 @@
         <v>1599</v>
       </c>
       <c r="B1573" s="0" t="s">
-        <v>2300</v>
+        <v>2299</v>
       </c>
       <c r="C1573" s="0" t="n">
         <v>3</v>
@@ -64343,13 +64339,13 @@
         <v>1600</v>
       </c>
       <c r="B1574" s="0" t="s">
-        <v>2301</v>
+        <v>2300</v>
       </c>
       <c r="C1574" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E1574" s="0" t="s">
-        <v>2270</v>
+        <v>2269</v>
       </c>
       <c r="F1574" s="0" t="s">
         <v>88</v>
@@ -64378,13 +64374,13 @@
         <v>1601</v>
       </c>
       <c r="B1575" s="0" t="s">
-        <v>2302</v>
+        <v>2301</v>
       </c>
       <c r="C1575" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E1575" s="0" t="s">
-        <v>2209</v>
+        <v>2208</v>
       </c>
       <c r="F1575" s="0" t="s">
         <v>88</v>
@@ -64413,13 +64409,13 @@
         <v>1602</v>
       </c>
       <c r="B1576" s="0" t="s">
+        <v>2302</v>
+      </c>
+      <c r="C1576" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1576" s="0" t="s">
         <v>2303</v>
-      </c>
-      <c r="C1576" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1576" s="0" t="s">
-        <v>2304</v>
       </c>
       <c r="F1576" s="0" t="s">
         <v>22</v>
@@ -64445,13 +64441,13 @@
         <v>1603</v>
       </c>
       <c r="B1577" s="0" t="s">
+        <v>2304</v>
+      </c>
+      <c r="C1577" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1577" s="0" t="s">
         <v>2305</v>
-      </c>
-      <c r="C1577" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1577" s="0" t="s">
-        <v>2306</v>
       </c>
       <c r="F1577" s="0" t="s">
         <v>22</v>
@@ -64480,7 +64476,7 @@
         <v>1604</v>
       </c>
       <c r="B1578" s="0" t="s">
-        <v>2307</v>
+        <v>2306</v>
       </c>
       <c r="C1578" s="0" t="n">
         <v>3</v>
@@ -64515,7 +64511,7 @@
         <v>1605</v>
       </c>
       <c r="B1579" s="0" t="s">
-        <v>2308</v>
+        <v>2307</v>
       </c>
       <c r="C1579" s="0" t="n">
         <v>3</v>
@@ -64585,13 +64581,13 @@
         <v>1607</v>
       </c>
       <c r="B1581" s="0" t="s">
+        <v>2308</v>
+      </c>
+      <c r="C1581" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1581" s="0" t="s">
         <v>2309</v>
-      </c>
-      <c r="C1581" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1581" s="0" t="s">
-        <v>2310</v>
       </c>
       <c r="F1581" s="0" t="s">
         <v>22</v>
@@ -64620,13 +64616,13 @@
         <v>1608</v>
       </c>
       <c r="B1582" s="0" t="s">
+        <v>2310</v>
+      </c>
+      <c r="C1582" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1582" s="0" t="s">
         <v>2311</v>
-      </c>
-      <c r="C1582" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1582" s="0" t="s">
-        <v>2312</v>
       </c>
       <c r="F1582" s="0" t="s">
         <v>22</v>
@@ -64655,13 +64651,13 @@
         <v>1609</v>
       </c>
       <c r="B1583" s="0" t="s">
-        <v>2313</v>
+        <v>2312</v>
       </c>
       <c r="C1583" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E1583" s="0" t="s">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="F1583" s="0" t="s">
         <v>930</v>
@@ -64690,7 +64686,7 @@
         <v>1610</v>
       </c>
       <c r="B1584" s="0" t="s">
-        <v>2314</v>
+        <v>2313</v>
       </c>
       <c r="C1584" s="0" t="n">
         <v>3</v>
@@ -64725,13 +64721,13 @@
         <v>1611</v>
       </c>
       <c r="B1585" s="0" t="s">
+        <v>2314</v>
+      </c>
+      <c r="C1585" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1585" s="0" t="s">
         <v>2315</v>
-      </c>
-      <c r="C1585" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1585" s="0" t="s">
-        <v>2316</v>
       </c>
       <c r="F1585" s="0" t="s">
         <v>22</v>
@@ -64760,7 +64756,7 @@
         <v>1612</v>
       </c>
       <c r="B1586" s="0" t="s">
-        <v>2317</v>
+        <v>2316</v>
       </c>
       <c r="C1586" s="0" t="n">
         <v>3</v>
@@ -64795,13 +64791,13 @@
         <v>1613</v>
       </c>
       <c r="B1587" s="0" t="s">
-        <v>2318</v>
+        <v>2317</v>
       </c>
       <c r="C1587" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E1587" s="0" t="s">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="F1587" s="0" t="s">
         <v>22</v>
@@ -64830,13 +64826,13 @@
         <v>1614</v>
       </c>
       <c r="B1588" s="0" t="s">
-        <v>2319</v>
+        <v>2318</v>
       </c>
       <c r="C1588" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E1588" s="0" t="s">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="F1588" s="0" t="s">
         <v>22</v>
@@ -64865,13 +64861,13 @@
         <v>1615</v>
       </c>
       <c r="B1589" s="0" t="s">
+        <v>2319</v>
+      </c>
+      <c r="C1589" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1589" s="0" t="s">
         <v>2320</v>
-      </c>
-      <c r="C1589" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1589" s="0" t="s">
-        <v>2321</v>
       </c>
       <c r="F1589" s="0" t="s">
         <v>22</v>
@@ -64900,7 +64896,7 @@
         <v>1616</v>
       </c>
       <c r="B1590" s="0" t="s">
-        <v>2322</v>
+        <v>2321</v>
       </c>
       <c r="C1590" s="0" t="n">
         <v>3</v>
@@ -64935,7 +64931,7 @@
         <v>1617</v>
       </c>
       <c r="B1591" s="0" t="s">
-        <v>2323</v>
+        <v>2322</v>
       </c>
       <c r="C1591" s="0" t="n">
         <v>3</v>
@@ -64970,13 +64966,13 @@
         <v>1618</v>
       </c>
       <c r="B1592" s="0" t="s">
+        <v>2323</v>
+      </c>
+      <c r="C1592" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1592" s="0" t="s">
         <v>2324</v>
-      </c>
-      <c r="C1592" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1592" s="0" t="s">
-        <v>2325</v>
       </c>
       <c r="F1592" s="0" t="s">
         <v>88</v>
@@ -65005,13 +65001,13 @@
         <v>1619</v>
       </c>
       <c r="B1593" s="0" t="s">
+        <v>2325</v>
+      </c>
+      <c r="C1593" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1593" s="0" t="s">
         <v>2326</v>
-      </c>
-      <c r="C1593" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1593" s="0" t="s">
-        <v>2327</v>
       </c>
       <c r="F1593" s="0" t="s">
         <v>88</v>
@@ -65040,7 +65036,7 @@
         <v>1620</v>
       </c>
       <c r="B1594" s="0" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="C1594" s="0" t="n">
         <v>3</v>
@@ -65078,7 +65074,7 @@
         <v>1621</v>
       </c>
       <c r="B1595" s="0" t="s">
-        <v>2329</v>
+        <v>2328</v>
       </c>
       <c r="C1595" s="0" t="n">
         <v>3</v>
@@ -65113,13 +65109,13 @@
         <v>1622</v>
       </c>
       <c r="B1596" s="0" t="s">
+        <v>2329</v>
+      </c>
+      <c r="C1596" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1596" s="0" t="s">
         <v>2330</v>
-      </c>
-      <c r="C1596" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1596" s="0" t="s">
-        <v>2331</v>
       </c>
       <c r="F1596" s="0" t="s">
         <v>941</v>
@@ -65148,7 +65144,7 @@
         <v>1623</v>
       </c>
       <c r="B1597" s="0" t="s">
-        <v>2332</v>
+        <v>2331</v>
       </c>
       <c r="C1597" s="0" t="n">
         <v>3</v>
@@ -65183,7 +65179,7 @@
         <v>1624</v>
       </c>
       <c r="B1598" s="0" t="s">
-        <v>2333</v>
+        <v>2332</v>
       </c>
       <c r="C1598" s="0" t="n">
         <v>3</v>
@@ -65218,13 +65214,13 @@
         <v>1625</v>
       </c>
       <c r="B1599" s="0" t="s">
+        <v>2333</v>
+      </c>
+      <c r="C1599" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1599" s="0" t="s">
         <v>2334</v>
-      </c>
-      <c r="C1599" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1599" s="0" t="s">
-        <v>2335</v>
       </c>
       <c r="F1599" s="0" t="s">
         <v>22</v>
@@ -65256,13 +65252,13 @@
         <v>1626</v>
       </c>
       <c r="B1600" s="0" t="s">
-        <v>2336</v>
+        <v>2335</v>
       </c>
       <c r="C1600" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E1600" s="0" t="s">
-        <v>2099</v>
+        <v>2098</v>
       </c>
       <c r="F1600" s="0" t="s">
         <v>88</v>
@@ -65291,7 +65287,7 @@
         <v>1627</v>
       </c>
       <c r="B1601" s="0" t="s">
-        <v>2337</v>
+        <v>2336</v>
       </c>
       <c r="C1601" s="0" t="n">
         <v>3</v>
@@ -65326,7 +65322,7 @@
         <v>1628</v>
       </c>
       <c r="B1602" s="0" t="s">
-        <v>2338</v>
+        <v>2337</v>
       </c>
       <c r="C1602" s="0" t="n">
         <v>3</v>
@@ -65361,7 +65357,7 @@
         <v>1629</v>
       </c>
       <c r="B1603" s="0" t="s">
-        <v>2339</v>
+        <v>2338</v>
       </c>
       <c r="C1603" s="0" t="n">
         <v>3</v>
@@ -65396,7 +65392,7 @@
         <v>1630</v>
       </c>
       <c r="B1604" s="0" t="s">
-        <v>2340</v>
+        <v>2339</v>
       </c>
       <c r="C1604" s="0" t="n">
         <v>3</v>
@@ -65434,7 +65430,7 @@
         <v>1631</v>
       </c>
       <c r="B1605" s="0" t="s">
-        <v>2341</v>
+        <v>2340</v>
       </c>
       <c r="C1605" s="0" t="n">
         <v>3</v>
@@ -65469,13 +65465,13 @@
         <v>1632</v>
       </c>
       <c r="B1606" s="0" t="s">
+        <v>2341</v>
+      </c>
+      <c r="C1606" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1606" s="0" t="s">
         <v>2342</v>
-      </c>
-      <c r="C1606" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1606" s="0" t="s">
-        <v>2343</v>
       </c>
       <c r="F1606" s="0" t="s">
         <v>22</v>
@@ -65504,7 +65500,7 @@
         <v>1633</v>
       </c>
       <c r="B1607" s="0" t="s">
-        <v>2344</v>
+        <v>2343</v>
       </c>
       <c r="C1607" s="0" t="n">
         <v>3</v>
@@ -65545,7 +65541,7 @@
         <v>3</v>
       </c>
       <c r="E1608" s="0" t="s">
-        <v>2345</v>
+        <v>2344</v>
       </c>
       <c r="F1608" s="0" t="s">
         <v>22</v>
@@ -65574,13 +65570,13 @@
         <v>1635</v>
       </c>
       <c r="B1609" s="0" t="s">
+        <v>2345</v>
+      </c>
+      <c r="C1609" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1609" s="0" t="s">
         <v>2346</v>
-      </c>
-      <c r="C1609" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1609" s="0" t="s">
-        <v>2347</v>
       </c>
       <c r="F1609" s="0" t="s">
         <v>22</v>
@@ -65609,7 +65605,7 @@
         <v>1636</v>
       </c>
       <c r="B1610" s="0" t="s">
-        <v>2348</v>
+        <v>2347</v>
       </c>
       <c r="C1610" s="0" t="n">
         <v>3</v>
@@ -65644,7 +65640,7 @@
         <v>1637</v>
       </c>
       <c r="B1611" s="0" t="s">
-        <v>2349</v>
+        <v>2348</v>
       </c>
       <c r="C1611" s="0" t="n">
         <v>3</v>
@@ -65682,13 +65678,13 @@
         <v>1638</v>
       </c>
       <c r="B1612" s="0" t="s">
-        <v>2350</v>
+        <v>2349</v>
       </c>
       <c r="C1612" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E1612" s="0" t="s">
-        <v>2282</v>
+        <v>2281</v>
       </c>
       <c r="F1612" s="0" t="s">
         <v>528</v>
@@ -65717,13 +65713,13 @@
         <v>1639</v>
       </c>
       <c r="B1613" s="0" t="s">
-        <v>2351</v>
+        <v>2350</v>
       </c>
       <c r="C1613" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E1613" s="0" t="s">
-        <v>2282</v>
+        <v>2281</v>
       </c>
       <c r="F1613" s="0" t="s">
         <v>22</v>
@@ -65752,13 +65748,13 @@
         <v>1640</v>
       </c>
       <c r="B1614" s="0" t="s">
-        <v>2352</v>
+        <v>2351</v>
       </c>
       <c r="C1614" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E1614" s="0" t="s">
-        <v>2282</v>
+        <v>2281</v>
       </c>
       <c r="F1614" s="0" t="s">
         <v>718</v>
@@ -65787,13 +65783,13 @@
         <v>1641</v>
       </c>
       <c r="B1615" s="0" t="s">
+        <v>2352</v>
+      </c>
+      <c r="C1615" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1615" s="0" t="s">
         <v>2353</v>
-      </c>
-      <c r="C1615" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1615" s="0" t="s">
-        <v>2354</v>
       </c>
       <c r="F1615" s="0" t="s">
         <v>22</v>
@@ -65822,7 +65818,7 @@
         <v>1642</v>
       </c>
       <c r="B1616" s="0" t="s">
-        <v>2355</v>
+        <v>2354</v>
       </c>
       <c r="C1616" s="0" t="n">
         <v>3</v>
@@ -65857,13 +65853,13 @@
         <v>1643</v>
       </c>
       <c r="B1617" s="0" t="s">
+        <v>2355</v>
+      </c>
+      <c r="C1617" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1617" s="0" t="s">
         <v>2356</v>
-      </c>
-      <c r="C1617" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1617" s="0" t="s">
-        <v>2357</v>
       </c>
       <c r="F1617" s="0" t="s">
         <v>22</v>
@@ -65898,7 +65894,7 @@
         <v>3</v>
       </c>
       <c r="E1618" s="0" t="s">
-        <v>2197</v>
+        <v>2196</v>
       </c>
       <c r="F1618" s="0" t="s">
         <v>22</v>
@@ -65924,7 +65920,7 @@
         <v>1645</v>
       </c>
       <c r="B1619" s="0" t="s">
-        <v>2358</v>
+        <v>2357</v>
       </c>
       <c r="C1619" s="0" t="n">
         <v>3</v>
@@ -65959,7 +65955,7 @@
         <v>1646</v>
       </c>
       <c r="B1620" s="0" t="s">
-        <v>2069</v>
+        <v>2068</v>
       </c>
       <c r="C1620" s="0" t="n">
         <v>3</v>
@@ -65997,13 +65993,13 @@
         <v>1647</v>
       </c>
       <c r="B1621" s="0" t="s">
-        <v>2359</v>
+        <v>2358</v>
       </c>
       <c r="C1621" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E1621" s="0" t="s">
-        <v>2082</v>
+        <v>2081</v>
       </c>
       <c r="F1621" s="0" t="s">
         <v>1596</v>
@@ -66032,16 +66028,16 @@
         <v>1648</v>
       </c>
       <c r="B1622" s="0" t="s">
+        <v>2359</v>
+      </c>
+      <c r="C1622" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1622" s="0" t="s">
         <v>2360</v>
       </c>
-      <c r="C1622" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1622" s="0" t="s">
+      <c r="F1622" s="0" t="s">
         <v>2361</v>
-      </c>
-      <c r="F1622" s="0" t="s">
-        <v>2362</v>
       </c>
       <c r="G1622" s="0" t="n">
         <v>0</v>
@@ -66067,13 +66063,13 @@
         <v>1649</v>
       </c>
       <c r="B1623" s="0" t="s">
-        <v>2363</v>
+        <v>2362</v>
       </c>
       <c r="C1623" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E1623" s="0" t="s">
-        <v>2082</v>
+        <v>2081</v>
       </c>
       <c r="F1623" s="0" t="s">
         <v>662</v>
@@ -66102,16 +66098,16 @@
         <v>1650</v>
       </c>
       <c r="B1624" s="0" t="s">
-        <v>2364</v>
+        <v>2363</v>
       </c>
       <c r="C1624" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E1624" s="0" t="s">
+        <v>2360</v>
+      </c>
+      <c r="F1624" s="0" t="s">
         <v>2361</v>
-      </c>
-      <c r="F1624" s="0" t="s">
-        <v>2362</v>
       </c>
       <c r="G1624" s="0" t="n">
         <v>0</v>
@@ -66137,13 +66133,13 @@
         <v>1651</v>
       </c>
       <c r="B1625" s="0" t="s">
-        <v>2365</v>
+        <v>2364</v>
       </c>
       <c r="C1625" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E1625" s="0" t="s">
-        <v>2082</v>
+        <v>2081</v>
       </c>
       <c r="F1625" s="0" t="s">
         <v>1305</v>
@@ -66172,13 +66168,13 @@
         <v>1652</v>
       </c>
       <c r="B1626" s="0" t="s">
-        <v>2366</v>
+        <v>2365</v>
       </c>
       <c r="C1626" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E1626" s="0" t="s">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="F1626" s="0" t="s">
         <v>512</v>
@@ -66207,16 +66203,16 @@
         <v>1653</v>
       </c>
       <c r="B1627" s="0" t="s">
-        <v>2367</v>
+        <v>2366</v>
       </c>
       <c r="C1627" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E1627" s="0" t="s">
-        <v>2082</v>
+        <v>2081</v>
       </c>
       <c r="F1627" s="0" t="s">
-        <v>1861</v>
+        <v>1860</v>
       </c>
       <c r="G1627" s="0" t="n">
         <v>0</v>
@@ -66242,7 +66238,7 @@
         <v>1654</v>
       </c>
       <c r="B1628" s="0" t="s">
-        <v>2368</v>
+        <v>2367</v>
       </c>
       <c r="C1628" s="0" t="n">
         <v>3</v>
@@ -66251,7 +66247,7 @@
         <v>998</v>
       </c>
       <c r="F1628" s="0" t="s">
-        <v>2369</v>
+        <v>2368</v>
       </c>
       <c r="G1628" s="0" t="n">
         <v>0</v>
@@ -66277,7 +66273,7 @@
         <v>1655</v>
       </c>
       <c r="B1629" s="0" t="s">
-        <v>2370</v>
+        <v>2369</v>
       </c>
       <c r="C1629" s="0" t="n">
         <v>3</v>
@@ -66312,7 +66308,7 @@
         <v>1656</v>
       </c>
       <c r="B1630" s="0" t="s">
-        <v>2371</v>
+        <v>2370</v>
       </c>
       <c r="C1630" s="0" t="n">
         <v>3</v>
@@ -66347,13 +66343,13 @@
         <v>1657</v>
       </c>
       <c r="B1631" s="0" t="s">
+        <v>2371</v>
+      </c>
+      <c r="C1631" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1631" s="0" t="s">
         <v>2372</v>
-      </c>
-      <c r="C1631" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1631" s="0" t="s">
-        <v>2373</v>
       </c>
       <c r="F1631" s="0" t="s">
         <v>22</v>
@@ -66382,16 +66378,16 @@
         <v>1658</v>
       </c>
       <c r="B1632" s="0" t="s">
+        <v>2373</v>
+      </c>
+      <c r="C1632" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1632" s="0" t="s">
+        <v>2372</v>
+      </c>
+      <c r="F1632" s="0" t="s">
         <v>2374</v>
-      </c>
-      <c r="C1632" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1632" s="0" t="s">
-        <v>2373</v>
-      </c>
-      <c r="F1632" s="0" t="s">
-        <v>2375</v>
       </c>
       <c r="G1632" s="0" t="n">
         <v>0</v>
@@ -66414,7 +66410,7 @@
         <v>1659</v>
       </c>
       <c r="B1633" s="0" t="s">
-        <v>2376</v>
+        <v>2375</v>
       </c>
       <c r="C1633" s="0" t="n">
         <v>3</v>
@@ -66449,7 +66445,7 @@
         <v>1660</v>
       </c>
       <c r="B1634" s="0" t="s">
-        <v>2377</v>
+        <v>2376</v>
       </c>
       <c r="C1634" s="0" t="n">
         <v>3</v>
@@ -66484,13 +66480,13 @@
         <v>1661</v>
       </c>
       <c r="B1635" s="0" t="s">
-        <v>2378</v>
+        <v>2377</v>
       </c>
       <c r="C1635" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E1635" s="0" t="s">
-        <v>1768</v>
+        <v>1767</v>
       </c>
       <c r="F1635" s="0" t="s">
         <v>22</v>
@@ -66516,13 +66512,13 @@
         <v>1662</v>
       </c>
       <c r="B1636" s="0" t="s">
+        <v>2378</v>
+      </c>
+      <c r="C1636" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1636" s="0" t="s">
         <v>2379</v>
-      </c>
-      <c r="C1636" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1636" s="0" t="s">
-        <v>2380</v>
       </c>
       <c r="F1636" s="0" t="s">
         <v>1252</v>
@@ -66551,13 +66547,13 @@
         <v>1663</v>
       </c>
       <c r="B1637" s="0" t="s">
+        <v>2380</v>
+      </c>
+      <c r="C1637" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1637" s="0" t="s">
         <v>2381</v>
-      </c>
-      <c r="C1637" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1637" s="0" t="s">
-        <v>2382</v>
       </c>
       <c r="F1637" s="0" t="s">
         <v>22</v>
@@ -66586,13 +66582,13 @@
         <v>1664</v>
       </c>
       <c r="B1638" s="0" t="s">
+        <v>2382</v>
+      </c>
+      <c r="C1638" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1638" s="0" t="s">
         <v>2383</v>
-      </c>
-      <c r="C1638" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1638" s="0" t="s">
-        <v>2384</v>
       </c>
       <c r="F1638" s="0" t="s">
         <v>22</v>
@@ -66618,7 +66614,7 @@
         <v>1665</v>
       </c>
       <c r="B1639" s="0" t="s">
-        <v>2385</v>
+        <v>2384</v>
       </c>
       <c r="C1639" s="0" t="n">
         <v>3</v>
@@ -66650,7 +66646,7 @@
         <v>1666</v>
       </c>
       <c r="B1640" s="0" t="s">
-        <v>2386</v>
+        <v>2385</v>
       </c>
       <c r="C1640" s="0" t="n">
         <v>3</v>
@@ -66682,7 +66678,7 @@
         <v>1667</v>
       </c>
       <c r="B1641" s="0" t="s">
-        <v>2387</v>
+        <v>2386</v>
       </c>
       <c r="C1641" s="0" t="n">
         <v>3</v>
@@ -66717,13 +66713,13 @@
         <v>1668</v>
       </c>
       <c r="B1642" s="0" t="s">
+        <v>2387</v>
+      </c>
+      <c r="C1642" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1642" s="0" t="s">
         <v>2388</v>
-      </c>
-      <c r="C1642" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1642" s="0" t="s">
-        <v>2389</v>
       </c>
       <c r="F1642" s="0" t="s">
         <v>22</v>
@@ -66749,13 +66745,13 @@
         <v>1669</v>
       </c>
       <c r="B1643" s="0" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="C1643" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E1643" s="0" t="s">
-        <v>2198</v>
+        <v>2197</v>
       </c>
       <c r="F1643" s="0" t="s">
         <v>22</v>
@@ -66781,13 +66777,13 @@
         <v>1670</v>
       </c>
       <c r="B1644" s="0" t="s">
+        <v>2390</v>
+      </c>
+      <c r="C1644" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1644" s="0" t="s">
         <v>2391</v>
-      </c>
-      <c r="C1644" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1644" s="0" t="s">
-        <v>2392</v>
       </c>
       <c r="F1644" s="0" t="s">
         <v>22</v>
@@ -66816,7 +66812,7 @@
         <v>1671</v>
       </c>
       <c r="B1645" s="0" t="s">
-        <v>2393</v>
+        <v>2392</v>
       </c>
       <c r="C1645" s="0" t="n">
         <v>3</v>
@@ -66851,7 +66847,7 @@
         <v>1672</v>
       </c>
       <c r="B1646" s="0" t="s">
-        <v>2394</v>
+        <v>2393</v>
       </c>
       <c r="C1646" s="0" t="n">
         <v>3</v>
@@ -66886,7 +66882,7 @@
         <v>1673</v>
       </c>
       <c r="B1647" s="0" t="s">
-        <v>2395</v>
+        <v>2394</v>
       </c>
       <c r="C1647" s="0" t="n">
         <v>3</v>
@@ -66895,7 +66891,7 @@
         <v>224</v>
       </c>
       <c r="F1647" s="0" t="s">
-        <v>1898</v>
+        <v>1897</v>
       </c>
       <c r="G1647" s="0" t="n">
         <v>0</v>
@@ -66927,7 +66923,7 @@
         <v>3</v>
       </c>
       <c r="E1648" s="0" t="s">
-        <v>2396</v>
+        <v>2395</v>
       </c>
       <c r="F1648" s="0" t="s">
         <v>22</v>
@@ -66956,7 +66952,7 @@
         <v>1675</v>
       </c>
       <c r="B1649" s="0" t="s">
-        <v>2397</v>
+        <v>2396</v>
       </c>
       <c r="C1649" s="0" t="n">
         <v>3</v>
@@ -66991,13 +66987,13 @@
         <v>1676</v>
       </c>
       <c r="B1650" s="0" t="s">
+        <v>2397</v>
+      </c>
+      <c r="C1650" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1650" s="0" t="s">
         <v>2398</v>
-      </c>
-      <c r="C1650" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1650" s="0" t="s">
-        <v>2399</v>
       </c>
       <c r="F1650" s="0" t="s">
         <v>22</v>
@@ -67029,13 +67025,13 @@
         <v>1677</v>
       </c>
       <c r="B1651" s="0" t="s">
-        <v>2400</v>
+        <v>2399</v>
       </c>
       <c r="C1651" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E1651" s="0" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
       <c r="F1651" s="0" t="s">
         <v>22</v>
@@ -67064,13 +67060,13 @@
         <v>1678</v>
       </c>
       <c r="B1652" s="0" t="s">
+        <v>2400</v>
+      </c>
+      <c r="C1652" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1652" s="0" t="s">
         <v>2401</v>
-      </c>
-      <c r="C1652" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1652" s="0" t="s">
-        <v>2402</v>
       </c>
       <c r="F1652" s="0" t="s">
         <v>1209</v>
@@ -67099,13 +67095,13 @@
         <v>1679</v>
       </c>
       <c r="B1653" s="0" t="s">
+        <v>2402</v>
+      </c>
+      <c r="C1653" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1653" s="0" t="s">
         <v>2403</v>
-      </c>
-      <c r="C1653" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1653" s="0" t="s">
-        <v>2404</v>
       </c>
       <c r="F1653" s="0" t="s">
         <v>857</v>
@@ -67140,10 +67136,10 @@
         <v>3</v>
       </c>
       <c r="E1654" s="0" t="s">
-        <v>2384</v>
+        <v>2383</v>
       </c>
       <c r="F1654" s="0" t="s">
-        <v>2405</v>
+        <v>2404</v>
       </c>
       <c r="G1654" s="0" t="n">
         <v>0</v>
@@ -67169,13 +67165,13 @@
         <v>1681</v>
       </c>
       <c r="B1655" s="0" t="s">
+        <v>2405</v>
+      </c>
+      <c r="C1655" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1655" s="0" t="s">
         <v>2406</v>
-      </c>
-      <c r="C1655" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1655" s="0" t="s">
-        <v>2407</v>
       </c>
       <c r="F1655" s="0" t="s">
         <v>22</v>
@@ -67204,7 +67200,7 @@
         <v>1682</v>
       </c>
       <c r="B1656" s="0" t="s">
-        <v>2408</v>
+        <v>2407</v>
       </c>
       <c r="C1656" s="0" t="n">
         <v>3</v>
@@ -67239,13 +67235,13 @@
         <v>1683</v>
       </c>
       <c r="B1657" s="0" t="s">
+        <v>2408</v>
+      </c>
+      <c r="C1657" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1657" s="0" t="s">
         <v>2409</v>
-      </c>
-      <c r="C1657" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1657" s="0" t="s">
-        <v>2410</v>
       </c>
       <c r="F1657" s="0" t="s">
         <v>22</v>
@@ -67274,7 +67270,7 @@
         <v>1684</v>
       </c>
       <c r="B1658" s="0" t="s">
-        <v>2411</v>
+        <v>2410</v>
       </c>
       <c r="C1658" s="0" t="n">
         <v>3</v>
@@ -67309,7 +67305,7 @@
         <v>1685</v>
       </c>
       <c r="B1659" s="0" t="s">
-        <v>2412</v>
+        <v>2411</v>
       </c>
       <c r="C1659" s="0" t="n">
         <v>3</v>
@@ -67344,7 +67340,7 @@
         <v>1686</v>
       </c>
       <c r="B1660" s="0" t="s">
-        <v>2413</v>
+        <v>2412</v>
       </c>
       <c r="C1660" s="0" t="n">
         <v>3</v>
@@ -67376,13 +67372,13 @@
         <v>1687</v>
       </c>
       <c r="B1661" s="0" t="s">
+        <v>2413</v>
+      </c>
+      <c r="C1661" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1661" s="0" t="s">
         <v>2414</v>
-      </c>
-      <c r="C1661" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1661" s="0" t="s">
-        <v>2415</v>
       </c>
       <c r="F1661" s="0" t="s">
         <v>22</v>
@@ -67408,13 +67404,13 @@
         <v>1688</v>
       </c>
       <c r="B1662" s="0" t="s">
+        <v>2415</v>
+      </c>
+      <c r="C1662" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1662" s="0" t="s">
         <v>2416</v>
-      </c>
-      <c r="C1662" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1662" s="0" t="s">
-        <v>2417</v>
       </c>
       <c r="F1662" s="0" t="s">
         <v>22</v>
@@ -67443,16 +67439,16 @@
         <v>1689</v>
       </c>
       <c r="B1663" s="0" t="s">
-        <v>2418</v>
+        <v>2417</v>
       </c>
       <c r="C1663" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E1663" s="0" t="s">
-        <v>2082</v>
+        <v>2081</v>
       </c>
       <c r="F1663" s="0" t="s">
-        <v>1830</v>
+        <v>1829</v>
       </c>
       <c r="G1663" s="0" t="n">
         <v>0</v>
@@ -67478,7 +67474,7 @@
         <v>1690</v>
       </c>
       <c r="B1664" s="0" t="s">
-        <v>2419</v>
+        <v>2418</v>
       </c>
       <c r="C1664" s="0" t="n">
         <v>3</v>
@@ -67513,7 +67509,7 @@
         <v>1691</v>
       </c>
       <c r="B1665" s="0" t="s">
-        <v>2420</v>
+        <v>2419</v>
       </c>
       <c r="C1665" s="0" t="n">
         <v>3</v>
@@ -67548,7 +67544,7 @@
         <v>1692</v>
       </c>
       <c r="B1666" s="0" t="s">
-        <v>2421</v>
+        <v>2420</v>
       </c>
       <c r="C1666" s="0" t="n">
         <v>3</v>
@@ -67583,16 +67579,16 @@
         <v>1693</v>
       </c>
       <c r="B1667" s="0" t="s">
+        <v>2421</v>
+      </c>
+      <c r="C1667" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1667" s="0" t="s">
         <v>2422</v>
       </c>
-      <c r="C1667" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1667" s="0" t="s">
-        <v>2423</v>
-      </c>
       <c r="F1667" s="0" t="s">
-        <v>1930</v>
+        <v>1929</v>
       </c>
       <c r="G1667" s="0" t="n">
         <v>0</v>
@@ -67618,13 +67614,13 @@
         <v>1694</v>
       </c>
       <c r="B1668" s="0" t="s">
-        <v>2424</v>
+        <v>2423</v>
       </c>
       <c r="C1668" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E1668" s="0" t="s">
-        <v>1796</v>
+        <v>1795</v>
       </c>
       <c r="F1668" s="0" t="s">
         <v>22</v>
@@ -67653,16 +67649,16 @@
         <v>1695</v>
       </c>
       <c r="B1669" s="0" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C1669" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1669" s="0" t="s">
         <v>2424</v>
       </c>
-      <c r="C1669" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1669" s="0" t="s">
+      <c r="F1669" s="0" t="s">
         <v>2425</v>
-      </c>
-      <c r="F1669" s="0" t="s">
-        <v>2426</v>
       </c>
       <c r="G1669" s="0" t="n">
         <v>0</v>
@@ -67688,7 +67684,7 @@
         <v>1696</v>
       </c>
       <c r="B1670" s="0" t="s">
-        <v>2427</v>
+        <v>2426</v>
       </c>
       <c r="C1670" s="0" t="n">
         <v>3</v>
@@ -67729,10 +67725,10 @@
         <v>3</v>
       </c>
       <c r="E1671" s="0" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="F1671" s="0" t="s">
-        <v>2428</v>
+        <v>2427</v>
       </c>
       <c r="G1671" s="0" t="n">
         <v>0</v>
@@ -67758,7 +67754,7 @@
         <v>1698</v>
       </c>
       <c r="B1672" s="0" t="s">
-        <v>2429</v>
+        <v>2428</v>
       </c>
       <c r="C1672" s="0" t="n">
         <v>3</v>
@@ -67767,7 +67763,7 @@
         <v>511</v>
       </c>
       <c r="F1672" s="0" t="s">
-        <v>1839</v>
+        <v>1838</v>
       </c>
       <c r="G1672" s="0" t="n">
         <v>0</v>
@@ -67793,13 +67789,13 @@
         <v>1699</v>
       </c>
       <c r="B1673" s="0" t="s">
+        <v>2429</v>
+      </c>
+      <c r="C1673" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1673" s="0" t="s">
         <v>2430</v>
-      </c>
-      <c r="C1673" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1673" s="0" t="s">
-        <v>2431</v>
       </c>
       <c r="F1673" s="0" t="s">
         <v>22</v>
@@ -67828,7 +67824,7 @@
         <v>1700</v>
       </c>
       <c r="B1674" s="0" t="s">
-        <v>2432</v>
+        <v>2431</v>
       </c>
       <c r="C1674" s="0" t="n">
         <v>3</v>
@@ -67837,7 +67833,7 @@
         <v>233</v>
       </c>
       <c r="F1674" s="0" t="s">
-        <v>2433</v>
+        <v>2432</v>
       </c>
       <c r="G1674" s="0" t="n">
         <v>0</v>
@@ -67863,7 +67859,7 @@
         <v>1701</v>
       </c>
       <c r="B1675" s="0" t="s">
-        <v>2434</v>
+        <v>2433</v>
       </c>
       <c r="C1675" s="0" t="n">
         <v>3</v>
@@ -67898,13 +67894,13 @@
         <v>1702</v>
       </c>
       <c r="B1676" s="0" t="s">
+        <v>2434</v>
+      </c>
+      <c r="C1676" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1676" s="0" t="s">
         <v>2435</v>
-      </c>
-      <c r="C1676" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1676" s="0" t="s">
-        <v>2436</v>
       </c>
       <c r="F1676" s="0" t="s">
         <v>88</v>
@@ -67933,7 +67929,7 @@
         <v>1703</v>
       </c>
       <c r="B1677" s="0" t="s">
-        <v>2437</v>
+        <v>2436</v>
       </c>
       <c r="C1677" s="0" t="n">
         <v>3</v>
@@ -67968,16 +67964,16 @@
         <v>1704</v>
       </c>
       <c r="B1678" s="0" t="s">
+        <v>2437</v>
+      </c>
+      <c r="C1678" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1678" s="0" t="s">
         <v>2438</v>
       </c>
-      <c r="C1678" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1678" s="0" t="s">
+      <c r="F1678" s="0" t="s">
         <v>2439</v>
-      </c>
-      <c r="F1678" s="0" t="s">
-        <v>2440</v>
       </c>
       <c r="G1678" s="0" t="n">
         <v>0</v>
@@ -68003,7 +67999,7 @@
         <v>1705</v>
       </c>
       <c r="B1679" s="0" t="s">
-        <v>2441</v>
+        <v>2440</v>
       </c>
       <c r="C1679" s="0" t="n">
         <v>3</v>
@@ -68038,13 +68034,13 @@
         <v>1706</v>
       </c>
       <c r="B1680" s="0" t="s">
+        <v>2441</v>
+      </c>
+      <c r="C1680" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1680" s="0" t="s">
         <v>2442</v>
-      </c>
-      <c r="C1680" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1680" s="0" t="s">
-        <v>2443</v>
       </c>
       <c r="F1680" s="0" t="s">
         <v>22</v>
@@ -68073,13 +68069,13 @@
         <v>1707</v>
       </c>
       <c r="B1681" s="0" t="s">
+        <v>2443</v>
+      </c>
+      <c r="C1681" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1681" s="0" t="s">
         <v>2444</v>
-      </c>
-      <c r="C1681" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1681" s="0" t="s">
-        <v>2445</v>
       </c>
       <c r="F1681" s="0" t="s">
         <v>22</v>
@@ -68108,7 +68104,7 @@
         <v>1708</v>
       </c>
       <c r="B1682" s="0" t="s">
-        <v>2446</v>
+        <v>2445</v>
       </c>
       <c r="C1682" s="0" t="n">
         <v>3</v>
@@ -68143,7 +68139,7 @@
         <v>1709</v>
       </c>
       <c r="B1683" s="0" t="s">
-        <v>2447</v>
+        <v>2446</v>
       </c>
       <c r="C1683" s="0" t="n">
         <v>3</v>
@@ -68178,13 +68174,13 @@
         <v>1710</v>
       </c>
       <c r="B1684" s="0" t="s">
+        <v>2447</v>
+      </c>
+      <c r="C1684" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1684" s="0" t="s">
         <v>2448</v>
-      </c>
-      <c r="C1684" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1684" s="0" t="s">
-        <v>2449</v>
       </c>
       <c r="F1684" s="0" t="s">
         <v>22</v>
@@ -68213,13 +68209,13 @@
         <v>1711</v>
       </c>
       <c r="B1685" s="0" t="s">
+        <v>2449</v>
+      </c>
+      <c r="C1685" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1685" s="0" t="s">
         <v>2450</v>
-      </c>
-      <c r="C1685" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1685" s="0" t="s">
-        <v>2451</v>
       </c>
       <c r="F1685" s="0" t="s">
         <v>22</v>
@@ -68280,16 +68276,16 @@
         <v>1713</v>
       </c>
       <c r="B1687" s="0" t="s">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="C1687" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E1687" s="0" t="s">
-        <v>2306</v>
+        <v>2305</v>
       </c>
       <c r="F1687" s="0" t="s">
-        <v>2452</v>
+        <v>2451</v>
       </c>
       <c r="G1687" s="0" t="n">
         <v>0</v>
@@ -68347,13 +68343,13 @@
         <v>1715</v>
       </c>
       <c r="B1689" s="0" t="s">
+        <v>2452</v>
+      </c>
+      <c r="C1689" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1689" s="0" t="s">
         <v>2453</v>
-      </c>
-      <c r="C1689" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1689" s="0" t="s">
-        <v>2454</v>
       </c>
       <c r="F1689" s="0" t="s">
         <v>22</v>
@@ -68379,7 +68375,7 @@
         <v>1716</v>
       </c>
       <c r="B1690" s="0" t="s">
-        <v>2455</v>
+        <v>2454</v>
       </c>
       <c r="C1690" s="0" t="n">
         <v>3</v>
@@ -68414,13 +68410,13 @@
         <v>1717</v>
       </c>
       <c r="B1691" s="0" t="s">
+        <v>2455</v>
+      </c>
+      <c r="C1691" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1691" s="0" t="s">
         <v>2456</v>
-      </c>
-      <c r="C1691" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1691" s="0" t="s">
-        <v>2457</v>
       </c>
       <c r="F1691" s="0" t="s">
         <v>635</v>
@@ -68449,7 +68445,7 @@
         <v>1718</v>
       </c>
       <c r="B1692" s="0" t="s">
-        <v>2458</v>
+        <v>2457</v>
       </c>
       <c r="C1692" s="0" t="n">
         <v>3</v>
@@ -68484,7 +68480,7 @@
         <v>1719</v>
       </c>
       <c r="B1693" s="0" t="s">
-        <v>2459</v>
+        <v>2458</v>
       </c>
       <c r="C1693" s="0" t="n">
         <v>3</v>
@@ -68519,7 +68515,7 @@
         <v>1720</v>
       </c>
       <c r="B1694" s="0" t="s">
-        <v>2460</v>
+        <v>2459</v>
       </c>
       <c r="C1694" s="0" t="n">
         <v>3</v>
@@ -68554,13 +68550,13 @@
         <v>1721</v>
       </c>
       <c r="B1695" s="0" t="s">
+        <v>2460</v>
+      </c>
+      <c r="C1695" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1695" s="0" t="s">
         <v>2461</v>
-      </c>
-      <c r="C1695" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1695" s="0" t="s">
-        <v>2462</v>
       </c>
       <c r="F1695" s="0" t="s">
         <v>1342</v>
@@ -68589,13 +68585,13 @@
         <v>1722</v>
       </c>
       <c r="B1696" s="0" t="s">
+        <v>2462</v>
+      </c>
+      <c r="C1696" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1696" s="0" t="s">
         <v>2463</v>
-      </c>
-      <c r="C1696" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1696" s="0" t="s">
-        <v>2464</v>
       </c>
       <c r="F1696" s="0" t="s">
         <v>464</v>
@@ -68624,7 +68620,7 @@
         <v>1723</v>
       </c>
       <c r="B1697" s="0" t="s">
-        <v>2465</v>
+        <v>2464</v>
       </c>
       <c r="C1697" s="0" t="n">
         <v>3</v>
@@ -68633,7 +68629,7 @@
         <v>384</v>
       </c>
       <c r="F1697" s="0" t="s">
-        <v>1772</v>
+        <v>1771</v>
       </c>
       <c r="G1697" s="0" t="n">
         <v>0</v>
@@ -68659,7 +68655,7 @@
         <v>1724</v>
       </c>
       <c r="B1698" s="0" t="s">
-        <v>2466</v>
+        <v>2465</v>
       </c>
       <c r="C1698" s="0" t="n">
         <v>3</v>
@@ -68668,7 +68664,7 @@
         <v>1355</v>
       </c>
       <c r="F1698" s="0" t="s">
-        <v>1927</v>
+        <v>1926</v>
       </c>
       <c r="G1698" s="0" t="n">
         <v>0</v>
@@ -68694,13 +68690,13 @@
         <v>1725</v>
       </c>
       <c r="B1699" s="0" t="s">
+        <v>2466</v>
+      </c>
+      <c r="C1699" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1699" s="0" t="s">
         <v>2467</v>
-      </c>
-      <c r="C1699" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1699" s="0" t="s">
-        <v>2468</v>
       </c>
       <c r="F1699" s="0" t="s">
         <v>447</v>
@@ -68729,13 +68725,13 @@
         <v>1726</v>
       </c>
       <c r="B1700" s="0" t="s">
+        <v>2468</v>
+      </c>
+      <c r="C1700" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1700" s="0" t="s">
         <v>2469</v>
-      </c>
-      <c r="C1700" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1700" s="0" t="s">
-        <v>2470</v>
       </c>
       <c r="F1700" s="0" t="s">
         <v>136</v>
@@ -68764,7 +68760,7 @@
         <v>1727</v>
       </c>
       <c r="B1701" s="0" t="s">
-        <v>2471</v>
+        <v>2470</v>
       </c>
       <c r="C1701" s="0" t="n">
         <v>3</v>
@@ -68799,16 +68795,16 @@
         <v>1728</v>
       </c>
       <c r="B1702" s="0" t="s">
+        <v>2471</v>
+      </c>
+      <c r="C1702" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1702" s="0" t="s">
         <v>2472</v>
       </c>
-      <c r="C1702" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1702" s="0" t="s">
-        <v>2473</v>
-      </c>
       <c r="F1702" s="0" t="s">
-        <v>1839</v>
+        <v>1838</v>
       </c>
       <c r="G1702" s="0" t="n">
         <v>0</v>
@@ -68834,13 +68830,13 @@
         <v>1729</v>
       </c>
       <c r="B1703" s="0" t="s">
+        <v>2473</v>
+      </c>
+      <c r="C1703" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1703" s="0" t="s">
         <v>2474</v>
-      </c>
-      <c r="C1703" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1703" s="0" t="s">
-        <v>2475</v>
       </c>
       <c r="F1703" s="0" t="s">
         <v>1101</v>
@@ -68869,13 +68865,13 @@
         <v>1730</v>
       </c>
       <c r="B1704" s="0" t="s">
+        <v>2475</v>
+      </c>
+      <c r="C1704" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1704" s="0" t="s">
         <v>2476</v>
-      </c>
-      <c r="C1704" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1704" s="0" t="s">
-        <v>2477</v>
       </c>
       <c r="F1704" s="0" t="s">
         <v>1429</v>
@@ -68904,7 +68900,7 @@
         <v>1731</v>
       </c>
       <c r="B1705" s="0" t="s">
-        <v>2478</v>
+        <v>2477</v>
       </c>
       <c r="C1705" s="0" t="n">
         <v>3</v>
@@ -68939,13 +68935,13 @@
         <v>1732</v>
       </c>
       <c r="B1706" s="0" t="s">
+        <v>2478</v>
+      </c>
+      <c r="C1706" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1706" s="0" t="s">
         <v>2479</v>
-      </c>
-      <c r="C1706" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1706" s="0" t="s">
-        <v>2480</v>
       </c>
       <c r="F1706" s="0" t="s">
         <v>528</v>
@@ -68974,13 +68970,13 @@
         <v>1733</v>
       </c>
       <c r="B1707" s="0" t="s">
+        <v>2480</v>
+      </c>
+      <c r="C1707" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1707" s="0" t="s">
         <v>2481</v>
-      </c>
-      <c r="C1707" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1707" s="0" t="s">
-        <v>2482</v>
       </c>
       <c r="F1707" s="0" t="s">
         <v>22</v>
@@ -69009,7 +69005,7 @@
         <v>1734</v>
       </c>
       <c r="B1708" s="0" t="s">
-        <v>2483</v>
+        <v>2482</v>
       </c>
       <c r="C1708" s="0" t="n">
         <v>3</v>
@@ -69044,7 +69040,7 @@
         <v>1735</v>
       </c>
       <c r="B1709" s="0" t="s">
-        <v>2484</v>
+        <v>2483</v>
       </c>
       <c r="C1709" s="0" t="n">
         <v>3</v>
@@ -69079,7 +69075,7 @@
         <v>1736</v>
       </c>
       <c r="B1710" s="0" t="s">
-        <v>2485</v>
+        <v>2484</v>
       </c>
       <c r="C1710" s="0" t="n">
         <v>3</v>
@@ -69114,7 +69110,7 @@
         <v>1737</v>
       </c>
       <c r="B1711" s="0" t="s">
-        <v>2486</v>
+        <v>2485</v>
       </c>
       <c r="C1711" s="0" t="n">
         <v>3</v>
@@ -69123,7 +69119,7 @@
         <v>129</v>
       </c>
       <c r="F1711" s="0" t="s">
-        <v>2487</v>
+        <v>2486</v>
       </c>
       <c r="G1711" s="0" t="n">
         <v>0</v>
@@ -69149,13 +69145,13 @@
         <v>1738</v>
       </c>
       <c r="B1712" s="0" t="s">
-        <v>2488</v>
+        <v>2487</v>
       </c>
       <c r="C1712" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E1712" s="0" t="s">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="F1712" s="0" t="s">
         <v>37</v>
@@ -69184,16 +69180,16 @@
         <v>1739</v>
       </c>
       <c r="B1713" s="0" t="s">
+        <v>2488</v>
+      </c>
+      <c r="C1713" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1713" s="0" t="s">
         <v>2489</v>
       </c>
-      <c r="C1713" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1713" s="0" t="s">
+      <c r="F1713" s="0" t="s">
         <v>2490</v>
-      </c>
-      <c r="F1713" s="0" t="s">
-        <v>2491</v>
       </c>
       <c r="G1713" s="0" t="n">
         <v>0</v>
@@ -69219,16 +69215,16 @@
         <v>1740</v>
       </c>
       <c r="B1714" s="0" t="s">
+        <v>2491</v>
+      </c>
+      <c r="C1714" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1714" s="0" t="s">
         <v>2492</v>
       </c>
-      <c r="C1714" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1714" s="0" t="s">
-        <v>2493</v>
-      </c>
       <c r="F1714" s="0" t="s">
-        <v>1830</v>
+        <v>1829</v>
       </c>
       <c r="G1714" s="0" t="n">
         <v>0</v>
@@ -69254,13 +69250,13 @@
         <v>1741</v>
       </c>
       <c r="B1715" s="0" t="s">
+        <v>2493</v>
+      </c>
+      <c r="C1715" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1715" s="0" t="s">
         <v>2494</v>
-      </c>
-      <c r="C1715" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1715" s="0" t="s">
-        <v>2495</v>
       </c>
       <c r="F1715" s="0" t="s">
         <v>528</v>
@@ -69289,16 +69285,16 @@
         <v>1742</v>
       </c>
       <c r="B1716" s="0" t="s">
+        <v>2495</v>
+      </c>
+      <c r="C1716" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1716" s="0" t="s">
+        <v>2476</v>
+      </c>
+      <c r="F1716" s="0" t="s">
         <v>2496</v>
-      </c>
-      <c r="C1716" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1716" s="0" t="s">
-        <v>2477</v>
-      </c>
-      <c r="F1716" s="0" t="s">
-        <v>2497</v>
       </c>
       <c r="G1716" s="0" t="n">
         <v>0</v>
@@ -69324,16 +69320,16 @@
         <v>1743</v>
       </c>
       <c r="B1717" s="0" t="s">
+        <v>2497</v>
+      </c>
+      <c r="C1717" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1717" s="0" t="s">
+        <v>2476</v>
+      </c>
+      <c r="F1717" s="0" t="s">
         <v>2498</v>
-      </c>
-      <c r="C1717" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1717" s="0" t="s">
-        <v>2477</v>
-      </c>
-      <c r="F1717" s="0" t="s">
-        <v>2499</v>
       </c>
       <c r="G1717" s="0" t="n">
         <v>0</v>
@@ -69359,13 +69355,13 @@
         <v>1744</v>
       </c>
       <c r="B1718" s="0" t="s">
+        <v>2499</v>
+      </c>
+      <c r="C1718" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1718" s="0" t="s">
         <v>2500</v>
-      </c>
-      <c r="C1718" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1718" s="0" t="s">
-        <v>2501</v>
       </c>
       <c r="F1718" s="0" t="s">
         <v>170</v>
@@ -69394,7 +69390,7 @@
         <v>1745</v>
       </c>
       <c r="B1719" s="0" t="s">
-        <v>2502</v>
+        <v>2501</v>
       </c>
       <c r="C1719" s="0" t="n">
         <v>3</v>
@@ -69429,13 +69425,13 @@
         <v>1746</v>
       </c>
       <c r="B1720" s="0" t="s">
+        <v>2502</v>
+      </c>
+      <c r="C1720" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1720" s="0" t="s">
         <v>2503</v>
-      </c>
-      <c r="C1720" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1720" s="0" t="s">
-        <v>2504</v>
       </c>
       <c r="F1720" s="0" t="s">
         <v>22</v>
@@ -69464,13 +69460,13 @@
         <v>1747</v>
       </c>
       <c r="B1721" s="0" t="s">
-        <v>2505</v>
+        <v>2504</v>
       </c>
       <c r="C1721" s="0" t="n">
         <v>4</v>
       </c>
       <c r="E1721" s="0" t="s">
-        <v>2410</v>
+        <v>2409</v>
       </c>
       <c r="F1721" s="0" t="s">
         <v>22</v>
@@ -69499,7 +69495,7 @@
         <v>1748</v>
       </c>
       <c r="B1722" s="0" t="s">
-        <v>2506</v>
+        <v>2505</v>
       </c>
       <c r="C1722" s="0" t="n">
         <v>3</v>
@@ -69575,7 +69571,7 @@
         <v>3</v>
       </c>
       <c r="E1724" s="0" t="s">
-        <v>2507</v>
+        <v>2506</v>
       </c>
       <c r="F1724" s="0" t="s">
         <v>22</v>
@@ -69604,13 +69600,13 @@
         <v>1751</v>
       </c>
       <c r="B1725" s="0" t="s">
+        <v>2507</v>
+      </c>
+      <c r="C1725" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1725" s="0" t="s">
         <v>2508</v>
-      </c>
-      <c r="C1725" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1725" s="0" t="s">
-        <v>2509</v>
       </c>
       <c r="F1725" s="0" t="s">
         <v>122</v>
@@ -69639,7 +69635,7 @@
         <v>1752</v>
       </c>
       <c r="B1726" s="0" t="s">
-        <v>2510</v>
+        <v>2509</v>
       </c>
       <c r="C1726" s="0" t="n">
         <v>3</v>
@@ -69680,7 +69676,7 @@
         <v>3</v>
       </c>
       <c r="E1727" s="0" t="s">
-        <v>2511</v>
+        <v>2510</v>
       </c>
       <c r="F1727" s="0" t="s">
         <v>22</v>
@@ -69706,7 +69702,7 @@
         <v>1754</v>
       </c>
       <c r="B1728" s="0" t="s">
-        <v>2069</v>
+        <v>2068</v>
       </c>
       <c r="C1728" s="0" t="n">
         <v>3</v>
@@ -69738,7 +69734,7 @@
         <v>1755</v>
       </c>
       <c r="B1729" s="0" t="s">
-        <v>2512</v>
+        <v>2511</v>
       </c>
       <c r="C1729" s="0" t="n">
         <v>3</v>
@@ -69773,7 +69769,7 @@
         <v>1756</v>
       </c>
       <c r="B1730" s="0" t="s">
-        <v>2513</v>
+        <v>2512</v>
       </c>
       <c r="C1730" s="0" t="n">
         <v>3</v>
@@ -69808,13 +69804,13 @@
         <v>1757</v>
       </c>
       <c r="B1731" s="0" t="s">
-        <v>2514</v>
+        <v>2513</v>
       </c>
       <c r="C1731" s="0" t="n">
         <v>4</v>
       </c>
       <c r="E1731" s="0" t="s">
-        <v>2515</v>
+        <v>2514</v>
       </c>
       <c r="F1731" s="0" t="s">
         <v>22</v>
@@ -69843,7 +69839,7 @@
         <v>1758</v>
       </c>
       <c r="B1732" s="0" t="s">
-        <v>2516</v>
+        <v>2515</v>
       </c>
       <c r="C1732" s="0" t="n">
         <v>4</v>
@@ -69878,13 +69874,13 @@
         <v>1759</v>
       </c>
       <c r="B1733" s="0" t="s">
-        <v>2517</v>
+        <v>2516</v>
       </c>
       <c r="C1733" s="0" t="n">
         <v>4</v>
       </c>
       <c r="E1733" s="0" t="s">
-        <v>2518</v>
+        <v>2517</v>
       </c>
       <c r="F1733" s="0" t="s">
         <v>1101</v>
@@ -69913,13 +69909,13 @@
         <v>1760</v>
       </c>
       <c r="B1734" s="0" t="s">
-        <v>2519</v>
+        <v>2518</v>
       </c>
       <c r="C1734" s="0" t="n">
         <v>4</v>
       </c>
       <c r="E1734" s="0" t="s">
-        <v>2520</v>
+        <v>2519</v>
       </c>
       <c r="F1734" s="0" t="s">
         <v>1101</v>
@@ -69948,7 +69944,7 @@
         <v>1761</v>
       </c>
       <c r="B1735" s="0" t="s">
-        <v>2521</v>
+        <v>2520</v>
       </c>
       <c r="C1735" s="0" t="n">
         <v>3</v>
@@ -69957,7 +69953,7 @@
         <v>1009</v>
       </c>
       <c r="F1735" s="0" t="s">
-        <v>2522</v>
+        <v>2521</v>
       </c>
       <c r="G1735" s="0" t="n">
         <v>0</v>
@@ -69983,13 +69979,13 @@
         <v>1762</v>
       </c>
       <c r="B1736" s="0" t="s">
+        <v>2522</v>
+      </c>
+      <c r="C1736" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1736" s="0" t="s">
         <v>2523</v>
-      </c>
-      <c r="C1736" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1736" s="0" t="s">
-        <v>2524</v>
       </c>
       <c r="F1736" s="0" t="s">
         <v>88</v>
@@ -70018,13 +70014,13 @@
         <v>1763</v>
       </c>
       <c r="B1737" s="0" t="s">
+        <v>2524</v>
+      </c>
+      <c r="C1737" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1737" s="0" t="s">
         <v>2525</v>
-      </c>
-      <c r="C1737" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1737" s="0" t="s">
-        <v>2526</v>
       </c>
       <c r="F1737" s="0" t="s">
         <v>22</v>
@@ -70053,13 +70049,13 @@
         <v>1764</v>
       </c>
       <c r="B1738" s="0" t="s">
+        <v>2526</v>
+      </c>
+      <c r="C1738" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1738" s="0" t="s">
         <v>2527</v>
-      </c>
-      <c r="C1738" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1738" s="0" t="s">
-        <v>2528</v>
       </c>
       <c r="F1738" s="0" t="s">
         <v>930</v>
@@ -70088,16 +70084,16 @@
         <v>1765</v>
       </c>
       <c r="B1739" s="0" t="s">
+        <v>2528</v>
+      </c>
+      <c r="C1739" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1739" s="0" t="s">
         <v>2529</v>
       </c>
-      <c r="C1739" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1739" s="0" t="s">
-        <v>2530</v>
-      </c>
       <c r="F1739" s="0" t="s">
-        <v>2104</v>
+        <v>2103</v>
       </c>
       <c r="G1739" s="0" t="n">
         <v>0</v>
@@ -70123,13 +70119,13 @@
         <v>1766</v>
       </c>
       <c r="B1740" s="0" t="s">
+        <v>2530</v>
+      </c>
+      <c r="C1740" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1740" s="0" t="s">
         <v>2531</v>
-      </c>
-      <c r="C1740" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1740" s="0" t="s">
-        <v>2532</v>
       </c>
       <c r="F1740" s="0" t="s">
         <v>742</v>
@@ -70158,13 +70154,13 @@
         <v>1767</v>
       </c>
       <c r="B1741" s="0" t="s">
+        <v>2532</v>
+      </c>
+      <c r="C1741" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1741" s="0" t="s">
         <v>2533</v>
-      </c>
-      <c r="C1741" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1741" s="0" t="s">
-        <v>2534</v>
       </c>
       <c r="F1741" s="0" t="s">
         <v>1101</v>
@@ -70193,16 +70189,16 @@
         <v>1768</v>
       </c>
       <c r="B1742" s="0" t="s">
+        <v>2534</v>
+      </c>
+      <c r="C1742" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1742" s="0" t="s">
         <v>2535</v>
       </c>
-      <c r="C1742" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1742" s="0" t="s">
-        <v>2536</v>
-      </c>
       <c r="F1742" s="0" t="s">
-        <v>1839</v>
+        <v>1838</v>
       </c>
       <c r="G1742" s="0" t="n">
         <v>0</v>
@@ -70228,13 +70224,13 @@
         <v>1769</v>
       </c>
       <c r="B1743" s="0" t="s">
-        <v>1819</v>
+        <v>1818</v>
       </c>
       <c r="C1743" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E1743" s="0" t="s">
-        <v>2537</v>
+        <v>2536</v>
       </c>
       <c r="F1743" s="0" t="s">
         <v>22</v>
@@ -70260,7 +70256,7 @@
         <v>1770</v>
       </c>
       <c r="B1744" s="0" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
       <c r="C1744" s="0" t="n">
         <v>3</v>
@@ -70295,7 +70291,7 @@
         <v>1771</v>
       </c>
       <c r="B1745" s="0" t="s">
-        <v>2538</v>
+        <v>2537</v>
       </c>
       <c r="C1745" s="0" t="n">
         <v>3</v>
@@ -70327,13 +70323,13 @@
         <v>1772</v>
       </c>
       <c r="B1746" s="0" t="s">
-        <v>2539</v>
+        <v>2538</v>
       </c>
       <c r="C1746" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E1746" s="0" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="F1746" s="0" t="s">
         <v>88</v>
@@ -70362,7 +70358,7 @@
         <v>1773</v>
       </c>
       <c r="B1747" s="0" t="s">
-        <v>2540</v>
+        <v>2539</v>
       </c>
       <c r="C1747" s="0" t="n">
         <v>3</v>
@@ -70371,7 +70367,7 @@
         <v>306</v>
       </c>
       <c r="F1747" s="0" t="s">
-        <v>2541</v>
+        <v>2540</v>
       </c>
       <c r="G1747" s="0" t="n">
         <v>0</v>
@@ -70397,7 +70393,7 @@
         <v>1774</v>
       </c>
       <c r="B1748" s="0" t="s">
-        <v>2542</v>
+        <v>2541</v>
       </c>
       <c r="C1748" s="0" t="n">
         <v>3</v>
@@ -70432,13 +70428,13 @@
         <v>1775</v>
       </c>
       <c r="B1749" s="0" t="s">
+        <v>2542</v>
+      </c>
+      <c r="C1749" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1749" s="0" t="s">
         <v>2543</v>
-      </c>
-      <c r="C1749" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1749" s="0" t="s">
-        <v>2544</v>
       </c>
       <c r="F1749" s="0" t="s">
         <v>22</v>
@@ -70464,13 +70460,13 @@
         <v>1776</v>
       </c>
       <c r="B1750" s="0" t="s">
-        <v>2545</v>
+        <v>2544</v>
       </c>
       <c r="C1750" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E1750" s="0" t="s">
-        <v>2544</v>
+        <v>2543</v>
       </c>
       <c r="F1750" s="0" t="s">
         <v>22</v>
@@ -70496,13 +70492,13 @@
         <v>1777</v>
       </c>
       <c r="B1751" s="0" t="s">
+        <v>2545</v>
+      </c>
+      <c r="C1751" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1751" s="0" t="s">
         <v>2546</v>
-      </c>
-      <c r="C1751" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1751" s="0" t="s">
-        <v>2547</v>
       </c>
       <c r="F1751" s="0" t="s">
         <v>22</v>
@@ -70528,16 +70524,16 @@
         <v>1778</v>
       </c>
       <c r="B1752" s="0" t="s">
+        <v>2547</v>
+      </c>
+      <c r="C1752" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1752" s="0" t="s">
         <v>2548</v>
       </c>
-      <c r="C1752" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1752" s="0" t="s">
+      <c r="F1752" s="0" t="s">
         <v>2549</v>
-      </c>
-      <c r="F1752" s="0" t="s">
-        <v>2550</v>
       </c>
       <c r="G1752" s="0" t="n">
         <v>0</v>
@@ -70563,7 +70559,7 @@
         <v>1779</v>
       </c>
       <c r="B1753" s="0" t="s">
-        <v>2551</v>
+        <v>2550</v>
       </c>
       <c r="C1753" s="0" t="n">
         <v>3</v>
@@ -70572,7 +70568,7 @@
         <v>1113</v>
       </c>
       <c r="F1753" s="0" t="s">
-        <v>2552</v>
+        <v>2551</v>
       </c>
       <c r="G1753" s="0" t="n">
         <v>0</v>
@@ -70598,16 +70594,16 @@
         <v>1780</v>
       </c>
       <c r="B1754" s="0" t="s">
+        <v>2552</v>
+      </c>
+      <c r="C1754" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1754" s="0" t="s">
         <v>2553</v>
       </c>
-      <c r="C1754" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1754" s="0" t="s">
-        <v>2554</v>
-      </c>
       <c r="F1754" s="0" t="s">
-        <v>1898</v>
+        <v>1897</v>
       </c>
       <c r="G1754" s="0" t="n">
         <v>0</v>
@@ -70633,7 +70629,7 @@
         <v>1781</v>
       </c>
       <c r="B1755" s="0" t="s">
-        <v>2555</v>
+        <v>2554</v>
       </c>
       <c r="C1755" s="0" t="n">
         <v>3</v>
@@ -70668,7 +70664,7 @@
         <v>1782</v>
       </c>
       <c r="B1756" s="0" t="s">
-        <v>2556</v>
+        <v>2555</v>
       </c>
       <c r="C1756" s="0" t="n">
         <v>3</v>
@@ -70700,13 +70696,13 @@
         <v>1783</v>
       </c>
       <c r="B1757" s="0" t="s">
-        <v>2557</v>
+        <v>2556</v>
       </c>
       <c r="C1757" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E1757" s="0" t="s">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="F1757" s="0" t="s">
         <v>22</v>
@@ -70732,7 +70728,7 @@
         <v>1784</v>
       </c>
       <c r="B1758" s="0" t="s">
-        <v>2558</v>
+        <v>2557</v>
       </c>
       <c r="C1758" s="0" t="n">
         <v>3</v>
@@ -70764,7 +70760,7 @@
         <v>1785</v>
       </c>
       <c r="B1759" s="0" t="s">
-        <v>2559</v>
+        <v>2558</v>
       </c>
       <c r="C1759" s="0" t="n">
         <v>3</v>
@@ -70802,7 +70798,7 @@
         <v>3</v>
       </c>
       <c r="E1760" s="0" t="s">
-        <v>2560</v>
+        <v>2559</v>
       </c>
       <c r="F1760" s="0" t="s">
         <v>1238</v>
@@ -70831,13 +70827,13 @@
         <v>1787</v>
       </c>
       <c r="B1761" s="0" t="s">
+        <v>2560</v>
+      </c>
+      <c r="C1761" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1761" s="0" t="s">
         <v>2561</v>
-      </c>
-      <c r="C1761" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1761" s="0" t="s">
-        <v>2562</v>
       </c>
       <c r="F1761" s="0" t="s">
         <v>22</v>
@@ -70863,13 +70859,13 @@
         <v>1788</v>
       </c>
       <c r="B1762" s="0" t="s">
+        <v>2562</v>
+      </c>
+      <c r="C1762" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1762" s="0" t="s">
         <v>2563</v>
-      </c>
-      <c r="C1762" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1762" s="0" t="s">
-        <v>2564</v>
       </c>
       <c r="F1762" s="0" t="s">
         <v>27</v>
@@ -70898,13 +70894,13 @@
         <v>1789</v>
       </c>
       <c r="B1763" s="0" t="s">
+        <v>2564</v>
+      </c>
+      <c r="C1763" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1763" s="0" t="s">
         <v>2565</v>
-      </c>
-      <c r="C1763" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1763" s="0" t="s">
-        <v>2566</v>
       </c>
       <c r="F1763" s="0" t="s">
         <v>22</v>
@@ -70933,7 +70929,7 @@
         <v>1790</v>
       </c>
       <c r="B1764" s="0" t="s">
-        <v>2567</v>
+        <v>2566</v>
       </c>
       <c r="C1764" s="0" t="n">
         <v>3</v>
@@ -70965,13 +70961,13 @@
         <v>1791</v>
       </c>
       <c r="B1765" s="0" t="s">
-        <v>2568</v>
+        <v>2567</v>
       </c>
       <c r="C1765" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E1765" s="0" t="s">
-        <v>1948</v>
+        <v>1947</v>
       </c>
       <c r="F1765" s="0" t="s">
         <v>22</v>
@@ -71000,16 +70996,16 @@
         <v>1792</v>
       </c>
       <c r="B1766" s="0" t="s">
+        <v>2568</v>
+      </c>
+      <c r="C1766" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1766" s="0" t="s">
         <v>2569</v>
       </c>
-      <c r="C1766" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1766" s="0" t="s">
+      <c r="F1766" s="0" t="s">
         <v>2570</v>
-      </c>
-      <c r="F1766" s="0" t="s">
-        <v>2571</v>
       </c>
       <c r="G1766" s="0" t="n">
         <v>0</v>
@@ -71032,7 +71028,7 @@
         <v>1793</v>
       </c>
       <c r="B1767" s="0" t="s">
-        <v>2572</v>
+        <v>2571</v>
       </c>
       <c r="C1767" s="0" t="n">
         <v>3</v>
@@ -71064,13 +71060,13 @@
         <v>1794</v>
       </c>
       <c r="B1768" s="0" t="s">
+        <v>2572</v>
+      </c>
+      <c r="C1768" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1768" s="0" t="s">
         <v>2573</v>
-      </c>
-      <c r="C1768" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1768" s="0" t="s">
-        <v>2574</v>
       </c>
       <c r="F1768" s="0" t="s">
         <v>22</v>
@@ -71099,13 +71095,13 @@
         <v>1795</v>
       </c>
       <c r="B1769" s="0" t="s">
+        <v>2574</v>
+      </c>
+      <c r="C1769" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1769" s="0" t="s">
         <v>2575</v>
-      </c>
-      <c r="C1769" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1769" s="0" t="s">
-        <v>2576</v>
       </c>
       <c r="F1769" s="0" t="s">
         <v>447</v>
@@ -71134,7 +71130,7 @@
         <v>1796</v>
       </c>
       <c r="B1770" s="0" t="s">
-        <v>2577</v>
+        <v>2576</v>
       </c>
       <c r="C1770" s="0" t="n">
         <v>3</v>
@@ -71169,7 +71165,7 @@
         <v>1797</v>
       </c>
       <c r="B1771" s="0" t="s">
-        <v>2578</v>
+        <v>2577</v>
       </c>
       <c r="C1771" s="0" t="n">
         <v>4</v>
@@ -71178,7 +71174,7 @@
         <v>1020</v>
       </c>
       <c r="F1771" s="0" t="s">
-        <v>2579</v>
+        <v>2578</v>
       </c>
       <c r="G1771" s="0" t="n">
         <v>0</v>
@@ -71204,16 +71200,16 @@
         <v>1798</v>
       </c>
       <c r="B1772" s="0" t="s">
-        <v>2580</v>
+        <v>2579</v>
       </c>
       <c r="C1772" s="0" t="n">
         <v>4</v>
       </c>
       <c r="E1772" s="0" t="s">
+        <v>2580</v>
+      </c>
+      <c r="F1772" s="0" t="s">
         <v>2581</v>
-      </c>
-      <c r="F1772" s="0" t="s">
-        <v>2582</v>
       </c>
       <c r="G1772" s="0" t="n">
         <v>0</v>
@@ -71239,7 +71235,7 @@
         <v>1799</v>
       </c>
       <c r="B1773" s="0" t="s">
-        <v>2583</v>
+        <v>2582</v>
       </c>
       <c r="C1773" s="0" t="n">
         <v>4</v>
@@ -71274,13 +71270,13 @@
         <v>1800</v>
       </c>
       <c r="B1774" s="0" t="s">
-        <v>2584</v>
+        <v>2583</v>
       </c>
       <c r="C1774" s="0" t="n">
         <v>4</v>
       </c>
       <c r="E1774" s="0" t="s">
-        <v>2585</v>
+        <v>2584</v>
       </c>
       <c r="F1774" s="0" t="s">
         <v>22</v>
@@ -71309,7 +71305,7 @@
         <v>1801</v>
       </c>
       <c r="B1775" s="0" t="s">
-        <v>2586</v>
+        <v>2585</v>
       </c>
       <c r="C1775" s="0" t="n">
         <v>4</v>
@@ -71344,13 +71340,13 @@
         <v>1802</v>
       </c>
       <c r="B1776" s="0" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="C1776" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E1776" s="0" t="s">
-        <v>2380</v>
+        <v>2379</v>
       </c>
       <c r="F1776" s="0" t="s">
         <v>106</v>
@@ -71376,16 +71372,16 @@
         <v>1803</v>
       </c>
       <c r="B1777" s="0" t="s">
+        <v>2586</v>
+      </c>
+      <c r="C1777" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1777" s="0" t="s">
         <v>2587</v>
       </c>
-      <c r="C1777" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1777" s="0" t="s">
-        <v>2588</v>
-      </c>
       <c r="F1777" s="0" t="s">
-        <v>2487</v>
+        <v>2486</v>
       </c>
       <c r="G1777" s="0" t="n">
         <v>0</v>
@@ -71411,13 +71407,13 @@
         <v>1804</v>
       </c>
       <c r="B1778" s="0" t="s">
+        <v>2588</v>
+      </c>
+      <c r="C1778" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1778" s="0" t="s">
         <v>2589</v>
-      </c>
-      <c r="C1778" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1778" s="0" t="s">
-        <v>2590</v>
       </c>
       <c r="F1778" s="0" t="s">
         <v>27</v>
@@ -71443,7 +71439,7 @@
         <v>1805</v>
       </c>
       <c r="B1779" s="0" t="s">
-        <v>2591</v>
+        <v>2590</v>
       </c>
       <c r="C1779" s="0" t="n">
         <v>3</v>
@@ -71475,7 +71471,7 @@
         <v>1806</v>
       </c>
       <c r="B1780" s="0" t="s">
-        <v>2592</v>
+        <v>2591</v>
       </c>
       <c r="C1780" s="0" t="n">
         <v>3</v>
@@ -71507,16 +71503,16 @@
         <v>1807</v>
       </c>
       <c r="B1781" s="0" t="s">
+        <v>2592</v>
+      </c>
+      <c r="C1781" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1781" s="0" t="s">
         <v>2593</v>
       </c>
-      <c r="C1781" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1781" s="0" t="s">
+      <c r="F1781" s="0" t="s">
         <v>2594</v>
-      </c>
-      <c r="F1781" s="0" t="s">
-        <v>2595</v>
       </c>
       <c r="G1781" s="0" t="n">
         <v>0</v>
@@ -71542,13 +71538,13 @@
         <v>1808</v>
       </c>
       <c r="B1782" s="0" t="s">
-        <v>1798</v>
+        <v>1797</v>
       </c>
       <c r="C1782" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E1782" s="0" t="s">
-        <v>2596</v>
+        <v>2595</v>
       </c>
       <c r="F1782" s="0" t="s">
         <v>22</v>
@@ -71577,13 +71573,13 @@
         <v>1809</v>
       </c>
       <c r="B1783" s="0" t="s">
+        <v>2596</v>
+      </c>
+      <c r="C1783" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1783" s="0" t="s">
         <v>2597</v>
-      </c>
-      <c r="C1783" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1783" s="0" t="s">
-        <v>2598</v>
       </c>
       <c r="F1783" s="0" t="s">
         <v>1596</v>
@@ -71612,7 +71608,7 @@
         <v>1810</v>
       </c>
       <c r="B1784" s="0" t="s">
-        <v>2599</v>
+        <v>2598</v>
       </c>
       <c r="C1784" s="0" t="n">
         <v>3</v>
@@ -71644,7 +71640,7 @@
         <v>1811</v>
       </c>
       <c r="B1785" s="0" t="s">
-        <v>2600</v>
+        <v>2599</v>
       </c>
       <c r="C1785" s="0" t="n">
         <v>3</v>
@@ -71676,7 +71672,7 @@
         <v>1812</v>
       </c>
       <c r="B1786" s="0" t="s">
-        <v>2601</v>
+        <v>2600</v>
       </c>
       <c r="C1786" s="0" t="n">
         <v>3</v>
@@ -71708,7 +71704,7 @@
         <v>1813</v>
       </c>
       <c r="B1787" s="0" t="s">
-        <v>2602</v>
+        <v>2601</v>
       </c>
       <c r="C1787" s="0" t="n">
         <v>3</v>
@@ -71740,7 +71736,7 @@
         <v>1814</v>
       </c>
       <c r="B1788" s="0" t="s">
-        <v>2603</v>
+        <v>2602</v>
       </c>
       <c r="C1788" s="0" t="n">
         <v>3</v>
@@ -71772,7 +71768,7 @@
         <v>1815</v>
       </c>
       <c r="B1789" s="0" t="s">
-        <v>2604</v>
+        <v>2603</v>
       </c>
       <c r="C1789" s="0" t="n">
         <v>3</v>
@@ -71804,7 +71800,7 @@
         <v>1816</v>
       </c>
       <c r="B1790" s="0" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
       <c r="C1790" s="0" t="n">
         <v>3</v>
@@ -71836,7 +71832,7 @@
         <v>1817</v>
       </c>
       <c r="B1791" s="0" t="s">
-        <v>2606</v>
+        <v>2605</v>
       </c>
       <c r="C1791" s="0" t="n">
         <v>3</v>
@@ -71868,7 +71864,7 @@
         <v>1818</v>
       </c>
       <c r="B1792" s="0" t="s">
-        <v>2607</v>
+        <v>2606</v>
       </c>
       <c r="C1792" s="0" t="n">
         <v>3</v>
@@ -71900,7 +71896,7 @@
         <v>1819</v>
       </c>
       <c r="B1793" s="0" t="s">
-        <v>2608</v>
+        <v>2607</v>
       </c>
       <c r="C1793" s="0" t="n">
         <v>3</v>
